--- a/AA_improved_bus_planning.xlsx
+++ b/AA_improved_bus_planning.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H389"/>
+  <dimension ref="A1:H411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6974,48 +6974,46 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
-        <v>1.596527777777778</v>
+        <v>1.590972222222222</v>
       </c>
       <c r="D193" s="2" t="n">
-        <v>1.6125</v>
+        <v>1.59375</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F193" t="n">
-        <v>401</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr"/>
       <c r="G193" t="n">
-        <v>10.8036</v>
+        <v>1.979999999999999</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C194" s="2" t="n">
         <v>1.596527777777778</v>
       </c>
       <c r="D194" s="2" t="n">
-        <v>1.611805555555556</v>
+        <v>1.6125</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -7023,33 +7021,33 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G194" t="n">
-        <v>12.3</v>
+        <v>10.8036</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
-        <v>1.597916666666667</v>
+        <v>1.596527777777778</v>
       </c>
       <c r="D195" s="2" t="n">
-        <v>1.613194444444444</v>
+        <v>1.611805555555556</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -7060,11 +7058,11 @@
         <v>400</v>
       </c>
       <c r="G195" t="n">
-        <v>12.8496</v>
+        <v>12.3</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -7076,48 +7074,46 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
-        <v>1.6</v>
+        <v>1.596875</v>
       </c>
       <c r="D196" s="2" t="n">
-        <v>1.615277777777778</v>
+        <v>1.599652777777778</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F196" t="n">
-        <v>400</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr"/>
       <c r="G196" t="n">
-        <v>12.8496</v>
+        <v>1.979999999999999</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
-        <v>1.601388888888889</v>
+        <v>1.597916666666667</v>
       </c>
       <c r="D197" s="2" t="n">
-        <v>1.617708333333333</v>
+        <v>1.613194444444444</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -7125,21 +7121,21 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G197" t="n">
-        <v>10.86</v>
+        <v>12.8496</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -7148,25 +7144,25 @@
         </is>
       </c>
       <c r="C198" s="2" t="n">
-        <v>1.602083333333333</v>
+        <v>1.597222222222222</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>1.617361111111111</v>
+        <v>1.6</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>service trip</t>
+          <t>material trip</t>
         </is>
       </c>
       <c r="F198" t="n">
         <v>400</v>
       </c>
       <c r="G198" t="n">
-        <v>12.3</v>
+        <v>1.98</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -7182,10 +7178,10 @@
         </is>
       </c>
       <c r="C199" s="2" t="n">
-        <v>1.603472222222222</v>
+        <v>1.6</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>1.619444444444444</v>
+        <v>1.615277777777778</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -7193,14 +7189,14 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G199" t="n">
-        <v>10.8036</v>
+        <v>12.8496</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -7216,10 +7212,10 @@
         </is>
       </c>
       <c r="C200" s="2" t="n">
-        <v>1.606944444444444</v>
+        <v>1.601388888888889</v>
       </c>
       <c r="D200" s="2" t="n">
-        <v>1.622222222222222</v>
+        <v>1.617708333333333</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -7227,33 +7223,33 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G200" t="n">
-        <v>12.3</v>
+        <v>10.86</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
-        <v>1.608333333333333</v>
+        <v>1.602083333333333</v>
       </c>
       <c r="D201" s="2" t="n">
-        <v>1.623611111111111</v>
+        <v>1.617361111111111</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -7264,30 +7260,30 @@
         <v>400</v>
       </c>
       <c r="G201" t="n">
-        <v>12.8496</v>
+        <v>12.3</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
-        <v>1.608333333333333</v>
+        <v>1.603472222222222</v>
       </c>
       <c r="D202" s="2" t="n">
-        <v>1.624652777777778</v>
+        <v>1.619444444444444</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -7298,45 +7294,43 @@
         <v>401</v>
       </c>
       <c r="G202" t="n">
-        <v>10.86</v>
+        <v>10.8036</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
-        <v>1.610416666666667</v>
+        <v>1.59375</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>1.626388888888889</v>
+        <v>1.606944444444444</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F203" t="n">
-        <v>401</v>
-      </c>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
       <c r="G203" t="n">
-        <v>10.8036</v>
+        <v>-142.5</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
@@ -7352,10 +7346,10 @@
         </is>
       </c>
       <c r="C204" s="2" t="n">
-        <v>1.615277777777778</v>
+        <v>1.606944444444444</v>
       </c>
       <c r="D204" s="2" t="n">
-        <v>1.631597222222222</v>
+        <v>1.622222222222222</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -7363,33 +7357,33 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G204" t="n">
-        <v>10.86</v>
+        <v>12.3</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
-        <v>1.617361111111111</v>
+        <v>1.608333333333333</v>
       </c>
       <c r="D205" s="2" t="n">
-        <v>1.632638888888889</v>
+        <v>1.623611111111111</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -7400,30 +7394,30 @@
         <v>400</v>
       </c>
       <c r="G205" t="n">
-        <v>12.3</v>
+        <v>12.8496</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C206" s="2" t="n">
-        <v>1.617361111111111</v>
+        <v>1.608333333333333</v>
       </c>
       <c r="D206" s="2" t="n">
-        <v>1.633333333333333</v>
+        <v>1.624652777777778</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -7434,98 +7428,94 @@
         <v>401</v>
       </c>
       <c r="G206" t="n">
-        <v>10.8036</v>
+        <v>10.86</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C207" s="2" t="n">
-        <v>1.61875</v>
+        <v>1.599652777777778</v>
       </c>
       <c r="D207" s="2" t="n">
-        <v>1.634027777777778</v>
+        <v>1.610416666666667</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F207" t="n">
-        <v>400</v>
-      </c>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr"/>
       <c r="G207" t="n">
-        <v>12.8496</v>
+        <v>-116.25</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
-        <v>1.620833333333333</v>
+        <v>1.606944444444444</v>
       </c>
       <c r="D208" s="2" t="n">
-        <v>1.636111111111111</v>
+        <v>1.609722222222222</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F208" t="n">
-        <v>400</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr"/>
       <c r="G208" t="n">
-        <v>12.8496</v>
+        <v>1.98</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C209" s="2" t="n">
-        <v>1.622222222222222</v>
+        <v>1.610416666666667</v>
       </c>
       <c r="D209" s="2" t="n">
-        <v>1.638541666666667</v>
+        <v>1.626388888888889</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7536,11 +7526,11 @@
         <v>401</v>
       </c>
       <c r="G209" t="n">
-        <v>10.86</v>
+        <v>10.8036</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
@@ -7556,10 +7546,10 @@
         </is>
       </c>
       <c r="C210" s="2" t="n">
-        <v>1.622916666666667</v>
+        <v>1.615277777777778</v>
       </c>
       <c r="D210" s="2" t="n">
-        <v>1.638194444444444</v>
+        <v>1.631597222222222</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7567,33 +7557,33 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G210" t="n">
-        <v>12.3</v>
+        <v>10.86</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
-        <v>1.624305555555555</v>
+        <v>1.617361111111111</v>
       </c>
       <c r="D211" s="2" t="n">
-        <v>1.640277777777778</v>
+        <v>1.632638888888889</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -7601,101 +7591,97 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G211" t="n">
-        <v>10.8036</v>
+        <v>12.3</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
-        <v>1.627777777777778</v>
+        <v>1.611805555555556</v>
       </c>
       <c r="D212" s="2" t="n">
-        <v>1.643055555555556</v>
+        <v>1.614583333333333</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F212" t="n">
-        <v>400</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr"/>
       <c r="G212" t="n">
-        <v>12.3</v>
+        <v>1.979999999999999</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
-        <v>1.629166666666667</v>
+        <v>1.610416666666667</v>
       </c>
       <c r="D213" s="2" t="n">
-        <v>1.644444444444444</v>
+        <v>1.613194444444444</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F213" t="n">
-        <v>400</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr"/>
       <c r="G213" t="n">
-        <v>12.8496</v>
+        <v>1.98</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C214" s="2" t="n">
-        <v>1.629166666666667</v>
+        <v>1.617361111111111</v>
       </c>
       <c r="D214" s="2" t="n">
-        <v>1.645486111111111</v>
+        <v>1.633333333333333</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -7706,11 +7692,11 @@
         <v>401</v>
       </c>
       <c r="G214" t="n">
-        <v>10.86</v>
+        <v>10.8036</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
@@ -7726,10 +7712,10 @@
         </is>
       </c>
       <c r="C215" s="2" t="n">
-        <v>1.63125</v>
+        <v>1.61875</v>
       </c>
       <c r="D215" s="2" t="n">
-        <v>1.647222222222222</v>
+        <v>1.634027777777778</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -7737,48 +7723,48 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G215" t="n">
-        <v>10.8036</v>
+        <v>12.8496</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
+        <v>1.620833333333333</v>
+      </c>
+      <c r="D216" s="2" t="n">
         <v>1.636111111111111</v>
       </c>
-      <c r="D216" s="2" t="n">
-        <v>1.652430555555556</v>
-      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>service trip</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G216" t="n">
-        <v>10.86</v>
+        <v>12.8496</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
@@ -7794,10 +7780,10 @@
         </is>
       </c>
       <c r="C217" s="2" t="n">
-        <v>1.638194444444444</v>
+        <v>1.622222222222222</v>
       </c>
       <c r="D217" s="2" t="n">
-        <v>1.653472222222222</v>
+        <v>1.638541666666667</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -7805,48 +7791,48 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G217" t="n">
-        <v>12.3</v>
+        <v>10.86</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
+        <v>1.622916666666667</v>
+      </c>
+      <c r="D218" s="2" t="n">
         <v>1.638194444444444</v>
       </c>
-      <c r="D218" s="2" t="n">
-        <v>1.654166666666667</v>
-      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>service trip</t>
         </is>
       </c>
       <c r="F218" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G218" t="n">
-        <v>10.8036</v>
+        <v>12.3</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -7862,10 +7848,10 @@
         </is>
       </c>
       <c r="C219" s="2" t="n">
-        <v>1.639583333333333</v>
+        <v>1.624305555555555</v>
       </c>
       <c r="D219" s="2" t="n">
-        <v>1.654861111111111</v>
+        <v>1.640277777777778</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -7873,48 +7859,46 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G219" t="n">
-        <v>12.8496</v>
+        <v>10.8036</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C220" s="2" t="n">
-        <v>1.641666666666667</v>
+        <v>1.614583333333333</v>
       </c>
       <c r="D220" s="2" t="n">
-        <v>1.656944444444445</v>
+        <v>1.627777777777778</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F220" t="n">
-        <v>400</v>
-      </c>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr"/>
       <c r="G220" t="n">
-        <v>12.8496</v>
+        <v>-142.5</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -7930,44 +7914,44 @@
         </is>
       </c>
       <c r="C221" s="2" t="n">
+        <v>1.627777777777778</v>
+      </c>
+      <c r="D221" s="2" t="n">
         <v>1.643055555555556</v>
       </c>
-      <c r="D221" s="2" t="n">
-        <v>1.659375</v>
-      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>service trip</t>
         </is>
       </c>
       <c r="F221" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G221" t="n">
-        <v>10.86</v>
+        <v>12.3</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C222" s="2" t="n">
-        <v>1.64375</v>
+        <v>1.629166666666667</v>
       </c>
       <c r="D222" s="2" t="n">
-        <v>1.659027777777778</v>
+        <v>1.644444444444444</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7978,30 +7962,30 @@
         <v>400</v>
       </c>
       <c r="G222" t="n">
-        <v>12.3</v>
+        <v>12.8496</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C223" s="2" t="n">
-        <v>1.645138888888889</v>
+        <v>1.629166666666667</v>
       </c>
       <c r="D223" s="2" t="n">
-        <v>1.661111111111111</v>
+        <v>1.645486111111111</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -8012,30 +7996,30 @@
         <v>401</v>
       </c>
       <c r="G223" t="n">
-        <v>10.8036</v>
+        <v>10.86</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C224" s="2" t="n">
-        <v>1.648611111111111</v>
+        <v>1.63125</v>
       </c>
       <c r="D224" s="2" t="n">
-        <v>1.663888888888889</v>
+        <v>1.647222222222222</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -8043,33 +8027,33 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G224" t="n">
-        <v>12.3</v>
+        <v>10.8036</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C225" s="2" t="n">
-        <v>1.65</v>
+        <v>1.636111111111111</v>
       </c>
       <c r="D225" s="2" t="n">
-        <v>1.665277777777778</v>
+        <v>1.652430555555556</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -8077,14 +8061,14 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G225" t="n">
-        <v>12.8496</v>
+        <v>10.86</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
@@ -8100,10 +8084,10 @@
         </is>
       </c>
       <c r="C226" s="2" t="n">
-        <v>1.65</v>
+        <v>1.638194444444444</v>
       </c>
       <c r="D226" s="2" t="n">
-        <v>1.666319444444444</v>
+        <v>1.653472222222222</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -8111,67 +8095,65 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G226" t="n">
-        <v>10.86</v>
+        <v>12.3</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C227" s="2" t="n">
-        <v>1.652083333333333</v>
+        <v>1.627777777777778</v>
       </c>
       <c r="D227" s="2" t="n">
-        <v>1.668055555555556</v>
+        <v>1.630555555555556</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F227" t="n">
-        <v>401</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr"/>
       <c r="G227" t="n">
-        <v>10.8036</v>
+        <v>1.98</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C228" s="2" t="n">
-        <v>1.656944444444445</v>
+        <v>1.638194444444444</v>
       </c>
       <c r="D228" s="2" t="n">
-        <v>1.673263888888889</v>
+        <v>1.654166666666667</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -8182,30 +8164,30 @@
         <v>401</v>
       </c>
       <c r="G228" t="n">
-        <v>10.86</v>
+        <v>10.8036</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C229" s="2" t="n">
-        <v>1.659027777777778</v>
+        <v>1.639583333333333</v>
       </c>
       <c r="D229" s="2" t="n">
-        <v>1.674305555555556</v>
+        <v>1.654861111111111</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -8216,11 +8198,11 @@
         <v>400</v>
       </c>
       <c r="G229" t="n">
-        <v>12.3</v>
+        <v>12.8496</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
@@ -8236,10 +8218,10 @@
         </is>
       </c>
       <c r="C230" s="2" t="n">
-        <v>1.659027777777778</v>
+        <v>1.641666666666667</v>
       </c>
       <c r="D230" s="2" t="n">
-        <v>1.675</v>
+        <v>1.656944444444445</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -8247,33 +8229,33 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G230" t="n">
-        <v>10.8036</v>
+        <v>12.8496</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C231" s="2" t="n">
-        <v>1.660416666666667</v>
+        <v>1.643055555555556</v>
       </c>
       <c r="D231" s="2" t="n">
-        <v>1.675694444444444</v>
+        <v>1.659375</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -8281,33 +8263,33 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G231" t="n">
-        <v>12.8496</v>
+        <v>10.86</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C232" s="2" t="n">
-        <v>1.6625</v>
+        <v>1.64375</v>
       </c>
       <c r="D232" s="2" t="n">
-        <v>1.677777777777778</v>
+        <v>1.659027777777778</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -8318,7 +8300,7 @@
         <v>400</v>
       </c>
       <c r="G232" t="n">
-        <v>12.8496</v>
+        <v>12.3</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -8329,19 +8311,19 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C233" s="2" t="n">
-        <v>1.663888888888889</v>
+        <v>1.645138888888889</v>
       </c>
       <c r="D233" s="2" t="n">
-        <v>1.680208333333333</v>
+        <v>1.661111111111111</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -8352,11 +8334,11 @@
         <v>401</v>
       </c>
       <c r="G233" t="n">
-        <v>10.86</v>
+        <v>10.8036</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -8372,10 +8354,10 @@
         </is>
       </c>
       <c r="C234" s="2" t="n">
-        <v>1.664583333333333</v>
+        <v>1.648611111111111</v>
       </c>
       <c r="D234" s="2" t="n">
-        <v>1.679861111111111</v>
+        <v>1.663888888888889</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -8390,7 +8372,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
@@ -8406,10 +8388,10 @@
         </is>
       </c>
       <c r="C235" s="2" t="n">
-        <v>1.665972222222222</v>
+        <v>1.65</v>
       </c>
       <c r="D235" s="2" t="n">
-        <v>1.681944444444444</v>
+        <v>1.665277777777778</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -8417,14 +8399,14 @@
         </is>
       </c>
       <c r="F235" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G235" t="n">
-        <v>10.8036</v>
+        <v>12.8496</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -8440,10 +8422,10 @@
         </is>
       </c>
       <c r="C236" s="2" t="n">
-        <v>1.669444444444444</v>
+        <v>1.65</v>
       </c>
       <c r="D236" s="2" t="n">
-        <v>1.684722222222222</v>
+        <v>1.666319444444444</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -8451,14 +8433,14 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G236" t="n">
-        <v>12.3</v>
+        <v>10.86</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
@@ -8474,10 +8456,10 @@
         </is>
       </c>
       <c r="C237" s="2" t="n">
-        <v>1.670833333333333</v>
+        <v>1.652083333333333</v>
       </c>
       <c r="D237" s="2" t="n">
-        <v>1.686111111111111</v>
+        <v>1.668055555555556</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -8485,14 +8467,14 @@
         </is>
       </c>
       <c r="F237" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G237" t="n">
-        <v>12.8496</v>
+        <v>10.8036</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
@@ -8508,10 +8490,10 @@
         </is>
       </c>
       <c r="C238" s="2" t="n">
-        <v>1.670833333333333</v>
+        <v>1.656944444444445</v>
       </c>
       <c r="D238" s="2" t="n">
-        <v>1.687152777777778</v>
+        <v>1.673263888888889</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -8526,26 +8508,26 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C239" s="2" t="n">
-        <v>1.672916666666667</v>
+        <v>1.659027777777778</v>
       </c>
       <c r="D239" s="2" t="n">
-        <v>1.688888888888889</v>
+        <v>1.674305555555556</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -8553,33 +8535,33 @@
         </is>
       </c>
       <c r="F239" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G239" t="n">
-        <v>10.8036</v>
+        <v>12.3</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C240" s="2" t="n">
-        <v>1.677777777777778</v>
+        <v>1.659027777777778</v>
       </c>
       <c r="D240" s="2" t="n">
-        <v>1.694097222222222</v>
+        <v>1.675</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -8590,11 +8572,11 @@
         <v>401</v>
       </c>
       <c r="G240" t="n">
-        <v>10.86</v>
+        <v>10.8036</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
@@ -8610,10 +8592,10 @@
         </is>
       </c>
       <c r="C241" s="2" t="n">
-        <v>1.674305555555556</v>
+        <v>1.659375</v>
       </c>
       <c r="D241" s="2" t="n">
-        <v>1.677083333333333</v>
+        <v>1.662152777777778</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -8626,7 +8608,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
@@ -8642,10 +8624,10 @@
         </is>
       </c>
       <c r="C242" s="2" t="n">
-        <v>1.679861111111111</v>
+        <v>1.660416666666667</v>
       </c>
       <c r="D242" s="2" t="n">
-        <v>1.695833333333333</v>
+        <v>1.675694444444444</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -8653,33 +8635,33 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G242" t="n">
-        <v>10.8036</v>
+        <v>12.8496</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C243" s="2" t="n">
-        <v>1.679861111111111</v>
+        <v>1.6625</v>
       </c>
       <c r="D243" s="2" t="n">
-        <v>1.695138888888889</v>
+        <v>1.677777777777778</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -8690,62 +8672,64 @@
         <v>400</v>
       </c>
       <c r="G243" t="n">
-        <v>12.3</v>
+        <v>12.8496</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C244" s="2" t="n">
+        <v>1.663888888888889</v>
+      </c>
+      <c r="D244" s="2" t="n">
         <v>1.680208333333333</v>
       </c>
-      <c r="D244" s="2" t="n">
-        <v>1.682986111111111</v>
-      </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F244" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>401</v>
+      </c>
       <c r="G244" t="n">
-        <v>1.979999999999999</v>
+        <v>10.86</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C245" s="2" t="n">
-        <v>1.68125</v>
+        <v>1.664583333333333</v>
       </c>
       <c r="D245" s="2" t="n">
-        <v>1.696527777777778</v>
+        <v>1.679861111111111</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -8756,45 +8740,43 @@
         <v>400</v>
       </c>
       <c r="G245" t="n">
-        <v>12.8496</v>
+        <v>12.3</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
           <t>ehvgar</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
       <c r="C246" s="2" t="n">
-        <v>1.680555555555556</v>
+        <v>1.663888888888889</v>
       </c>
       <c r="D246" s="2" t="n">
-        <v>1.683333333333333</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>material trip</t>
         </is>
       </c>
-      <c r="F246" t="n">
-        <v>400</v>
-      </c>
+      <c r="F246" t="inlineStr"/>
       <c r="G246" t="n">
-        <v>1.98</v>
+        <v>1.979999999999999</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
@@ -8810,10 +8792,10 @@
         </is>
       </c>
       <c r="C247" s="2" t="n">
-        <v>1.683333333333333</v>
+        <v>1.665972222222222</v>
       </c>
       <c r="D247" s="2" t="n">
-        <v>1.698611111111111</v>
+        <v>1.681944444444444</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -8821,14 +8803,14 @@
         </is>
       </c>
       <c r="F247" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G247" t="n">
-        <v>12.8496</v>
+        <v>10.8036</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
@@ -8844,44 +8826,44 @@
         </is>
       </c>
       <c r="C248" s="2" t="n">
+        <v>1.669444444444444</v>
+      </c>
+      <c r="D248" s="2" t="n">
         <v>1.684722222222222</v>
       </c>
-      <c r="D248" s="2" t="n">
-        <v>1.701041666666667</v>
-      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>service trip</t>
         </is>
       </c>
       <c r="F248" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G248" t="n">
-        <v>10.86</v>
+        <v>12.3</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C249" s="2" t="n">
-        <v>1.685416666666667</v>
+        <v>1.670833333333333</v>
       </c>
       <c r="D249" s="2" t="n">
-        <v>1.700694444444444</v>
+        <v>1.686111111111111</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -8892,30 +8874,30 @@
         <v>400</v>
       </c>
       <c r="G249" t="n">
-        <v>12.3</v>
+        <v>12.8496</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C250" s="2" t="n">
-        <v>1.686805555555555</v>
+        <v>1.670833333333333</v>
       </c>
       <c r="D250" s="2" t="n">
-        <v>1.702777777777778</v>
+        <v>1.687152777777778</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -8926,11 +8908,11 @@
         <v>401</v>
       </c>
       <c r="G250" t="n">
-        <v>10.8036</v>
+        <v>10.86</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
@@ -8946,10 +8928,10 @@
         </is>
       </c>
       <c r="C251" s="2" t="n">
-        <v>1.677083333333333</v>
+        <v>1.662152777777778</v>
       </c>
       <c r="D251" s="2" t="n">
-        <v>1.690277777777778</v>
+        <v>1.672916666666667</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -8958,18 +8940,18 @@
       </c>
       <c r="F251" t="inlineStr"/>
       <c r="G251" t="n">
-        <v>-142.5</v>
+        <v>-116.25</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -8978,44 +8960,44 @@
         </is>
       </c>
       <c r="C252" s="2" t="n">
-        <v>1.690277777777778</v>
+        <v>1.670138888888889</v>
       </c>
       <c r="D252" s="2" t="n">
-        <v>1.705555555555556</v>
+        <v>1.672916666666667</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>service trip</t>
+          <t>material trip</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G252" t="n">
-        <v>12.3</v>
+        <v>1.98</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C253" s="2" t="n">
-        <v>1.691666666666667</v>
+        <v>1.672916666666667</v>
       </c>
       <c r="D253" s="2" t="n">
-        <v>1.707986111111111</v>
+        <v>1.688888888888889</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -9026,84 +9008,82 @@
         <v>401</v>
       </c>
       <c r="G253" t="n">
-        <v>10.86</v>
+        <v>10.8036</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C254" s="2" t="n">
-        <v>1.691666666666667</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D254" s="2" t="n">
-        <v>1.706944444444444</v>
+        <v>1.677777777777778</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F254" t="n">
-        <v>400</v>
-      </c>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr"/>
       <c r="G254" t="n">
-        <v>12.8496</v>
+        <v>-120</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
+          <t>ehvapt</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
           <t>ehvgar</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>ehvgar</t>
-        </is>
-      </c>
       <c r="C255" s="2" t="n">
-        <v>1.682986111111111</v>
+        <v>1.677777777777778</v>
       </c>
       <c r="D255" s="2" t="n">
-        <v>1.69375</v>
+        <v>1.691666666666667</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>charging</t>
+          <t>material trip</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
       <c r="G255" t="n">
-        <v>-116.25</v>
+        <v>10.8</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -9112,19 +9092,21 @@
         </is>
       </c>
       <c r="C256" s="2" t="n">
-        <v>1.690277777777778</v>
+        <v>1.677777777777778</v>
       </c>
       <c r="D256" s="2" t="n">
-        <v>1.693055555555556</v>
+        <v>1.694097222222222</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F256" t="n">
+        <v>401</v>
+      </c>
       <c r="G256" t="n">
-        <v>1.98</v>
+        <v>10.86</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -9140,36 +9122,34 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C257" s="2" t="n">
-        <v>1.69375</v>
+        <v>1.679861111111111</v>
       </c>
       <c r="D257" s="2" t="n">
-        <v>1.709722222222222</v>
+        <v>1.682638888888889</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F257" t="n">
-        <v>401</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr"/>
       <c r="G257" t="n">
-        <v>10.8036</v>
+        <v>1.979999999999999</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -9178,44 +9158,42 @@
         </is>
       </c>
       <c r="C258" s="2" t="n">
-        <v>1.698611111111111</v>
+        <v>1.672916666666667</v>
       </c>
       <c r="D258" s="2" t="n">
-        <v>1.714930555555556</v>
+        <v>1.675694444444444</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F258" t="n">
-        <v>401</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr"/>
       <c r="G258" t="n">
-        <v>10.86</v>
+        <v>1.98</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C259" s="2" t="n">
-        <v>1.700694444444444</v>
+        <v>1.679861111111111</v>
       </c>
       <c r="D259" s="2" t="n">
-        <v>1.715972222222222</v>
+        <v>1.695833333333333</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -9223,65 +9201,67 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G259" t="n">
-        <v>12.3</v>
+        <v>10.8036</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C260" s="2" t="n">
+        <v>1.679861111111111</v>
+      </c>
+      <c r="D260" s="2" t="n">
         <v>1.695138888888889</v>
       </c>
-      <c r="D260" s="2" t="n">
-        <v>1.697916666666667</v>
-      </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F260" t="n">
+        <v>400</v>
+      </c>
       <c r="G260" t="n">
-        <v>1.979999999999999</v>
+        <v>12.3</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
           <t>ehvgar</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
       <c r="C261" s="2" t="n">
-        <v>1.69375</v>
+        <v>1.680208333333333</v>
       </c>
       <c r="D261" s="2" t="n">
-        <v>1.696527777777778</v>
+        <v>1.682986111111111</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -9290,11 +9270,11 @@
       </c>
       <c r="F261" t="inlineStr"/>
       <c r="G261" t="n">
-        <v>1.98</v>
+        <v>1.979999999999999</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -9310,10 +9290,10 @@
         </is>
       </c>
       <c r="C262" s="2" t="n">
-        <v>1.700694444444444</v>
+        <v>1.68125</v>
       </c>
       <c r="D262" s="2" t="n">
-        <v>1.716666666666667</v>
+        <v>1.696527777777778</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -9321,14 +9301,14 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G262" t="n">
-        <v>10.8036</v>
+        <v>12.8496</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -9344,10 +9324,10 @@
         </is>
       </c>
       <c r="C263" s="2" t="n">
-        <v>1.702083333333333</v>
+        <v>1.683333333333333</v>
       </c>
       <c r="D263" s="2" t="n">
-        <v>1.717361111111111</v>
+        <v>1.698611111111111</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -9362,26 +9342,26 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C264" s="2" t="n">
-        <v>1.704166666666667</v>
+        <v>1.684722222222222</v>
       </c>
       <c r="D264" s="2" t="n">
-        <v>1.719444444444445</v>
+        <v>1.701041666666667</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -9389,48 +9369,48 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G264" t="n">
-        <v>12.8496</v>
+        <v>10.86</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C265" s="2" t="n">
-        <v>1.705555555555556</v>
+        <v>1.671527777777778</v>
       </c>
       <c r="D265" s="2" t="n">
-        <v>1.721875</v>
+        <v>1.685416666666667</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>service trip</t>
+          <t>material trip</t>
         </is>
       </c>
       <c r="F265" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G265" t="n">
-        <v>10.86</v>
+        <v>10.8</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
@@ -9446,10 +9426,10 @@
         </is>
       </c>
       <c r="C266" s="2" t="n">
-        <v>1.70625</v>
+        <v>1.685416666666667</v>
       </c>
       <c r="D266" s="2" t="n">
-        <v>1.721527777777778</v>
+        <v>1.700694444444444</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -9464,73 +9444,73 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C267" s="2" t="n">
-        <v>1.707638888888889</v>
+        <v>1.677777777777778</v>
       </c>
       <c r="D267" s="2" t="n">
-        <v>1.723611111111111</v>
+        <v>1.680555555555556</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F267" t="n">
-        <v>401</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr"/>
       <c r="G267" t="n">
-        <v>10.8036</v>
+        <v>1.98</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C268" s="2" t="n">
-        <v>1.697916666666667</v>
+        <v>1.686805555555555</v>
       </c>
       <c r="D268" s="2" t="n">
-        <v>1.711111111111111</v>
+        <v>1.702777777777778</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>charging</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
+        <v>401</v>
+      </c>
       <c r="G268" t="n">
-        <v>-142.5</v>
+        <v>10.8036</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
@@ -9546,10 +9526,10 @@
         </is>
       </c>
       <c r="C269" s="2" t="n">
-        <v>1.711111111111111</v>
+        <v>1.690277777777778</v>
       </c>
       <c r="D269" s="2" t="n">
-        <v>1.726388888888889</v>
+        <v>1.705555555555556</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -9564,7 +9544,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
@@ -9580,10 +9560,10 @@
         </is>
       </c>
       <c r="C270" s="2" t="n">
-        <v>1.7125</v>
+        <v>1.691666666666667</v>
       </c>
       <c r="D270" s="2" t="n">
-        <v>1.728819444444444</v>
+        <v>1.707986111111111</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -9598,7 +9578,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
@@ -9614,10 +9594,10 @@
         </is>
       </c>
       <c r="C271" s="2" t="n">
-        <v>1.7125</v>
+        <v>1.691666666666667</v>
       </c>
       <c r="D271" s="2" t="n">
-        <v>1.727777777777778</v>
+        <v>1.706944444444444</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -9632,126 +9612,124 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C272" s="2" t="n">
-        <v>1.714583333333333</v>
+        <v>1.682638888888889</v>
       </c>
       <c r="D272" s="2" t="n">
-        <v>1.730555555555556</v>
+        <v>1.69375</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F272" t="n">
-        <v>401</v>
-      </c>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr"/>
       <c r="G272" t="n">
-        <v>10.8036</v>
+        <v>-120</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C273" s="2" t="n">
-        <v>1.719444444444445</v>
+        <v>1.682986111111111</v>
       </c>
       <c r="D273" s="2" t="n">
-        <v>1.735763888888889</v>
+        <v>1.69375</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F273" t="n">
-        <v>401</v>
-      </c>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr"/>
       <c r="G273" t="n">
-        <v>10.86</v>
+        <v>-116.25</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C274" s="2" t="n">
-        <v>1.711111111111111</v>
+        <v>1.69375</v>
       </c>
       <c r="D274" s="2" t="n">
-        <v>1.713888888888889</v>
+        <v>1.709722222222222</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
+        <v>401</v>
+      </c>
       <c r="G274" t="n">
-        <v>1.98</v>
+        <v>10.8036</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C275" s="2" t="n">
-        <v>1.721527777777778</v>
+        <v>1.698611111111111</v>
       </c>
       <c r="D275" s="2" t="n">
-        <v>1.7375</v>
+        <v>1.714930555555556</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -9762,11 +9740,11 @@
         <v>401</v>
       </c>
       <c r="G275" t="n">
-        <v>10.8036</v>
+        <v>10.86</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
@@ -9782,10 +9760,10 @@
         </is>
       </c>
       <c r="C276" s="2" t="n">
-        <v>1.721527777777778</v>
+        <v>1.700694444444444</v>
       </c>
       <c r="D276" s="2" t="n">
-        <v>1.736805555555556</v>
+        <v>1.715972222222222</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -9800,41 +9778,39 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C277" s="2" t="n">
-        <v>1.722916666666667</v>
+        <v>1.69375</v>
       </c>
       <c r="D277" s="2" t="n">
-        <v>1.738194444444444</v>
+        <v>1.696527777777778</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F277" t="n">
-        <v>400</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr"/>
       <c r="G277" t="n">
-        <v>12.8496</v>
+        <v>1.98</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -9850,10 +9826,10 @@
         </is>
       </c>
       <c r="C278" s="2" t="n">
-        <v>1.725</v>
+        <v>1.700694444444444</v>
       </c>
       <c r="D278" s="2" t="n">
-        <v>1.740277777777778</v>
+        <v>1.716666666666667</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -9861,10 +9837,10 @@
         </is>
       </c>
       <c r="F278" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G278" t="n">
-        <v>12.8496</v>
+        <v>10.8036</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -9875,64 +9851,60 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C279" s="2" t="n">
-        <v>1.726388888888889</v>
+        <v>1.691666666666667</v>
       </c>
       <c r="D279" s="2" t="n">
-        <v>1.742708333333333</v>
+        <v>1.702083333333333</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F279" t="n">
-        <v>401</v>
-      </c>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr"/>
       <c r="G279" t="n">
-        <v>10.86</v>
+        <v>-112.5</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C280" s="2" t="n">
-        <v>1.727083333333333</v>
+        <v>1.701041666666667</v>
       </c>
       <c r="D280" s="2" t="n">
-        <v>1.742361111111111</v>
+        <v>1.703819444444445</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F280" t="n">
-        <v>400</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr"/>
       <c r="G280" t="n">
-        <v>12.3</v>
+        <v>1.979999999999999</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -9943,30 +9915,28 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C281" s="2" t="n">
-        <v>1.728472222222222</v>
+        <v>1.69375</v>
       </c>
       <c r="D281" s="2" t="n">
-        <v>1.744444444444444</v>
+        <v>1.696527777777778</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F281" t="n">
-        <v>401</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr"/>
       <c r="G281" t="n">
-        <v>10.8036</v>
+        <v>1.98</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -9977,51 +9947,53 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C282" s="2" t="n">
-        <v>1.727777777777778</v>
+        <v>1.702083333333333</v>
       </c>
       <c r="D282" s="2" t="n">
-        <v>1.741666666666667</v>
+        <v>1.717361111111111</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F282" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>400</v>
+      </c>
       <c r="G282" t="n">
-        <v>10.8</v>
+        <v>12.8496</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C283" s="2" t="n">
-        <v>1.731944444444444</v>
+        <v>1.704166666666667</v>
       </c>
       <c r="D283" s="2" t="n">
-        <v>1.747222222222222</v>
+        <v>1.719444444444445</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -10032,30 +10004,30 @@
         <v>400</v>
       </c>
       <c r="G283" t="n">
-        <v>12.3</v>
+        <v>12.8496</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C284" s="2" t="n">
-        <v>1.733333333333333</v>
+        <v>1.705555555555556</v>
       </c>
       <c r="D284" s="2" t="n">
-        <v>1.748611111111111</v>
+        <v>1.721875</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -10063,67 +10035,67 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G284" t="n">
-        <v>12.8496</v>
+        <v>10.86</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C285" s="2" t="n">
-        <v>1.719444444444445</v>
+        <v>1.70625</v>
       </c>
       <c r="D285" s="2" t="n">
-        <v>1.733333333333333</v>
+        <v>1.721527777777778</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>material trip</t>
+          <t>service trip</t>
         </is>
       </c>
       <c r="F285" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G285" t="n">
-        <v>10.8</v>
+        <v>12.3</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>bus14</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C286" s="2" t="n">
-        <v>1.733333333333333</v>
+        <v>1.707638888888889</v>
       </c>
       <c r="D286" s="2" t="n">
-        <v>1.749652777777778</v>
+        <v>1.723611111111111</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -10134,30 +10106,30 @@
         <v>401</v>
       </c>
       <c r="G286" t="n">
-        <v>10.86</v>
+        <v>10.8036</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>bus14</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C287" s="2" t="n">
-        <v>1.735416666666667</v>
+        <v>1.711111111111111</v>
       </c>
       <c r="D287" s="2" t="n">
-        <v>1.751388888888889</v>
+        <v>1.726388888888889</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -10165,14 +10137,14 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G287" t="n">
-        <v>10.8036</v>
+        <v>12.3</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -10188,10 +10160,10 @@
         </is>
       </c>
       <c r="C288" s="2" t="n">
-        <v>1.740277777777778</v>
+        <v>1.7125</v>
       </c>
       <c r="D288" s="2" t="n">
-        <v>1.756597222222222</v>
+        <v>1.728819444444444</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -10206,7 +10178,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
@@ -10222,10 +10194,10 @@
         </is>
       </c>
       <c r="C289" s="2" t="n">
-        <v>1.742361111111111</v>
+        <v>1.7125</v>
       </c>
       <c r="D289" s="2" t="n">
-        <v>1.758333333333333</v>
+        <v>1.727777777777778</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -10233,67 +10205,65 @@
         </is>
       </c>
       <c r="F289" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G289" t="n">
-        <v>10.8036</v>
+        <v>12.8496</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C290" s="2" t="n">
-        <v>1.742361111111111</v>
+        <v>1.703819444444445</v>
       </c>
       <c r="D290" s="2" t="n">
-        <v>1.757638888888889</v>
+        <v>1.714583333333333</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F290" t="n">
-        <v>400</v>
-      </c>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr"/>
       <c r="G290" t="n">
-        <v>12.3</v>
+        <v>-116.25</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C291" s="2" t="n">
-        <v>1.742708333333333</v>
+        <v>1.702083333333333</v>
       </c>
       <c r="D291" s="2" t="n">
-        <v>1.745486111111111</v>
+        <v>1.704861111111111</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -10302,11 +10272,11 @@
       </c>
       <c r="F291" t="inlineStr"/>
       <c r="G291" t="n">
-        <v>1.979999999999999</v>
+        <v>1.98</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
@@ -10322,10 +10292,10 @@
         </is>
       </c>
       <c r="C292" s="2" t="n">
-        <v>1.74375</v>
+        <v>1.714583333333333</v>
       </c>
       <c r="D292" s="2" t="n">
-        <v>1.759027777777778</v>
+        <v>1.730555555555556</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -10333,33 +10303,33 @@
         </is>
       </c>
       <c r="F292" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G292" t="n">
-        <v>12.8496</v>
+        <v>10.8036</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C293" s="2" t="n">
-        <v>1.745833333333333</v>
+        <v>1.719444444444445</v>
       </c>
       <c r="D293" s="2" t="n">
-        <v>1.761111111111111</v>
+        <v>1.735763888888889</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -10367,33 +10337,33 @@
         </is>
       </c>
       <c r="F293" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G293" t="n">
-        <v>12.8496</v>
+        <v>10.86</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C294" s="2" t="n">
-        <v>1.747222222222222</v>
+        <v>1.721527777777778</v>
       </c>
       <c r="D294" s="2" t="n">
-        <v>1.763541666666667</v>
+        <v>1.7375</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -10404,11 +10374,11 @@
         <v>401</v>
       </c>
       <c r="G294" t="n">
-        <v>10.86</v>
+        <v>10.8036</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
@@ -10424,10 +10394,10 @@
         </is>
       </c>
       <c r="C295" s="2" t="n">
-        <v>1.747916666666667</v>
+        <v>1.721527777777778</v>
       </c>
       <c r="D295" s="2" t="n">
-        <v>1.763194444444444</v>
+        <v>1.736805555555556</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -10454,68 +10424,68 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C296" s="2" t="n">
-        <v>1.749305555555555</v>
+        <v>1.721875</v>
       </c>
       <c r="D296" s="2" t="n">
-        <v>1.765277777777778</v>
+        <v>1.724652777777778</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F296" t="n">
-        <v>401</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr"/>
       <c r="G296" t="n">
-        <v>10.8036</v>
+        <v>1.979999999999999</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C297" s="2" t="n">
-        <v>1.741666666666667</v>
+        <v>1.722916666666667</v>
       </c>
       <c r="D297" s="2" t="n">
-        <v>1.752777777777778</v>
+        <v>1.738194444444444</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>charging</t>
-        </is>
-      </c>
-      <c r="F297" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F297" t="n">
+        <v>400</v>
+      </c>
       <c r="G297" t="n">
-        <v>-120</v>
+        <v>12.8496</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -10524,44 +10494,42 @@
         </is>
       </c>
       <c r="C298" s="2" t="n">
-        <v>1.752777777777778</v>
+        <v>1.714583333333333</v>
       </c>
       <c r="D298" s="2" t="n">
-        <v>1.768055555555556</v>
+        <v>1.717361111111111</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F298" t="n">
-        <v>400</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr"/>
       <c r="G298" t="n">
-        <v>12.3</v>
+        <v>1.98</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C299" s="2" t="n">
-        <v>1.754166666666667</v>
+        <v>1.725</v>
       </c>
       <c r="D299" s="2" t="n">
-        <v>1.770486111111111</v>
+        <v>1.740277777777778</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -10569,33 +10537,33 @@
         </is>
       </c>
       <c r="F299" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G299" t="n">
-        <v>10.86</v>
+        <v>12.8496</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C300" s="2" t="n">
-        <v>1.754861111111111</v>
+        <v>1.726388888888889</v>
       </c>
       <c r="D300" s="2" t="n">
-        <v>1.770138888888889</v>
+        <v>1.742708333333333</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -10603,46 +10571,48 @@
         </is>
       </c>
       <c r="F300" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G300" t="n">
-        <v>12.8496</v>
+        <v>10.86</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C301" s="2" t="n">
-        <v>1.745486111111111</v>
+        <v>1.727083333333333</v>
       </c>
       <c r="D301" s="2" t="n">
-        <v>1.759722222222222</v>
+        <v>1.742361111111111</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>charging</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F301" t="n">
+        <v>400</v>
+      </c>
       <c r="G301" t="n">
-        <v>-153.75</v>
+        <v>12.3</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
@@ -10658,10 +10628,10 @@
         </is>
       </c>
       <c r="C302" s="2" t="n">
-        <v>1.759722222222222</v>
+        <v>1.728472222222222</v>
       </c>
       <c r="D302" s="2" t="n">
-        <v>1.775694444444444</v>
+        <v>1.744444444444444</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -10676,41 +10646,39 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>bus14</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C303" s="2" t="n">
-        <v>1.761111111111111</v>
+        <v>1.715972222222222</v>
       </c>
       <c r="D303" s="2" t="n">
-        <v>1.777430555555556</v>
+        <v>1.73125</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F303" t="n">
-        <v>401</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr"/>
       <c r="G303" t="n">
-        <v>10.86</v>
+        <v>10.32</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -10726,10 +10694,10 @@
         </is>
       </c>
       <c r="C304" s="2" t="n">
-        <v>1.763194444444444</v>
+        <v>1.731944444444444</v>
       </c>
       <c r="D304" s="2" t="n">
-        <v>1.778472222222222</v>
+        <v>1.747222222222222</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -10744,7 +10712,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -10756,59 +10724,63 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C305" s="2" t="n">
-        <v>1.763541666666667</v>
+        <v>1.733333333333333</v>
       </c>
       <c r="D305" s="2" t="n">
-        <v>1.766319444444445</v>
+        <v>1.748611111111111</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F305" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F305" t="n">
+        <v>400</v>
+      </c>
       <c r="G305" t="n">
-        <v>1.979999999999999</v>
+        <v>12.8496</v>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C306" s="2" t="n">
-        <v>1.763194444444444</v>
+        <v>1.733333333333333</v>
       </c>
       <c r="D306" s="2" t="n">
-        <v>1.765972222222222</v>
+        <v>1.749652777777778</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F306" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F306" t="n">
+        <v>401</v>
+      </c>
       <c r="G306" t="n">
-        <v>1.979999999999999</v>
+        <v>10.86</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
@@ -10820,27 +10792,27 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C307" s="2" t="n">
-        <v>1.752777777777778</v>
+        <v>1.724652777777778</v>
       </c>
       <c r="D307" s="2" t="n">
-        <v>1.755555555555556</v>
+        <v>1.735416666666667</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>material trip</t>
+          <t>charging</t>
         </is>
       </c>
       <c r="F307" t="inlineStr"/>
       <c r="G307" t="n">
-        <v>1.98</v>
+        <v>-116.25</v>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
@@ -10856,10 +10828,10 @@
         </is>
       </c>
       <c r="C308" s="2" t="n">
-        <v>1.765277777777778</v>
+        <v>1.735416666666667</v>
       </c>
       <c r="D308" s="2" t="n">
-        <v>1.780555555555555</v>
+        <v>1.751388888888889</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -10867,33 +10839,33 @@
         </is>
       </c>
       <c r="F308" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G308" t="n">
-        <v>12.8496</v>
+        <v>10.8036</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C309" s="2" t="n">
-        <v>1.766666666666667</v>
+        <v>1.740277777777778</v>
       </c>
       <c r="D309" s="2" t="n">
-        <v>1.781944444444445</v>
+        <v>1.756597222222222</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -10901,33 +10873,33 @@
         </is>
       </c>
       <c r="F309" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G309" t="n">
-        <v>12.8496</v>
+        <v>10.86</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C310" s="2" t="n">
-        <v>1.768055555555556</v>
+        <v>1.742361111111111</v>
       </c>
       <c r="D310" s="2" t="n">
-        <v>1.784375</v>
+        <v>1.758333333333333</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -10938,11 +10910,11 @@
         <v>401</v>
       </c>
       <c r="G310" t="n">
-        <v>10.86</v>
+        <v>10.8036</v>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
@@ -10958,10 +10930,10 @@
         </is>
       </c>
       <c r="C311" s="2" t="n">
-        <v>1.76875</v>
+        <v>1.742361111111111</v>
       </c>
       <c r="D311" s="2" t="n">
-        <v>1.784027777777778</v>
+        <v>1.757638888888889</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
@@ -10976,37 +10948,35 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C312" s="2" t="n">
-        <v>1.770138888888889</v>
+        <v>1.735416666666667</v>
       </c>
       <c r="D312" s="2" t="n">
-        <v>1.786111111111111</v>
+        <v>1.738194444444444</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F312" t="n">
-        <v>401</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr"/>
       <c r="G312" t="n">
-        <v>10.8036</v>
+        <v>1.98</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
@@ -11017,7 +10987,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -11026,42 +10996,44 @@
         </is>
       </c>
       <c r="C313" s="2" t="n">
-        <v>1.759722222222222</v>
+        <v>1.74375</v>
       </c>
       <c r="D313" s="2" t="n">
-        <v>1.773611111111111</v>
+        <v>1.759027777777778</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F313" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F313" t="n">
+        <v>400</v>
+      </c>
       <c r="G313" t="n">
-        <v>10.8</v>
+        <v>12.8496</v>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C314" s="2" t="n">
-        <v>1.773611111111111</v>
+        <v>1.745833333333333</v>
       </c>
       <c r="D314" s="2" t="n">
-        <v>1.788888888888889</v>
+        <v>1.761111111111111</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -11072,30 +11044,30 @@
         <v>400</v>
       </c>
       <c r="G314" t="n">
-        <v>12.3</v>
+        <v>12.8496</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C315" s="2" t="n">
-        <v>1.775694444444444</v>
+        <v>1.747222222222222</v>
       </c>
       <c r="D315" s="2" t="n">
-        <v>1.790972222222222</v>
+        <v>1.763541666666667</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -11103,74 +11075,78 @@
         </is>
       </c>
       <c r="F315" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G315" t="n">
-        <v>12.8496</v>
+        <v>10.86</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C316" s="2" t="n">
-        <v>1.766319444444445</v>
+        <v>1.747916666666667</v>
       </c>
       <c r="D316" s="2" t="n">
-        <v>1.778472222222222</v>
+        <v>1.763194444444444</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>charging</t>
-        </is>
-      </c>
-      <c r="F316" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F316" t="n">
+        <v>400</v>
+      </c>
       <c r="G316" t="n">
-        <v>-131.25</v>
+        <v>12.3</v>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C317" s="2" t="n">
-        <v>1.765972222222222</v>
+        <v>1.749305555555555</v>
       </c>
       <c r="D317" s="2" t="n">
-        <v>1.778472222222222</v>
+        <v>1.765277777777778</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>charging</t>
-        </is>
-      </c>
-      <c r="F317" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F317" t="n">
+        <v>401</v>
+      </c>
       <c r="G317" t="n">
-        <v>-135</v>
+        <v>10.8036</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
@@ -11190,10 +11166,10 @@
         </is>
       </c>
       <c r="C318" s="2" t="n">
-        <v>1.778472222222222</v>
+        <v>1.752777777777778</v>
       </c>
       <c r="D318" s="2" t="n">
-        <v>1.794791666666667</v>
+        <v>1.768055555555556</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -11201,33 +11177,33 @@
         </is>
       </c>
       <c r="F318" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G318" t="n">
-        <v>10.86</v>
+        <v>12.3</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C319" s="2" t="n">
-        <v>1.780555555555555</v>
+        <v>1.754166666666667</v>
       </c>
       <c r="D319" s="2" t="n">
-        <v>1.796527777777778</v>
+        <v>1.770486111111111</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -11238,30 +11214,30 @@
         <v>401</v>
       </c>
       <c r="G319" t="n">
-        <v>10.8036</v>
+        <v>10.86</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C320" s="2" t="n">
-        <v>1.784027777777778</v>
+        <v>1.754861111111111</v>
       </c>
       <c r="D320" s="2" t="n">
-        <v>1.799305555555556</v>
+        <v>1.770138888888889</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -11272,11 +11248,11 @@
         <v>400</v>
       </c>
       <c r="G320" t="n">
-        <v>12.3</v>
+        <v>12.8496</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>bus14</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
@@ -11292,10 +11268,10 @@
         </is>
       </c>
       <c r="C321" s="2" t="n">
-        <v>1.784375</v>
+        <v>1.757638888888889</v>
       </c>
       <c r="D321" s="2" t="n">
-        <v>1.787152777777778</v>
+        <v>1.760416666666667</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -11308,7 +11284,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
@@ -11320,46 +11296,48 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C322" s="2" t="n">
-        <v>1.784027777777778</v>
+        <v>1.759722222222222</v>
       </c>
       <c r="D322" s="2" t="n">
-        <v>1.786805555555556</v>
+        <v>1.775694444444444</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F322" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F322" t="n">
+        <v>401</v>
+      </c>
       <c r="G322" t="n">
-        <v>1.979999999999999</v>
+        <v>10.8036</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C323" s="2" t="n">
-        <v>1.786111111111111</v>
+        <v>1.761111111111111</v>
       </c>
       <c r="D323" s="2" t="n">
-        <v>1.801388888888889</v>
+        <v>1.777430555555556</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -11367,14 +11345,14 @@
         </is>
       </c>
       <c r="F323" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G323" t="n">
-        <v>12.8496</v>
+        <v>10.86</v>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
@@ -11390,25 +11368,23 @@
         </is>
       </c>
       <c r="C324" s="2" t="n">
-        <v>1.7875</v>
+        <v>1.747222222222222</v>
       </c>
       <c r="D324" s="2" t="n">
-        <v>1.802777777777778</v>
+        <v>1.7625</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F324" t="n">
-        <v>400</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr"/>
       <c r="G324" t="n">
-        <v>12.8496</v>
+        <v>10.32</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -11424,10 +11400,10 @@
         </is>
       </c>
       <c r="C325" s="2" t="n">
-        <v>1.788888888888889</v>
+        <v>1.763194444444444</v>
       </c>
       <c r="D325" s="2" t="n">
-        <v>1.805208333333333</v>
+        <v>1.778472222222222</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -11435,33 +11411,33 @@
         </is>
       </c>
       <c r="F325" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G325" t="n">
-        <v>10.86</v>
+        <v>12.3</v>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C326" s="2" t="n">
-        <v>1.789583333333333</v>
+        <v>1.765277777777778</v>
       </c>
       <c r="D326" s="2" t="n">
-        <v>1.804861111111111</v>
+        <v>1.780555555555555</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -11472,62 +11448,64 @@
         <v>400</v>
       </c>
       <c r="G326" t="n">
-        <v>12.3</v>
+        <v>12.8496</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C327" s="2" t="n">
-        <v>1.778472222222222</v>
+        <v>1.766666666666667</v>
       </c>
       <c r="D327" s="2" t="n">
-        <v>1.78125</v>
+        <v>1.781944444444445</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F327" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F327" t="n">
+        <v>400</v>
+      </c>
       <c r="G327" t="n">
-        <v>1.98</v>
+        <v>12.8496</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C328" s="2" t="n">
-        <v>1.790972222222222</v>
+        <v>1.768055555555556</v>
       </c>
       <c r="D328" s="2" t="n">
-        <v>1.806944444444444</v>
+        <v>1.784375</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -11538,62 +11516,64 @@
         <v>401</v>
       </c>
       <c r="G328" t="n">
-        <v>10.8036</v>
+        <v>10.86</v>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C329" s="2" t="n">
-        <v>1.778472222222222</v>
+        <v>1.76875</v>
       </c>
       <c r="D329" s="2" t="n">
-        <v>1.792361111111111</v>
+        <v>1.784027777777778</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F329" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F329" t="n">
+        <v>400</v>
+      </c>
       <c r="G329" t="n">
-        <v>10.8</v>
+        <v>12.3</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C330" s="2" t="n">
-        <v>1.794444444444444</v>
+        <v>1.770138888888889</v>
       </c>
       <c r="D330" s="2" t="n">
-        <v>1.809722222222222</v>
+        <v>1.786111111111111</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -11601,112 +11581,114 @@
         </is>
       </c>
       <c r="F330" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G330" t="n">
-        <v>12.3</v>
+        <v>10.8036</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C331" s="2" t="n">
-        <v>1.796527777777778</v>
+        <v>1.760416666666667</v>
       </c>
       <c r="D331" s="2" t="n">
-        <v>1.811805555555555</v>
+        <v>1.773611111111111</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F331" t="n">
-        <v>400</v>
-      </c>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr"/>
       <c r="G331" t="n">
-        <v>12.8496</v>
+        <v>-142.5</v>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C332" s="2" t="n">
-        <v>1.787152777777778</v>
+        <v>1.773611111111111</v>
       </c>
       <c r="D332" s="2" t="n">
-        <v>1.799305555555556</v>
+        <v>1.788888888888889</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>charging</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F332" t="n">
+        <v>400</v>
+      </c>
       <c r="G332" t="n">
-        <v>-131.25</v>
+        <v>12.3</v>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C333" s="2" t="n">
-        <v>1.786805555555556</v>
+        <v>1.775694444444444</v>
       </c>
       <c r="D333" s="2" t="n">
-        <v>1.799305555555556</v>
+        <v>1.790972222222222</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>charging</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F333" t="n">
+        <v>400</v>
+      </c>
       <c r="G333" t="n">
-        <v>-135</v>
+        <v>12.8496</v>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
@@ -11722,10 +11704,10 @@
         </is>
       </c>
       <c r="C334" s="2" t="n">
-        <v>1.799305555555556</v>
+        <v>1.778472222222222</v>
       </c>
       <c r="D334" s="2" t="n">
-        <v>1.815625</v>
+        <v>1.794791666666667</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -11740,7 +11722,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -11756,10 +11738,10 @@
         </is>
       </c>
       <c r="C335" s="2" t="n">
-        <v>1.801388888888889</v>
+        <v>1.780555555555555</v>
       </c>
       <c r="D335" s="2" t="n">
-        <v>1.817361111111111</v>
+        <v>1.796527777777778</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -11774,7 +11756,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
@@ -11790,10 +11772,10 @@
         </is>
       </c>
       <c r="C336" s="2" t="n">
-        <v>1.804861111111111</v>
+        <v>1.784027777777778</v>
       </c>
       <c r="D336" s="2" t="n">
-        <v>1.820138888888889</v>
+        <v>1.799305555555556</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -11808,26 +11790,26 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
           <t>ehvgar</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>ehvbst</t>
-        </is>
-      </c>
       <c r="C337" s="2" t="n">
-        <v>1.799305555555556</v>
+        <v>1.784375</v>
       </c>
       <c r="D337" s="2" t="n">
-        <v>1.802083333333333</v>
+        <v>1.787152777777778</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -11836,11 +11818,11 @@
       </c>
       <c r="F337" t="inlineStr"/>
       <c r="G337" t="n">
-        <v>1.98</v>
+        <v>1.979999999999999</v>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
@@ -11856,10 +11838,10 @@
         </is>
       </c>
       <c r="C338" s="2" t="n">
-        <v>1.806944444444444</v>
+        <v>1.786111111111111</v>
       </c>
       <c r="D338" s="2" t="n">
-        <v>1.822222222222222</v>
+        <v>1.801388888888889</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -11874,14 +11856,14 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -11890,44 +11872,42 @@
         </is>
       </c>
       <c r="C339" s="2" t="n">
-        <v>1.809722222222222</v>
+        <v>1.773611111111111</v>
       </c>
       <c r="D339" s="2" t="n">
-        <v>1.826041666666667</v>
+        <v>1.776388888888889</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F339" t="n">
-        <v>401</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr"/>
       <c r="G339" t="n">
-        <v>10.86</v>
+        <v>1.98</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C340" s="2" t="n">
-        <v>1.810416666666667</v>
+        <v>1.7875</v>
       </c>
       <c r="D340" s="2" t="n">
-        <v>1.825694444444444</v>
+        <v>1.802777777777778</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -11938,18 +11918,18 @@
         <v>400</v>
       </c>
       <c r="G340" t="n">
-        <v>12.3</v>
+        <v>12.8496</v>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -11958,42 +11938,44 @@
         </is>
       </c>
       <c r="C341" s="2" t="n">
-        <v>1.799305555555556</v>
+        <v>1.788888888888889</v>
       </c>
       <c r="D341" s="2" t="n">
-        <v>1.802083333333333</v>
+        <v>1.805208333333333</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F341" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F341" t="n">
+        <v>401</v>
+      </c>
       <c r="G341" t="n">
-        <v>1.98</v>
+        <v>10.86</v>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C342" s="2" t="n">
-        <v>1.811805555555555</v>
+        <v>1.789583333333333</v>
       </c>
       <c r="D342" s="2" t="n">
-        <v>1.827777777777778</v>
+        <v>1.804861111111111</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -12001,14 +11983,14 @@
         </is>
       </c>
       <c r="F342" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G342" t="n">
-        <v>10.8036</v>
+        <v>12.3</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
@@ -12024,89 +12006,91 @@
         </is>
       </c>
       <c r="C343" s="2" t="n">
-        <v>1.799305555555556</v>
+        <v>1.790972222222222</v>
       </c>
       <c r="D343" s="2" t="n">
-        <v>1.814583333333333</v>
+        <v>1.806944444444444</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F343" t="n">
+        <v>401</v>
+      </c>
       <c r="G343" t="n">
-        <v>10.32</v>
+        <v>10.8036</v>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>bus14</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C344" s="2" t="n">
-        <v>1.815277777777778</v>
+        <v>1.778472222222222</v>
       </c>
       <c r="D344" s="2" t="n">
-        <v>1.830555555555556</v>
+        <v>1.79375</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F344" t="n">
-        <v>400</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr"/>
       <c r="G344" t="n">
-        <v>12.3</v>
+        <v>10.32</v>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>bus14</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C345" s="2" t="n">
-        <v>1.815625</v>
+        <v>1.794444444444444</v>
       </c>
       <c r="D345" s="2" t="n">
-        <v>1.818402777777778</v>
+        <v>1.809722222222222</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F345" t="n">
+        <v>400</v>
+      </c>
       <c r="G345" t="n">
-        <v>1.979999999999999</v>
+        <v>12.3</v>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -12122,10 +12106,10 @@
         </is>
       </c>
       <c r="C346" s="2" t="n">
-        <v>1.817361111111111</v>
+        <v>1.796527777777778</v>
       </c>
       <c r="D346" s="2" t="n">
-        <v>1.832638888888889</v>
+        <v>1.811805555555555</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -12140,60 +12124,58 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>bus3</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C347" s="2" t="n">
-        <v>1.820138888888889</v>
+        <v>1.787152777777778</v>
       </c>
       <c r="D347" s="2" t="n">
-        <v>1.836458333333333</v>
+        <v>1.799305555555556</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F347" t="n">
-        <v>401</v>
-      </c>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr"/>
       <c r="G347" t="n">
-        <v>10.86</v>
+        <v>-131.25</v>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C348" s="2" t="n">
-        <v>1.822222222222222</v>
+        <v>1.799305555555556</v>
       </c>
       <c r="D348" s="2" t="n">
-        <v>1.838194444444444</v>
+        <v>1.815625</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -12204,11 +12186,11 @@
         <v>401</v>
       </c>
       <c r="G348" t="n">
-        <v>10.8036</v>
+        <v>10.86</v>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
@@ -12224,57 +12206,57 @@
         </is>
       </c>
       <c r="C349" s="2" t="n">
-        <v>1.825694444444444</v>
+        <v>1.786111111111111</v>
       </c>
       <c r="D349" s="2" t="n">
-        <v>1.840972222222222</v>
+        <v>1.801388888888889</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F349" t="n">
-        <v>400</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr"/>
       <c r="G349" t="n">
-        <v>12.3</v>
+        <v>10.32</v>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C350" s="2" t="n">
-        <v>1.818402777777778</v>
+        <v>1.801388888888889</v>
       </c>
       <c r="D350" s="2" t="n">
-        <v>1.830555555555556</v>
+        <v>1.817361111111111</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>charging</t>
-        </is>
-      </c>
-      <c r="F350" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F350" t="n">
+        <v>401</v>
+      </c>
       <c r="G350" t="n">
-        <v>-131.25</v>
+        <v>10.8036</v>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
@@ -12290,10 +12272,10 @@
         </is>
       </c>
       <c r="C351" s="2" t="n">
-        <v>1.809722222222222</v>
+        <v>1.788888888888889</v>
       </c>
       <c r="D351" s="2" t="n">
-        <v>1.825</v>
+        <v>1.804166666666667</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -12306,7 +12288,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -12322,10 +12304,10 @@
         </is>
       </c>
       <c r="C352" s="2" t="n">
-        <v>1.830555555555556</v>
+        <v>1.804861111111111</v>
       </c>
       <c r="D352" s="2" t="n">
-        <v>1.846875</v>
+        <v>1.820138888888889</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
@@ -12333,14 +12315,14 @@
         </is>
       </c>
       <c r="F352" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G352" t="n">
-        <v>10.86</v>
+        <v>12.3</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -12356,76 +12338,76 @@
         </is>
       </c>
       <c r="C353" s="2" t="n">
-        <v>1.836111111111111</v>
+        <v>1.790972222222222</v>
       </c>
       <c r="D353" s="2" t="n">
-        <v>1.851388888888889</v>
+        <v>1.80625</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F353" t="n">
-        <v>400</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr"/>
       <c r="G353" t="n">
-        <v>12.3</v>
+        <v>10.32</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C354" s="2" t="n">
-        <v>1.817361111111111</v>
+        <v>1.806944444444444</v>
       </c>
       <c r="D354" s="2" t="n">
-        <v>1.83125</v>
+        <v>1.822222222222222</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F354" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F354" t="n">
+        <v>400</v>
+      </c>
       <c r="G354" t="n">
-        <v>10.8</v>
+        <v>12.8496</v>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C355" s="2" t="n">
-        <v>1.838194444444444</v>
+        <v>1.809722222222222</v>
       </c>
       <c r="D355" s="2" t="n">
-        <v>1.854166666666667</v>
+        <v>1.826041666666667</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -12436,77 +12418,77 @@
         <v>401</v>
       </c>
       <c r="G355" t="n">
-        <v>10.8036</v>
+        <v>10.86</v>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C356" s="2" t="n">
-        <v>1.840972222222222</v>
+        <v>1.794791666666667</v>
       </c>
       <c r="D356" s="2" t="n">
-        <v>1.857291666666667</v>
+        <v>1.810069444444444</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F356" t="n">
-        <v>401</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr"/>
       <c r="G356" t="n">
-        <v>10.86</v>
+        <v>10.32</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C357" s="2" t="n">
-        <v>1.83125</v>
+        <v>1.810416666666667</v>
       </c>
       <c r="D357" s="2" t="n">
-        <v>1.848611111111111</v>
+        <v>1.825694444444444</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>charging</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F357" t="n">
+        <v>400</v>
+      </c>
       <c r="G357" t="n">
-        <v>-187.5</v>
+        <v>12.3</v>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -12522,10 +12504,10 @@
         </is>
       </c>
       <c r="C358" s="2" t="n">
-        <v>1.848611111111111</v>
+        <v>1.811805555555555</v>
       </c>
       <c r="D358" s="2" t="n">
-        <v>1.864583333333333</v>
+        <v>1.827777777777778</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -12540,14 +12522,14 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -12556,10 +12538,10 @@
         </is>
       </c>
       <c r="C359" s="2" t="n">
-        <v>1.826041666666667</v>
+        <v>1.799305555555556</v>
       </c>
       <c r="D359" s="2" t="n">
-        <v>1.841319444444444</v>
+        <v>1.813194444444445</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -12568,7 +12550,7 @@
       </c>
       <c r="F359" t="inlineStr"/>
       <c r="G359" t="n">
-        <v>10.32</v>
+        <v>10.8</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
@@ -12588,10 +12570,10 @@
         </is>
       </c>
       <c r="C360" s="2" t="n">
-        <v>1.857638888888889</v>
+        <v>1.815277777777778</v>
       </c>
       <c r="D360" s="2" t="n">
-        <v>1.873958333333333</v>
+        <v>1.830555555555556</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
@@ -12599,10 +12581,10 @@
         </is>
       </c>
       <c r="F360" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G360" t="n">
-        <v>10.86</v>
+        <v>12.3</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
@@ -12622,10 +12604,10 @@
         </is>
       </c>
       <c r="C361" s="2" t="n">
-        <v>1.827777777777778</v>
+        <v>1.801388888888889</v>
       </c>
       <c r="D361" s="2" t="n">
-        <v>1.843055555555555</v>
+        <v>1.816666666666667</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
@@ -12638,7 +12620,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
@@ -12654,10 +12636,10 @@
         </is>
       </c>
       <c r="C362" s="2" t="n">
-        <v>1.859027777777778</v>
+        <v>1.817361111111111</v>
       </c>
       <c r="D362" s="2" t="n">
-        <v>1.875</v>
+        <v>1.832638888888889</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -12665,65 +12647,67 @@
         </is>
       </c>
       <c r="F362" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G362" t="n">
-        <v>10.8036</v>
+        <v>12.8496</v>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus6</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C363" s="2" t="n">
-        <v>1.830555555555556</v>
+        <v>1.820138888888889</v>
       </c>
       <c r="D363" s="2" t="n">
-        <v>1.844444444444445</v>
+        <v>1.836458333333333</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F363" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F363" t="n">
+        <v>401</v>
+      </c>
       <c r="G363" t="n">
-        <v>10.8</v>
+        <v>10.86</v>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus11</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C364" s="2" t="n">
-        <v>1.865277777777778</v>
+        <v>1.822222222222222</v>
       </c>
       <c r="D364" s="2" t="n">
-        <v>1.880555555555556</v>
+        <v>1.838194444444444</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -12731,14 +12715,14 @@
         </is>
       </c>
       <c r="F364" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G364" t="n">
-        <v>12.3</v>
+        <v>10.8036</v>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus15</t>
         </is>
       </c>
     </row>
@@ -12754,10 +12738,10 @@
         </is>
       </c>
       <c r="C365" s="2" t="n">
-        <v>1.830555555555556</v>
+        <v>1.805208333333333</v>
       </c>
       <c r="D365" s="2" t="n">
-        <v>1.845833333333333</v>
+        <v>1.820486111111111</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -12770,7 +12754,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>bus14</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
@@ -12786,10 +12770,10 @@
         </is>
       </c>
       <c r="C366" s="2" t="n">
-        <v>1.878472222222222</v>
+        <v>1.825694444444444</v>
       </c>
       <c r="D366" s="2" t="n">
-        <v>1.894791666666667</v>
+        <v>1.840972222222222</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -12797,65 +12781,67 @@
         </is>
       </c>
       <c r="F366" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G366" t="n">
-        <v>10.86</v>
+        <v>12.3</v>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>bus14</t>
+          <t>bus2</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C367" s="2" t="n">
-        <v>1.873958333333333</v>
+        <v>1.830555555555556</v>
       </c>
       <c r="D367" s="2" t="n">
-        <v>1.876736111111111</v>
+        <v>1.846875</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F367" t="n">
+        <v>401</v>
+      </c>
       <c r="G367" t="n">
-        <v>1.979999999999999</v>
+        <v>10.86</v>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus13</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C368" s="2" t="n">
-        <v>1.832638888888889</v>
+        <v>1.809722222222222</v>
       </c>
       <c r="D368" s="2" t="n">
-        <v>1.847916666666667</v>
+        <v>1.825</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -12875,19 +12861,19 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C369" s="2" t="n">
-        <v>1.879861111111111</v>
+        <v>1.836111111111111</v>
       </c>
       <c r="D369" s="2" t="n">
-        <v>1.895833333333333</v>
+        <v>1.851388888888889</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -12895,10 +12881,10 @@
         </is>
       </c>
       <c r="F369" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G369" t="n">
-        <v>10.8036</v>
+        <v>12.3</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
@@ -12909,32 +12895,32 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C370" s="2" t="n">
-        <v>1.876736111111111</v>
+        <v>1.811805555555555</v>
       </c>
       <c r="D370" s="2" t="n">
-        <v>1.899305555555556</v>
+        <v>1.827083333333333</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>charging</t>
+          <t>material trip</t>
         </is>
       </c>
       <c r="F370" t="inlineStr"/>
       <c r="G370" t="n">
-        <v>-202.7355200000001</v>
+        <v>10.32</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>bus12</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
@@ -12950,57 +12936,57 @@
         </is>
       </c>
       <c r="C371" s="2" t="n">
-        <v>1.836458333333333</v>
+        <v>1.838194444444444</v>
       </c>
       <c r="D371" s="2" t="n">
-        <v>1.851736111111111</v>
+        <v>1.854166666666667</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F371" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F371" t="n">
+        <v>401</v>
+      </c>
       <c r="G371" t="n">
-        <v>10.32</v>
+        <v>10.8036</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus7</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C372" s="2" t="n">
-        <v>1.899305555555556</v>
+        <v>1.815625</v>
       </c>
       <c r="D372" s="2" t="n">
-        <v>1.915625</v>
+        <v>1.830902777777778</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F372" t="n">
-        <v>401</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr"/>
       <c r="G372" t="n">
-        <v>10.86</v>
+        <v>10.32</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>bus1</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
@@ -13016,76 +13002,76 @@
         </is>
       </c>
       <c r="C373" s="2" t="n">
-        <v>1.838194444444444</v>
+        <v>1.840972222222222</v>
       </c>
       <c r="D373" s="2" t="n">
-        <v>1.853472222222222</v>
+        <v>1.857291666666667</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>material trip</t>
-        </is>
-      </c>
-      <c r="F373" t="inlineStr"/>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F373" t="n">
+        <v>401</v>
+      </c>
       <c r="G373" t="n">
-        <v>10.32</v>
+        <v>10.86</v>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus4</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C374" s="2" t="n">
-        <v>1.900694444444444</v>
+        <v>1.827777777777778</v>
       </c>
       <c r="D374" s="2" t="n">
-        <v>1.916666666666667</v>
+        <v>1.841666666666667</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F374" t="n">
-        <v>401</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr"/>
       <c r="G374" t="n">
-        <v>10.8036</v>
+        <v>10.8</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>bus6</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C375" s="2" t="n">
-        <v>1.840972222222222</v>
+        <v>1.817361111111111</v>
       </c>
       <c r="D375" s="2" t="n">
-        <v>1.85625</v>
+        <v>1.832638888888889</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -13098,26 +13084,26 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C376" s="2" t="n">
-        <v>1.920138888888889</v>
+        <v>1.848611111111111</v>
       </c>
       <c r="D376" s="2" t="n">
-        <v>1.936458333333333</v>
+        <v>1.864583333333333</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -13128,52 +13114,50 @@
         <v>401</v>
       </c>
       <c r="G376" t="n">
-        <v>10.86</v>
+        <v>10.8036</v>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>bus8</t>
+          <t>bus10</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C377" s="2" t="n">
-        <v>1.921527777777778</v>
+        <v>1.841666666666667</v>
       </c>
       <c r="D377" s="2" t="n">
-        <v>1.9375</v>
+        <v>1.857638888888889</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F377" t="n">
-        <v>401</v>
-      </c>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr"/>
       <c r="G377" t="n">
-        <v>10.8036</v>
+        <v>-172.5</v>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>bus9</t>
+          <t>bus1</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>ehvgar</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -13182,10 +13166,10 @@
         </is>
       </c>
       <c r="C378" s="2" t="n">
-        <v>1.848611111111111</v>
+        <v>1.820138888888889</v>
       </c>
       <c r="D378" s="2" t="n">
-        <v>1.8625</v>
+        <v>1.835416666666667</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -13194,11 +13178,11 @@
       </c>
       <c r="F378" t="inlineStr"/>
       <c r="G378" t="n">
-        <v>10.8</v>
+        <v>10.32</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -13214,10 +13198,10 @@
         </is>
       </c>
       <c r="C379" s="2" t="n">
-        <v>1.940972222222222</v>
+        <v>1.857638888888889</v>
       </c>
       <c r="D379" s="2" t="n">
-        <v>1.957291666666667</v>
+        <v>1.873958333333333</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -13232,7 +13216,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>bus11</t>
+          <t>bus8</t>
         </is>
       </c>
     </row>
@@ -13244,29 +13228,27 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C380" s="2" t="n">
-        <v>1.942361111111111</v>
+        <v>1.851388888888889</v>
       </c>
       <c r="D380" s="2" t="n">
-        <v>1.958333333333333</v>
+        <v>1.854166666666667</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F380" t="n">
-        <v>401</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr"/>
       <c r="G380" t="n">
-        <v>10.8036</v>
+        <v>1.979999999999999</v>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>bus5</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
@@ -13282,25 +13264,23 @@
         </is>
       </c>
       <c r="C381" s="2" t="n">
-        <v>1.961805555555556</v>
+        <v>1.822222222222222</v>
       </c>
       <c r="D381" s="2" t="n">
-        <v>1.978125</v>
+        <v>1.8375</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F381" t="n">
-        <v>401</v>
-      </c>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr"/>
       <c r="G381" t="n">
-        <v>10.86</v>
+        <v>10.32</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>bus13</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
@@ -13316,10 +13296,10 @@
         </is>
       </c>
       <c r="C382" s="2" t="n">
-        <v>1.963194444444444</v>
+        <v>1.859027777777778</v>
       </c>
       <c r="D382" s="2" t="n">
-        <v>1.979166666666667</v>
+        <v>1.875</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
@@ -13334,60 +13314,58 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>bus4</t>
+          <t>bus14</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvgar</t>
         </is>
       </c>
       <c r="C383" s="2" t="n">
-        <v>1.982638888888889</v>
+        <v>1.854166666666667</v>
       </c>
       <c r="D383" s="2" t="n">
-        <v>1.998958333333333</v>
+        <v>1.865277777777778</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>service trip</t>
-        </is>
-      </c>
-      <c r="F383" t="n">
-        <v>401</v>
-      </c>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr"/>
       <c r="G383" t="n">
-        <v>10.86</v>
+        <v>-120</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>bus2</t>
+          <t>bus3</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="C384" s="2" t="n">
-        <v>1.875</v>
+        <v>1.825694444444444</v>
       </c>
       <c r="D384" s="2" t="n">
-        <v>1.890277777777778</v>
+        <v>1.840972222222222</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
@@ -13400,26 +13378,26 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>ehvbst</t>
+          <t>ehvapt</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>ehvapt</t>
+          <t>ehvbst</t>
         </is>
       </c>
       <c r="C385" s="2" t="n">
-        <v>1.984027777777778</v>
+        <v>1.865277777777778</v>
       </c>
       <c r="D385" s="2" t="n">
-        <v>2</v>
+        <v>1.880555555555556</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -13427,14 +13405,14 @@
         </is>
       </c>
       <c r="F385" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G385" t="n">
-        <v>10.8036</v>
+        <v>12.3</v>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>bus10</t>
+          <t>bus9</t>
         </is>
       </c>
     </row>
@@ -13450,10 +13428,10 @@
         </is>
       </c>
       <c r="C386" s="2" t="n">
-        <v>1.880555555555556</v>
+        <v>1.826041666666667</v>
       </c>
       <c r="D386" s="2" t="n">
-        <v>1.895833333333333</v>
+        <v>1.841319444444444</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -13466,7 +13444,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
@@ -13482,10 +13460,10 @@
         </is>
       </c>
       <c r="C387" s="2" t="n">
-        <v>2.000694444444445</v>
+        <v>1.878472222222222</v>
       </c>
       <c r="D387" s="2" t="n">
-        <v>2.017013888888889</v>
+        <v>1.894791666666667</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
@@ -13500,7 +13478,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>bus7</t>
+          <t>bus5</t>
         </is>
       </c>
     </row>
@@ -13516,10 +13494,10 @@
         </is>
       </c>
       <c r="C388" s="2" t="n">
-        <v>2.00625</v>
+        <v>1.879861111111111</v>
       </c>
       <c r="D388" s="2" t="n">
-        <v>2.022222222222222</v>
+        <v>1.895833333333333</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
@@ -13534,7 +13512,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>bus14</t>
+          <t>bus12</t>
         </is>
       </c>
     </row>
@@ -13550,10 +13528,10 @@
         </is>
       </c>
       <c r="C389" s="2" t="n">
-        <v>2.021527777777778</v>
+        <v>1.899305555555556</v>
       </c>
       <c r="D389" s="2" t="n">
-        <v>2.037847222222222</v>
+        <v>1.915625</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -13568,7 +13546,735 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
+          <t>bus6</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>ehvapt</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="n">
+        <v>1.900694444444444</v>
+      </c>
+      <c r="D390" s="2" t="n">
+        <v>1.916666666666667</v>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F390" t="n">
+        <v>401</v>
+      </c>
+      <c r="G390" t="n">
+        <v>10.8036</v>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>bus11</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>ehvapt</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="n">
+        <v>1.920138888888889</v>
+      </c>
+      <c r="D391" s="2" t="n">
+        <v>1.936458333333333</v>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F391" t="n">
+        <v>401</v>
+      </c>
+      <c r="G391" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>bus15</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>ehvapt</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="n">
+        <v>1.921527777777778</v>
+      </c>
+      <c r="D392" s="2" t="n">
+        <v>1.9375</v>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F392" t="n">
+        <v>401</v>
+      </c>
+      <c r="G392" t="n">
+        <v>10.8036</v>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>bus2</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>ehvapt</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="n">
+        <v>1.846875</v>
+      </c>
+      <c r="D393" s="2" t="n">
+        <v>1.862152777777778</v>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>bus13</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>ehvapt</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="n">
+        <v>1.940972222222222</v>
+      </c>
+      <c r="D394" s="2" t="n">
+        <v>1.957291666666667</v>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F394" t="n">
+        <v>401</v>
+      </c>
+      <c r="G394" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>bus13</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>ehvapt</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="n">
+        <v>1.854166666666667</v>
+      </c>
+      <c r="D395" s="2" t="n">
+        <v>1.869444444444444</v>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>bus7</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>ehvapt</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="n">
+        <v>1.942361111111111</v>
+      </c>
+      <c r="D396" s="2" t="n">
+        <v>1.958333333333333</v>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F396" t="n">
+        <v>401</v>
+      </c>
+      <c r="G396" t="n">
+        <v>10.8036</v>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>bus7</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>ehvapt</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="n">
+        <v>1.857291666666667</v>
+      </c>
+      <c r="D397" s="2" t="n">
+        <v>1.872569444444444</v>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>bus4</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>ehvapt</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="n">
+        <v>1.961805555555556</v>
+      </c>
+      <c r="D398" s="2" t="n">
+        <v>1.978125</v>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F398" t="n">
+        <v>401</v>
+      </c>
+      <c r="G398" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>bus4</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>ehvapt</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="n">
+        <v>1.9375</v>
+      </c>
+      <c r="D399" s="2" t="n">
+        <v>1.951388888888889</v>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>bus2</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="n">
+        <v>1.857638888888889</v>
+      </c>
+      <c r="D400" s="2" t="n">
+        <v>1.860416666666667</v>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>bus1</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>ehvapt</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="n">
+        <v>1.963194444444444</v>
+      </c>
+      <c r="D401" s="2" t="n">
+        <v>1.979166666666667</v>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F401" t="n">
+        <v>401</v>
+      </c>
+      <c r="G401" t="n">
+        <v>10.8036</v>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>bus1</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="n">
+        <v>1.951388888888889</v>
+      </c>
+      <c r="D402" s="2" t="n">
+        <v>1.982638888888889</v>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>charging</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="n">
+        <v>-209.40528</v>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>bus2</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>ehvapt</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="n">
+        <v>1.982638888888889</v>
+      </c>
+      <c r="D403" s="2" t="n">
+        <v>1.998958333333333</v>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F403" t="n">
+        <v>401</v>
+      </c>
+      <c r="G403" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>bus10</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>ehvgar</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="n">
+        <v>1.865277777777778</v>
+      </c>
+      <c r="D404" s="2" t="n">
+        <v>1.868055555555556</v>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
           <t>bus3</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>ehvapt</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="n">
+        <v>1.984027777777778</v>
+      </c>
+      <c r="D405" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F405" t="n">
+        <v>401</v>
+      </c>
+      <c r="G405" t="n">
+        <v>10.8036</v>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>bus3</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>ehvapt</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="n">
+        <v>1.873958333333333</v>
+      </c>
+      <c r="D406" s="2" t="n">
+        <v>1.889236111111111</v>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>bus8</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>ehvapt</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="n">
+        <v>2.000694444444445</v>
+      </c>
+      <c r="D407" s="2" t="n">
+        <v>2.017013888888889</v>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F407" t="n">
+        <v>401</v>
+      </c>
+      <c r="G407" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>bus8</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>ehvapt</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="D408" s="2" t="n">
+        <v>1.890277777777778</v>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>bus14</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>ehvapt</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="n">
+        <v>2.00625</v>
+      </c>
+      <c r="D409" s="2" t="n">
+        <v>2.022222222222222</v>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F409" t="n">
+        <v>401</v>
+      </c>
+      <c r="G409" t="n">
+        <v>10.8036</v>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>bus14</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>ehvapt</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="n">
+        <v>1.880555555555556</v>
+      </c>
+      <c r="D410" s="2" t="n">
+        <v>1.895833333333333</v>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>material trip</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>bus9</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>ehvapt</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>ehvbst</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="n">
+        <v>2.021527777777778</v>
+      </c>
+      <c r="D411" s="2" t="n">
+        <v>2.037847222222222</v>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>service trip</t>
+        </is>
+      </c>
+      <c r="F411" t="n">
+        <v>401</v>
+      </c>
+      <c r="G411" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>bus9</t>
         </is>
       </c>
     </row>

--- a/AA_improved_bus_planning.xlsx
+++ b/AA_improved_bus_planning.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I731"/>
+  <dimension ref="A1:H731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,11 +466,6 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>total battery bus</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
           <t>bus</t>
         </is>
       </c>
@@ -508,9 +503,6 @@
         <v>1.98</v>
       </c>
       <c r="H2" t="n">
-        <v>253.02</v>
-      </c>
-      <c r="I2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -547,9 +539,6 @@
         <v>10.8036</v>
       </c>
       <c r="H3" t="n">
-        <v>242.2164</v>
-      </c>
-      <c r="I3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -584,9 +573,6 @@
         <v>2.833333333333333</v>
       </c>
       <c r="H4" t="n">
-        <v>239.3830666666667</v>
-      </c>
-      <c r="I4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -623,9 +609,6 @@
         <v>10.86</v>
       </c>
       <c r="H5" t="n">
-        <v>228.5230666666667</v>
-      </c>
-      <c r="I5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -660,9 +643,6 @@
         <v>1.541666666666667</v>
       </c>
       <c r="H6" t="n">
-        <v>226.9814</v>
-      </c>
-      <c r="I6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -699,9 +679,6 @@
         <v>10.8036</v>
       </c>
       <c r="H7" t="n">
-        <v>216.1778</v>
-      </c>
-      <c r="I7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -736,9 +713,6 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="H8" t="n">
-        <v>216.0111333333334</v>
-      </c>
-      <c r="I8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -775,9 +749,6 @@
         <v>10.86</v>
       </c>
       <c r="H9" t="n">
-        <v>205.1511333333333</v>
-      </c>
-      <c r="I9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -812,9 +783,6 @@
         <v>0.125</v>
       </c>
       <c r="H10" t="n">
-        <v>205.0261333333333</v>
-      </c>
-      <c r="I10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -851,9 +819,6 @@
         <v>12.8496</v>
       </c>
       <c r="H11" t="n">
-        <v>192.1765333333333</v>
-      </c>
-      <c r="I11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -888,9 +853,6 @@
         <v>0.5</v>
       </c>
       <c r="H12" t="n">
-        <v>191.6765333333333</v>
-      </c>
-      <c r="I12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -927,9 +889,6 @@
         <v>12.3</v>
       </c>
       <c r="H13" t="n">
-        <v>179.3765333333333</v>
-      </c>
-      <c r="I13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -964,9 +923,6 @@
         <v>0.25</v>
       </c>
       <c r="H14" t="n">
-        <v>179.1265333333333</v>
-      </c>
-      <c r="I14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1003,9 +959,6 @@
         <v>10.8036</v>
       </c>
       <c r="H15" t="n">
-        <v>168.3229333333333</v>
-      </c>
-      <c r="I15" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1040,9 +993,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H16" t="n">
-        <v>167.9062666666667</v>
-      </c>
-      <c r="I16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1079,9 +1029,6 @@
         <v>12.3</v>
       </c>
       <c r="H17" t="n">
-        <v>155.6062666666667</v>
-      </c>
-      <c r="I17" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1116,9 +1063,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H18" t="n">
-        <v>155.1896</v>
-      </c>
-      <c r="I18" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1155,9 +1099,6 @@
         <v>12.8496</v>
       </c>
       <c r="H19" t="n">
-        <v>142.34</v>
-      </c>
-      <c r="I19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1192,9 +1133,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>141.5066666666667</v>
-      </c>
-      <c r="I20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1231,9 +1169,6 @@
         <v>10.86</v>
       </c>
       <c r="H21" t="n">
-        <v>130.6466666666666</v>
-      </c>
-      <c r="I21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1268,9 +1203,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H22" t="n">
-        <v>129.855</v>
-      </c>
-      <c r="I22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1307,9 +1239,6 @@
         <v>10.8036</v>
       </c>
       <c r="H23" t="n">
-        <v>119.0514</v>
-      </c>
-      <c r="I23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1344,9 +1273,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H24" t="n">
-        <v>118.6347333333333</v>
-      </c>
-      <c r="I24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1383,9 +1309,6 @@
         <v>12.3</v>
       </c>
       <c r="H25" t="n">
-        <v>106.3347333333333</v>
-      </c>
-      <c r="I25" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1420,9 +1343,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H26" t="n">
-        <v>105.9180666666666</v>
-      </c>
-      <c r="I26" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1459,9 +1379,6 @@
         <v>12.8496</v>
       </c>
       <c r="H27" t="n">
-        <v>93.06846666666665</v>
-      </c>
-      <c r="I27" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1496,9 +1413,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H28" t="n">
-        <v>92.23513333333332</v>
-      </c>
-      <c r="I28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1535,9 +1449,6 @@
         <v>10.86</v>
       </c>
       <c r="H29" t="n">
-        <v>81.37513333333332</v>
-      </c>
-      <c r="I29" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1572,9 +1483,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H30" t="n">
-        <v>80.58346666666665</v>
-      </c>
-      <c r="I30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1611,9 +1519,6 @@
         <v>10.8036</v>
       </c>
       <c r="H31" t="n">
-        <v>69.77986666666665</v>
-      </c>
-      <c r="I31" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1648,9 +1553,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H32" t="n">
-        <v>69.36319999999998</v>
-      </c>
-      <c r="I32" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1687,9 +1589,6 @@
         <v>12.3</v>
       </c>
       <c r="H33" t="n">
-        <v>57.06319999999998</v>
-      </c>
-      <c r="I33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1724,9 +1623,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H34" t="n">
-        <v>56.64653333333332</v>
-      </c>
-      <c r="I34" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1763,9 +1659,6 @@
         <v>12.8496</v>
       </c>
       <c r="H35" t="n">
-        <v>43.79693333333331</v>
-      </c>
-      <c r="I35" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1800,9 +1693,6 @@
         <v>0.25</v>
       </c>
       <c r="H36" t="n">
-        <v>43.54693333333331</v>
-      </c>
-      <c r="I36" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1839,9 +1729,6 @@
         <v>12.3</v>
       </c>
       <c r="H37" t="n">
-        <v>31.24693333333332</v>
-      </c>
-      <c r="I37" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1876,9 +1763,6 @@
         <v>1.979999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>29.26693333333332</v>
-      </c>
-      <c r="I38" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1913,9 +1797,6 @@
         <v>-142.5</v>
       </c>
       <c r="H39" t="n">
-        <v>171.7669333333333</v>
-      </c>
-      <c r="I39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1950,9 +1831,6 @@
         <v>1.98</v>
       </c>
       <c r="H40" t="n">
-        <v>169.7869333333333</v>
-      </c>
-      <c r="I40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1987,9 +1865,6 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H41" t="n">
-        <v>168.8702666666667</v>
-      </c>
-      <c r="I41" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2026,9 +1901,6 @@
         <v>10.8036</v>
       </c>
       <c r="H42" t="n">
-        <v>158.0666666666667</v>
-      </c>
-      <c r="I42" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2063,9 +1935,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H43" t="n">
-        <v>157.7333333333333</v>
-      </c>
-      <c r="I43" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2102,9 +1971,6 @@
         <v>10.86</v>
       </c>
       <c r="H44" t="n">
-        <v>146.8733333333333</v>
-      </c>
-      <c r="I44" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2139,9 +2005,6 @@
         <v>0.9583333333333334</v>
       </c>
       <c r="H45" t="n">
-        <v>145.915</v>
-      </c>
-      <c r="I45" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2178,9 +2041,6 @@
         <v>12.8496</v>
       </c>
       <c r="H46" t="n">
-        <v>133.0654</v>
-      </c>
-      <c r="I46" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2215,9 +2075,6 @@
         <v>0.5</v>
       </c>
       <c r="H47" t="n">
-        <v>132.5654</v>
-      </c>
-      <c r="I47" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2254,9 +2111,6 @@
         <v>12.3</v>
       </c>
       <c r="H48" t="n">
-        <v>120.2654</v>
-      </c>
-      <c r="I48" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2291,9 +2145,6 @@
         <v>1.083333333333333</v>
       </c>
       <c r="H49" t="n">
-        <v>119.1820666666667</v>
-      </c>
-      <c r="I49" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2330,9 +2181,6 @@
         <v>12.8496</v>
       </c>
       <c r="H50" t="n">
-        <v>106.3324666666667</v>
-      </c>
-      <c r="I50" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2367,9 +2215,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H51" t="n">
-        <v>105.4991333333333</v>
-      </c>
-      <c r="I51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2406,9 +2251,6 @@
         <v>10.86</v>
       </c>
       <c r="H52" t="n">
-        <v>94.63913333333333</v>
-      </c>
-      <c r="I52" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2443,9 +2285,6 @@
         <v>2.041666666666667</v>
       </c>
       <c r="H53" t="n">
-        <v>92.59746666666666</v>
-      </c>
-      <c r="I53" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2482,9 +2321,6 @@
         <v>10.8036</v>
       </c>
       <c r="H54" t="n">
-        <v>81.79386666666666</v>
-      </c>
-      <c r="I54" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2519,9 +2355,6 @@
         <v>1.583333333333333</v>
       </c>
       <c r="H55" t="n">
-        <v>80.21053333333333</v>
-      </c>
-      <c r="I55" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2558,9 +2391,6 @@
         <v>10.86</v>
       </c>
       <c r="H56" t="n">
-        <v>69.35053333333333</v>
-      </c>
-      <c r="I56" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2595,9 +2425,6 @@
         <v>10.32</v>
       </c>
       <c r="H57" t="n">
-        <v>59.03053333333333</v>
-      </c>
-      <c r="I57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2632,9 +2459,6 @@
         <v>0.625</v>
       </c>
       <c r="H58" t="n">
-        <v>58.40553333333333</v>
-      </c>
-      <c r="I58" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2671,9 +2495,6 @@
         <v>12.3</v>
       </c>
       <c r="H59" t="n">
-        <v>46.10553333333333</v>
-      </c>
-      <c r="I59" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2708,9 +2529,6 @@
         <v>1.979999999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>44.12553333333334</v>
-      </c>
-      <c r="I60" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2745,9 +2563,6 @@
         <v>-150</v>
       </c>
       <c r="H61" t="n">
-        <v>194.1255333333334</v>
-      </c>
-      <c r="I61" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2782,9 +2597,6 @@
         <v>10.8</v>
       </c>
       <c r="H62" t="n">
-        <v>183.3255333333333</v>
-      </c>
-      <c r="I62" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2819,9 +2631,6 @@
         <v>13.33333333333333</v>
       </c>
       <c r="H63" t="n">
-        <v>169.9922</v>
-      </c>
-      <c r="I63" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2858,9 +2667,6 @@
         <v>10.86</v>
       </c>
       <c r="H64" t="n">
-        <v>159.1322</v>
-      </c>
-      <c r="I64" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2897,9 +2703,6 @@
         <v>1.98</v>
       </c>
       <c r="H65" t="n">
-        <v>253.02</v>
-      </c>
-      <c r="I65" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2936,9 +2739,6 @@
         <v>10.8036</v>
       </c>
       <c r="H66" t="n">
-        <v>242.2164</v>
-      </c>
-      <c r="I66" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2973,9 +2773,6 @@
         <v>10.32</v>
       </c>
       <c r="H67" t="n">
-        <v>231.8964</v>
-      </c>
-      <c r="I67" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3010,9 +2807,6 @@
         <v>0.75</v>
       </c>
       <c r="H68" t="n">
-        <v>231.1464</v>
-      </c>
-      <c r="I68" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3049,9 +2843,6 @@
         <v>10.8036</v>
       </c>
       <c r="H69" t="n">
-        <v>220.3428</v>
-      </c>
-      <c r="I69" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3086,9 +2877,6 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="H70" t="n">
-        <v>220.1761333333334</v>
-      </c>
-      <c r="I70" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3125,9 +2913,6 @@
         <v>10.86</v>
       </c>
       <c r="H71" t="n">
-        <v>209.3161333333334</v>
-      </c>
-      <c r="I71" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3162,9 +2947,6 @@
         <v>0.125</v>
       </c>
       <c r="H72" t="n">
-        <v>209.1911333333334</v>
-      </c>
-      <c r="I72" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3201,9 +2983,6 @@
         <v>12.8496</v>
       </c>
       <c r="H73" t="n">
-        <v>196.3415333333334</v>
-      </c>
-      <c r="I73" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3238,9 +3017,6 @@
         <v>0.5</v>
       </c>
       <c r="H74" t="n">
-        <v>195.8415333333334</v>
-      </c>
-      <c r="I74" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3277,9 +3053,6 @@
         <v>12.3</v>
       </c>
       <c r="H75" t="n">
-        <v>183.5415333333333</v>
-      </c>
-      <c r="I75" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3314,9 +3087,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H76" t="n">
-        <v>182.7082</v>
-      </c>
-      <c r="I76" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3353,9 +3123,6 @@
         <v>12.8496</v>
       </c>
       <c r="H77" t="n">
-        <v>169.8586</v>
-      </c>
-      <c r="I77" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3390,9 +3157,6 @@
         <v>0.5</v>
       </c>
       <c r="H78" t="n">
-        <v>169.3586</v>
-      </c>
-      <c r="I78" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3429,9 +3193,6 @@
         <v>12.3</v>
       </c>
       <c r="H79" t="n">
-        <v>157.0586</v>
-      </c>
-      <c r="I79" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3466,9 +3227,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H80" t="n">
-        <v>156.2252666666667</v>
-      </c>
-      <c r="I80" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3505,9 +3263,6 @@
         <v>12.8496</v>
       </c>
       <c r="H81" t="n">
-        <v>143.3756666666667</v>
-      </c>
-      <c r="I81" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3542,9 +3297,6 @@
         <v>0.5</v>
       </c>
       <c r="H82" t="n">
-        <v>142.8756666666667</v>
-      </c>
-      <c r="I82" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3581,9 +3333,6 @@
         <v>12.3</v>
       </c>
       <c r="H83" t="n">
-        <v>130.5756666666667</v>
-      </c>
-      <c r="I83" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3618,9 +3367,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H84" t="n">
-        <v>129.7423333333333</v>
-      </c>
-      <c r="I84" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3657,9 +3403,6 @@
         <v>12.8496</v>
       </c>
       <c r="H85" t="n">
-        <v>116.8927333333333</v>
-      </c>
-      <c r="I85" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3694,9 +3437,6 @@
         <v>0.5</v>
       </c>
       <c r="H86" t="n">
-        <v>116.3927333333333</v>
-      </c>
-      <c r="I86" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3733,9 +3473,6 @@
         <v>12.3</v>
       </c>
       <c r="H87" t="n">
-        <v>104.0927333333333</v>
-      </c>
-      <c r="I87" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3770,9 +3507,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H88" t="n">
-        <v>103.2594</v>
-      </c>
-      <c r="I88" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3809,9 +3543,6 @@
         <v>12.8496</v>
       </c>
       <c r="H89" t="n">
-        <v>90.40980000000002</v>
-      </c>
-      <c r="I89" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3846,9 +3577,6 @@
         <v>0.5</v>
       </c>
       <c r="H90" t="n">
-        <v>89.90980000000002</v>
-      </c>
-      <c r="I90" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3885,9 +3613,6 @@
         <v>12.3</v>
       </c>
       <c r="H91" t="n">
-        <v>77.60980000000002</v>
-      </c>
-      <c r="I91" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3922,9 +3647,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H92" t="n">
-        <v>76.77646666666669</v>
-      </c>
-      <c r="I92" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3961,9 +3683,6 @@
         <v>12.8496</v>
       </c>
       <c r="H93" t="n">
-        <v>63.9268666666667</v>
-      </c>
-      <c r="I93" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3998,9 +3717,6 @@
         <v>0.5</v>
       </c>
       <c r="H94" t="n">
-        <v>63.4268666666667</v>
-      </c>
-      <c r="I94" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4037,9 +3753,6 @@
         <v>12.3</v>
       </c>
       <c r="H95" t="n">
-        <v>51.1268666666667</v>
-      </c>
-      <c r="I95" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4074,9 +3787,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H96" t="n">
-        <v>50.29353333333336</v>
-      </c>
-      <c r="I96" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4113,9 +3823,6 @@
         <v>12.8496</v>
       </c>
       <c r="H97" t="n">
-        <v>37.44393333333336</v>
-      </c>
-      <c r="I97" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4150,9 +3857,6 @@
         <v>10.8</v>
       </c>
       <c r="H98" t="n">
-        <v>26.64393333333336</v>
-      </c>
-      <c r="I98" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4187,9 +3891,6 @@
         <v>-120</v>
       </c>
       <c r="H99" t="n">
-        <v>146.6439333333334</v>
-      </c>
-      <c r="I99" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4224,9 +3925,6 @@
         <v>1.98</v>
       </c>
       <c r="H100" t="n">
-        <v>144.6639333333334</v>
-      </c>
-      <c r="I100" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4261,9 +3959,6 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="H101" t="n">
-        <v>144.5806</v>
-      </c>
-      <c r="I101" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4300,9 +3995,6 @@
         <v>12.8496</v>
       </c>
       <c r="H102" t="n">
-        <v>131.731</v>
-      </c>
-      <c r="I102" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4337,9 +4029,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H103" t="n">
-        <v>130.8976666666667</v>
-      </c>
-      <c r="I103" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4376,9 +4065,6 @@
         <v>10.86</v>
       </c>
       <c r="H104" t="n">
-        <v>120.0376666666667</v>
-      </c>
-      <c r="I104" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4413,9 +4099,6 @@
         <v>1.625</v>
       </c>
       <c r="H105" t="n">
-        <v>118.4126666666667</v>
-      </c>
-      <c r="I105" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4452,9 +4135,6 @@
         <v>10.8036</v>
       </c>
       <c r="H106" t="n">
-        <v>107.6090666666667</v>
-      </c>
-      <c r="I106" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4489,9 +4169,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H107" t="n">
-        <v>107.2757333333333</v>
-      </c>
-      <c r="I107" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4528,9 +4205,6 @@
         <v>10.86</v>
       </c>
       <c r="H108" t="n">
-        <v>96.41573333333335</v>
-      </c>
-      <c r="I108" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4565,9 +4239,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H109" t="n">
-        <v>95.62406666666668</v>
-      </c>
-      <c r="I109" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4604,9 +4275,6 @@
         <v>10.8036</v>
       </c>
       <c r="H110" t="n">
-        <v>84.82046666666668</v>
-      </c>
-      <c r="I110" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4641,9 +4309,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H111" t="n">
-        <v>84.48713333333335</v>
-      </c>
-      <c r="I111" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4680,9 +4345,6 @@
         <v>10.86</v>
       </c>
       <c r="H112" t="n">
-        <v>73.62713333333335</v>
-      </c>
-      <c r="I112" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4717,9 +4379,6 @@
         <v>1.791666666666667</v>
       </c>
       <c r="H113" t="n">
-        <v>71.83546666666668</v>
-      </c>
-      <c r="I113" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4756,9 +4415,6 @@
         <v>12.8496</v>
       </c>
       <c r="H114" t="n">
-        <v>58.98586666666668</v>
-      </c>
-      <c r="I114" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4793,9 +4449,6 @@
         <v>1.083333333333333</v>
       </c>
       <c r="H115" t="n">
-        <v>57.90253333333334</v>
-      </c>
-      <c r="I115" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4832,9 +4485,6 @@
         <v>10.86</v>
       </c>
       <c r="H116" t="n">
-        <v>47.04253333333335</v>
-      </c>
-      <c r="I116" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4869,9 +4519,6 @@
         <v>1.979999999999999</v>
       </c>
       <c r="H117" t="n">
-        <v>45.06253333333335</v>
-      </c>
-      <c r="I117" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4906,9 +4553,6 @@
         <v>-131.25</v>
       </c>
       <c r="H118" t="n">
-        <v>176.3125333333334</v>
-      </c>
-      <c r="I118" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4943,9 +4587,6 @@
         <v>1.98</v>
       </c>
       <c r="H119" t="n">
-        <v>174.3325333333334</v>
-      </c>
-      <c r="I119" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4980,9 +4621,6 @@
         <v>1.166666666666667</v>
       </c>
       <c r="H120" t="n">
-        <v>173.1658666666667</v>
-      </c>
-      <c r="I120" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5019,9 +4657,6 @@
         <v>10.8036</v>
       </c>
       <c r="H121" t="n">
-        <v>162.3622666666667</v>
-      </c>
-      <c r="I121" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5056,9 +4691,6 @@
         <v>10.32</v>
       </c>
       <c r="H122" t="n">
-        <v>152.0422666666667</v>
-      </c>
-      <c r="I122" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5093,9 +4725,6 @@
         <v>4.416666666666666</v>
       </c>
       <c r="H123" t="n">
-        <v>147.6256000000001</v>
-      </c>
-      <c r="I123" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5132,9 +4761,6 @@
         <v>10.8036</v>
       </c>
       <c r="H124" t="n">
-        <v>136.8220000000001</v>
-      </c>
-      <c r="I124" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5171,9 +4797,6 @@
         <v>1.98</v>
       </c>
       <c r="H125" t="n">
-        <v>253.02</v>
-      </c>
-      <c r="I125" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5210,9 +4833,6 @@
         <v>10.8036</v>
       </c>
       <c r="H126" t="n">
-        <v>242.2164</v>
-      </c>
-      <c r="I126" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5247,9 +4867,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H127" t="n">
-        <v>241.8830666666667</v>
-      </c>
-      <c r="I127" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5286,9 +4903,6 @@
         <v>10.86</v>
       </c>
       <c r="H128" t="n">
-        <v>231.0230666666667</v>
-      </c>
-      <c r="I128" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5323,9 +4937,6 @@
         <v>0.125</v>
       </c>
       <c r="H129" t="n">
-        <v>230.8980666666667</v>
-      </c>
-      <c r="I129" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5362,9 +4973,6 @@
         <v>10.8036</v>
       </c>
       <c r="H130" t="n">
-        <v>220.0944666666667</v>
-      </c>
-      <c r="I130" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5399,9 +5007,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H131" t="n">
-        <v>219.7611333333333</v>
-      </c>
-      <c r="I131" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5438,9 +5043,6 @@
         <v>10.86</v>
       </c>
       <c r="H132" t="n">
-        <v>208.9011333333333</v>
-      </c>
-      <c r="I132" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5475,9 +5077,6 @@
         <v>0.125</v>
       </c>
       <c r="H133" t="n">
-        <v>208.7761333333333</v>
-      </c>
-      <c r="I133" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5514,9 +5113,6 @@
         <v>12.8496</v>
       </c>
       <c r="H134" t="n">
-        <v>195.9265333333333</v>
-      </c>
-      <c r="I134" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5551,9 +5147,6 @@
         <v>0.5</v>
       </c>
       <c r="H135" t="n">
-        <v>195.4265333333333</v>
-      </c>
-      <c r="I135" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5590,9 +5183,6 @@
         <v>12.3</v>
       </c>
       <c r="H136" t="n">
-        <v>183.1265333333333</v>
-      </c>
-      <c r="I136" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5627,9 +5217,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H137" t="n">
-        <v>182.2932</v>
-      </c>
-      <c r="I137" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5666,9 +5253,6 @@
         <v>12.8496</v>
       </c>
       <c r="H138" t="n">
-        <v>169.4436</v>
-      </c>
-      <c r="I138" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5703,9 +5287,6 @@
         <v>0.5</v>
       </c>
       <c r="H139" t="n">
-        <v>168.9436</v>
-      </c>
-      <c r="I139" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5742,9 +5323,6 @@
         <v>12.3</v>
       </c>
       <c r="H140" t="n">
-        <v>156.6436</v>
-      </c>
-      <c r="I140" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5779,9 +5357,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H141" t="n">
-        <v>155.8102666666666</v>
-      </c>
-      <c r="I141" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5818,9 +5393,6 @@
         <v>12.8496</v>
       </c>
       <c r="H142" t="n">
-        <v>142.9606666666666</v>
-      </c>
-      <c r="I142" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5855,9 +5427,6 @@
         <v>0.5</v>
       </c>
       <c r="H143" t="n">
-        <v>142.4606666666666</v>
-      </c>
-      <c r="I143" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5894,9 +5463,6 @@
         <v>12.3</v>
       </c>
       <c r="H144" t="n">
-        <v>130.1606666666667</v>
-      </c>
-      <c r="I144" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5931,9 +5497,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H145" t="n">
-        <v>129.3273333333333</v>
-      </c>
-      <c r="I145" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5970,9 +5533,6 @@
         <v>12.8496</v>
       </c>
       <c r="H146" t="n">
-        <v>116.4777333333333</v>
-      </c>
-      <c r="I146" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6007,9 +5567,6 @@
         <v>0.5</v>
       </c>
       <c r="H147" t="n">
-        <v>115.9777333333333</v>
-      </c>
-      <c r="I147" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6046,9 +5603,6 @@
         <v>12.3</v>
       </c>
       <c r="H148" t="n">
-        <v>103.6777333333333</v>
-      </c>
-      <c r="I148" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6083,9 +5637,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H149" t="n">
-        <v>102.8444</v>
-      </c>
-      <c r="I149" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6122,9 +5673,6 @@
         <v>12.8496</v>
       </c>
       <c r="H150" t="n">
-        <v>89.9948</v>
-      </c>
-      <c r="I150" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6159,9 +5707,6 @@
         <v>0.5</v>
       </c>
       <c r="H151" t="n">
-        <v>89.4948</v>
-      </c>
-      <c r="I151" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6198,9 +5743,6 @@
         <v>12.3</v>
       </c>
       <c r="H152" t="n">
-        <v>77.1948</v>
-      </c>
-      <c r="I152" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6235,9 +5777,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H153" t="n">
-        <v>76.36146666666667</v>
-      </c>
-      <c r="I153" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6274,9 +5813,6 @@
         <v>12.8496</v>
       </c>
       <c r="H154" t="n">
-        <v>63.51186666666668</v>
-      </c>
-      <c r="I154" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6311,9 +5847,6 @@
         <v>0.5</v>
       </c>
       <c r="H155" t="n">
-        <v>63.01186666666668</v>
-      </c>
-      <c r="I155" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6350,9 +5883,6 @@
         <v>12.3</v>
       </c>
       <c r="H156" t="n">
-        <v>50.71186666666668</v>
-      </c>
-      <c r="I156" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6387,9 +5917,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H157" t="n">
-        <v>49.87853333333334</v>
-      </c>
-      <c r="I157" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6426,9 +5953,6 @@
         <v>12.8496</v>
       </c>
       <c r="H158" t="n">
-        <v>37.02893333333334</v>
-      </c>
-      <c r="I158" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6463,9 +5987,6 @@
         <v>10.8</v>
       </c>
       <c r="H159" t="n">
-        <v>26.22893333333334</v>
-      </c>
-      <c r="I159" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6500,9 +6021,6 @@
         <v>-120</v>
       </c>
       <c r="H160" t="n">
-        <v>146.2289333333333</v>
-      </c>
-      <c r="I160" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6537,9 +6055,6 @@
         <v>1.98</v>
       </c>
       <c r="H161" t="n">
-        <v>144.2489333333334</v>
-      </c>
-      <c r="I161" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6574,9 +6089,6 @@
         <v>0.5</v>
       </c>
       <c r="H162" t="n">
-        <v>143.7489333333334</v>
-      </c>
-      <c r="I162" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6613,9 +6125,6 @@
         <v>10.8036</v>
       </c>
       <c r="H163" t="n">
-        <v>132.9453333333334</v>
-      </c>
-      <c r="I163" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6650,9 +6159,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H164" t="n">
-        <v>132.5286666666667</v>
-      </c>
-      <c r="I164" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6689,9 +6195,6 @@
         <v>12.3</v>
       </c>
       <c r="H165" t="n">
-        <v>120.2286666666667</v>
-      </c>
-      <c r="I165" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6726,9 +6229,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H166" t="n">
-        <v>119.3953333333334</v>
-      </c>
-      <c r="I166" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6765,9 +6265,6 @@
         <v>10.8036</v>
       </c>
       <c r="H167" t="n">
-        <v>108.5917333333334</v>
-      </c>
-      <c r="I167" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6802,9 +6299,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H168" t="n">
-        <v>108.1750666666667</v>
-      </c>
-      <c r="I168" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6841,9 +6335,6 @@
         <v>12.3</v>
       </c>
       <c r="H169" t="n">
-        <v>95.87506666666671</v>
-      </c>
-      <c r="I169" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6878,9 +6369,6 @@
         <v>1.416666666666667</v>
       </c>
       <c r="H170" t="n">
-        <v>94.45840000000004</v>
-      </c>
-      <c r="I170" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6917,9 +6405,6 @@
         <v>12.8496</v>
       </c>
       <c r="H171" t="n">
-        <v>81.60880000000004</v>
-      </c>
-      <c r="I171" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6954,9 +6439,6 @@
         <v>0.5</v>
       </c>
       <c r="H172" t="n">
-        <v>81.10880000000004</v>
-      </c>
-      <c r="I172" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6993,9 +6475,6 @@
         <v>12.3</v>
       </c>
       <c r="H173" t="n">
-        <v>68.80880000000005</v>
-      </c>
-      <c r="I173" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7030,9 +6509,6 @@
         <v>10.32</v>
       </c>
       <c r="H174" t="n">
-        <v>58.48880000000005</v>
-      </c>
-      <c r="I174" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7067,9 +6543,6 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="H175" t="n">
-        <v>58.40546666666671</v>
-      </c>
-      <c r="I175" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7106,9 +6579,6 @@
         <v>12.3</v>
       </c>
       <c r="H176" t="n">
-        <v>46.10546666666671</v>
-      </c>
-      <c r="I176" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7143,9 +6613,6 @@
         <v>1.979999999999999</v>
       </c>
       <c r="H177" t="n">
-        <v>44.12546666666672</v>
-      </c>
-      <c r="I177" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7180,9 +6647,6 @@
         <v>-142.5</v>
       </c>
       <c r="H178" t="n">
-        <v>186.6254666666667</v>
-      </c>
-      <c r="I178" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7217,9 +6681,6 @@
         <v>1.98</v>
       </c>
       <c r="H179" t="n">
-        <v>184.6454666666667</v>
-      </c>
-      <c r="I179" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7254,9 +6715,6 @@
         <v>1.166666666666667</v>
       </c>
       <c r="H180" t="n">
-        <v>183.4788000000001</v>
-      </c>
-      <c r="I180" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7293,9 +6751,6 @@
         <v>12.8496</v>
       </c>
       <c r="H181" t="n">
-        <v>170.6292000000001</v>
-      </c>
-      <c r="I181" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7330,9 +6785,6 @@
         <v>10.32</v>
       </c>
       <c r="H182" t="n">
-        <v>160.3092000000001</v>
-      </c>
-      <c r="I182" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7367,9 +6819,6 @@
         <v>2.583333333333333</v>
       </c>
       <c r="H183" t="n">
-        <v>157.7258666666667</v>
-      </c>
-      <c r="I183" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7406,9 +6855,6 @@
         <v>10.8036</v>
       </c>
       <c r="H184" t="n">
-        <v>146.9222666666667</v>
-      </c>
-      <c r="I184" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7443,9 +6889,6 @@
         <v>10.32</v>
       </c>
       <c r="H185" t="n">
-        <v>136.6022666666667</v>
-      </c>
-      <c r="I185" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7480,9 +6923,6 @@
         <v>13.91666666666667</v>
       </c>
       <c r="H186" t="n">
-        <v>122.6856000000001</v>
-      </c>
-      <c r="I186" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7519,9 +6959,6 @@
         <v>10.8036</v>
       </c>
       <c r="H187" t="n">
-        <v>111.8820000000001</v>
-      </c>
-      <c r="I187" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7558,9 +6995,6 @@
         <v>1.98</v>
       </c>
       <c r="H188" t="n">
-        <v>253.02</v>
-      </c>
-      <c r="I188" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7597,9 +7031,6 @@
         <v>12.8496</v>
       </c>
       <c r="H189" t="n">
-        <v>240.1704</v>
-      </c>
-      <c r="I189" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7634,9 +7065,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H190" t="n">
-        <v>239.7537333333333</v>
-      </c>
-      <c r="I190" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7673,9 +7101,6 @@
         <v>12.3</v>
       </c>
       <c r="H191" t="n">
-        <v>227.4537333333333</v>
-      </c>
-      <c r="I191" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7710,9 +7135,6 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="H192" t="n">
-        <v>226.7870666666667</v>
-      </c>
-      <c r="I192" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7749,9 +7171,6 @@
         <v>10.8036</v>
       </c>
       <c r="H193" t="n">
-        <v>215.9834666666667</v>
-      </c>
-      <c r="I193" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7786,9 +7205,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H194" t="n">
-        <v>215.6501333333333</v>
-      </c>
-      <c r="I194" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7825,9 +7241,6 @@
         <v>10.86</v>
       </c>
       <c r="H195" t="n">
-        <v>204.7901333333333</v>
-      </c>
-      <c r="I195" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7862,9 +7275,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H196" t="n">
-        <v>203.9984666666667</v>
-      </c>
-      <c r="I196" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7901,9 +7311,6 @@
         <v>10.8036</v>
       </c>
       <c r="H197" t="n">
-        <v>193.1948666666667</v>
-      </c>
-      <c r="I197" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7938,9 +7345,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H198" t="n">
-        <v>192.8615333333333</v>
-      </c>
-      <c r="I198" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7977,9 +7381,6 @@
         <v>10.86</v>
       </c>
       <c r="H199" t="n">
-        <v>182.0015333333333</v>
-      </c>
-      <c r="I199" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8014,9 +7415,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H200" t="n">
-        <v>181.2098666666667</v>
-      </c>
-      <c r="I200" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8053,9 +7451,6 @@
         <v>10.8036</v>
       </c>
       <c r="H201" t="n">
-        <v>170.4062666666667</v>
-      </c>
-      <c r="I201" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8090,9 +7485,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H202" t="n">
-        <v>170.0729333333333</v>
-      </c>
-      <c r="I202" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8129,9 +7521,6 @@
         <v>10.86</v>
       </c>
       <c r="H203" t="n">
-        <v>159.2129333333333</v>
-      </c>
-      <c r="I203" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8166,9 +7555,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H204" t="n">
-        <v>158.4212666666667</v>
-      </c>
-      <c r="I204" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8205,9 +7591,6 @@
         <v>10.8036</v>
       </c>
       <c r="H205" t="n">
-        <v>147.6176666666667</v>
-      </c>
-      <c r="I205" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8242,9 +7625,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H206" t="n">
-        <v>147.2843333333333</v>
-      </c>
-      <c r="I206" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8281,9 +7661,6 @@
         <v>10.86</v>
       </c>
       <c r="H207" t="n">
-        <v>136.4243333333333</v>
-      </c>
-      <c r="I207" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8318,9 +7695,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H208" t="n">
-        <v>135.6326666666667</v>
-      </c>
-      <c r="I208" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8357,9 +7731,6 @@
         <v>10.8036</v>
       </c>
       <c r="H209" t="n">
-        <v>124.8290666666667</v>
-      </c>
-      <c r="I209" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8394,9 +7765,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H210" t="n">
-        <v>124.4957333333333</v>
-      </c>
-      <c r="I210" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8433,9 +7801,6 @@
         <v>10.86</v>
       </c>
       <c r="H211" t="n">
-        <v>113.6357333333333</v>
-      </c>
-      <c r="I211" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8470,9 +7835,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H212" t="n">
-        <v>112.8440666666667</v>
-      </c>
-      <c r="I212" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8509,9 +7871,6 @@
         <v>10.8036</v>
       </c>
       <c r="H213" t="n">
-        <v>102.0404666666667</v>
-      </c>
-      <c r="I213" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8546,9 +7905,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H214" t="n">
-        <v>101.7071333333333</v>
-      </c>
-      <c r="I214" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8585,9 +7941,6 @@
         <v>10.86</v>
       </c>
       <c r="H215" t="n">
-        <v>90.84713333333333</v>
-      </c>
-      <c r="I215" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8622,9 +7975,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H216" t="n">
-        <v>90.05546666666666</v>
-      </c>
-      <c r="I216" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8661,9 +8011,6 @@
         <v>10.8036</v>
       </c>
       <c r="H217" t="n">
-        <v>79.25186666666666</v>
-      </c>
-      <c r="I217" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8698,9 +8045,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H218" t="n">
-        <v>78.91853333333333</v>
-      </c>
-      <c r="I218" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8737,9 +8081,6 @@
         <v>10.86</v>
       </c>
       <c r="H219" t="n">
-        <v>68.05853333333333</v>
-      </c>
-      <c r="I219" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8774,9 +8115,6 @@
         <v>0.9583333333333334</v>
       </c>
       <c r="H220" t="n">
-        <v>67.1002</v>
-      </c>
-      <c r="I220" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8813,9 +8151,6 @@
         <v>12.8496</v>
       </c>
       <c r="H221" t="n">
-        <v>54.25060000000001</v>
-      </c>
-      <c r="I221" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8850,9 +8185,6 @@
         <v>0.5</v>
       </c>
       <c r="H222" t="n">
-        <v>53.75060000000001</v>
-      </c>
-      <c r="I222" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8889,9 +8221,6 @@
         <v>12.3</v>
       </c>
       <c r="H223" t="n">
-        <v>41.45060000000001</v>
-      </c>
-      <c r="I223" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8926,9 +8255,6 @@
         <v>1.979999999999999</v>
       </c>
       <c r="H224" t="n">
-        <v>39.47060000000001</v>
-      </c>
-      <c r="I224" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8963,9 +8289,6 @@
         <v>-142.5</v>
       </c>
       <c r="H225" t="n">
-        <v>181.9706</v>
-      </c>
-      <c r="I225" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9000,9 +8323,6 @@
         <v>1.98</v>
       </c>
       <c r="H226" t="n">
-        <v>179.9906</v>
-      </c>
-      <c r="I226" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9037,9 +8357,6 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H227" t="n">
-        <v>179.0739333333334</v>
-      </c>
-      <c r="I227" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9076,9 +8393,6 @@
         <v>10.8036</v>
       </c>
       <c r="H228" t="n">
-        <v>168.2703333333334</v>
-      </c>
-      <c r="I228" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9113,9 +8427,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H229" t="n">
-        <v>167.937</v>
-      </c>
-      <c r="I229" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9152,9 +8463,6 @@
         <v>10.86</v>
       </c>
       <c r="H230" t="n">
-        <v>157.077</v>
-      </c>
-      <c r="I230" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9189,9 +8497,6 @@
         <v>1.625</v>
       </c>
       <c r="H231" t="n">
-        <v>155.452</v>
-      </c>
-      <c r="I231" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9228,9 +8533,6 @@
         <v>10.8036</v>
       </c>
       <c r="H232" t="n">
-        <v>144.6484</v>
-      </c>
-      <c r="I232" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9265,9 +8567,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H233" t="n">
-        <v>144.2317333333334</v>
-      </c>
-      <c r="I233" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9304,9 +8603,6 @@
         <v>12.3</v>
       </c>
       <c r="H234" t="n">
-        <v>131.9317333333334</v>
-      </c>
-      <c r="I234" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9341,9 +8637,6 @@
         <v>1.5</v>
       </c>
       <c r="H235" t="n">
-        <v>130.4317333333334</v>
-      </c>
-      <c r="I235" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9380,9 +8673,6 @@
         <v>12.8496</v>
       </c>
       <c r="H236" t="n">
-        <v>117.5821333333334</v>
-      </c>
-      <c r="I236" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9417,9 +8707,6 @@
         <v>1.666666666666667</v>
       </c>
       <c r="H237" t="n">
-        <v>115.9154666666667</v>
-      </c>
-      <c r="I237" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9456,9 +8743,6 @@
         <v>12.3</v>
       </c>
       <c r="H238" t="n">
-        <v>103.6154666666667</v>
-      </c>
-      <c r="I238" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9493,9 +8777,6 @@
         <v>10.32</v>
       </c>
       <c r="H239" t="n">
-        <v>93.29546666666673</v>
-      </c>
-      <c r="I239" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9530,9 +8811,6 @@
         <v>2.666666666666667</v>
       </c>
       <c r="H240" t="n">
-        <v>90.62880000000006</v>
-      </c>
-      <c r="I240" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9569,9 +8847,6 @@
         <v>10.86</v>
       </c>
       <c r="H241" t="n">
-        <v>79.76880000000006</v>
-      </c>
-      <c r="I241" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9606,9 +8881,6 @@
         <v>10.32</v>
       </c>
       <c r="H242" t="n">
-        <v>69.44880000000006</v>
-      </c>
-      <c r="I242" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9643,9 +8915,6 @@
         <v>13.375</v>
       </c>
       <c r="H243" t="n">
-        <v>56.07380000000006</v>
-      </c>
-      <c r="I243" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9682,9 +8951,6 @@
         <v>10.86</v>
       </c>
       <c r="H244" t="n">
-        <v>45.21380000000006</v>
-      </c>
-      <c r="I244" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9721,9 +8987,6 @@
         <v>1.98</v>
       </c>
       <c r="H245" t="n">
-        <v>253.02</v>
-      </c>
-      <c r="I245" t="n">
         <v>5</v>
       </c>
     </row>
@@ -9760,9 +9023,6 @@
         <v>12.8496</v>
       </c>
       <c r="H246" t="n">
-        <v>240.1704</v>
-      </c>
-      <c r="I246" t="n">
         <v>5</v>
       </c>
     </row>
@@ -9797,9 +9057,6 @@
         <v>0.5</v>
       </c>
       <c r="H247" t="n">
-        <v>239.6704</v>
-      </c>
-      <c r="I247" t="n">
         <v>5</v>
       </c>
     </row>
@@ -9836,9 +9093,6 @@
         <v>12.3</v>
       </c>
       <c r="H248" t="n">
-        <v>227.3704</v>
-      </c>
-      <c r="I248" t="n">
         <v>5</v>
       </c>
     </row>
@@ -9873,9 +9127,6 @@
         <v>0.25</v>
       </c>
       <c r="H249" t="n">
-        <v>227.1204</v>
-      </c>
-      <c r="I249" t="n">
         <v>5</v>
       </c>
     </row>
@@ -9912,9 +9163,6 @@
         <v>10.8036</v>
       </c>
       <c r="H250" t="n">
-        <v>216.3168</v>
-      </c>
-      <c r="I250" t="n">
         <v>5</v>
       </c>
     </row>
@@ -9949,9 +9197,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H251" t="n">
-        <v>215.9001333333334</v>
-      </c>
-      <c r="I251" t="n">
         <v>5</v>
       </c>
     </row>
@@ -9988,9 +9233,6 @@
         <v>12.3</v>
       </c>
       <c r="H252" t="n">
-        <v>203.6001333333334</v>
-      </c>
-      <c r="I252" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10025,9 +9267,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H253" t="n">
-        <v>203.1834666666667</v>
-      </c>
-      <c r="I253" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10064,9 +9303,6 @@
         <v>12.8496</v>
       </c>
       <c r="H254" t="n">
-        <v>190.3338666666667</v>
-      </c>
-      <c r="I254" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10101,9 +9337,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H255" t="n">
-        <v>189.5005333333334</v>
-      </c>
-      <c r="I255" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10140,9 +9373,6 @@
         <v>10.86</v>
       </c>
       <c r="H256" t="n">
-        <v>178.6405333333333</v>
-      </c>
-      <c r="I256" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10177,9 +9407,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H257" t="n">
-        <v>177.8488666666667</v>
-      </c>
-      <c r="I257" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10216,9 +9443,6 @@
         <v>10.8036</v>
       </c>
       <c r="H258" t="n">
-        <v>167.0452666666667</v>
-      </c>
-      <c r="I258" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10253,9 +9477,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H259" t="n">
-        <v>166.6286</v>
-      </c>
-      <c r="I259" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10292,9 +9513,6 @@
         <v>12.3</v>
       </c>
       <c r="H260" t="n">
-        <v>154.3286000000001</v>
-      </c>
-      <c r="I260" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10329,9 +9547,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H261" t="n">
-        <v>153.9119333333334</v>
-      </c>
-      <c r="I261" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10368,9 +9583,6 @@
         <v>12.8496</v>
       </c>
       <c r="H262" t="n">
-        <v>141.0623333333334</v>
-      </c>
-      <c r="I262" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10405,9 +9617,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H263" t="n">
-        <v>140.229</v>
-      </c>
-      <c r="I263" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10444,9 +9653,6 @@
         <v>10.86</v>
       </c>
       <c r="H264" t="n">
-        <v>129.369</v>
-      </c>
-      <c r="I264" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10481,9 +9687,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H265" t="n">
-        <v>128.5773333333334</v>
-      </c>
-      <c r="I265" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10520,9 +9723,6 @@
         <v>10.8036</v>
       </c>
       <c r="H266" t="n">
-        <v>117.7737333333334</v>
-      </c>
-      <c r="I266" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10557,9 +9757,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H267" t="n">
-        <v>117.3570666666667</v>
-      </c>
-      <c r="I267" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10596,9 +9793,6 @@
         <v>12.3</v>
       </c>
       <c r="H268" t="n">
-        <v>105.0570666666667</v>
-      </c>
-      <c r="I268" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10633,9 +9827,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H269" t="n">
-        <v>104.6404</v>
-      </c>
-      <c r="I269" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10672,9 +9863,6 @@
         <v>12.8496</v>
       </c>
       <c r="H270" t="n">
-        <v>91.79080000000003</v>
-      </c>
-      <c r="I270" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10709,9 +9897,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H271" t="n">
-        <v>90.9574666666667</v>
-      </c>
-      <c r="I271" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10748,9 +9933,6 @@
         <v>10.86</v>
       </c>
       <c r="H272" t="n">
-        <v>80.0974666666667</v>
-      </c>
-      <c r="I272" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10785,9 +9967,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H273" t="n">
-        <v>79.30580000000003</v>
-      </c>
-      <c r="I273" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10824,9 +10003,6 @@
         <v>10.8036</v>
       </c>
       <c r="H274" t="n">
-        <v>68.50220000000003</v>
-      </c>
-      <c r="I274" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10861,9 +10037,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H275" t="n">
-        <v>68.1688666666667</v>
-      </c>
-      <c r="I275" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10900,9 +10073,6 @@
         <v>10.86</v>
       </c>
       <c r="H276" t="n">
-        <v>57.3088666666667</v>
-      </c>
-      <c r="I276" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10937,9 +10107,6 @@
         <v>1.625</v>
       </c>
       <c r="H277" t="n">
-        <v>55.6838666666667</v>
-      </c>
-      <c r="I277" t="n">
         <v>5</v>
       </c>
     </row>
@@ -10976,9 +10143,6 @@
         <v>10.8036</v>
       </c>
       <c r="H278" t="n">
-        <v>44.8802666666667</v>
-      </c>
-      <c r="I278" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11013,9 +10177,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H279" t="n">
-        <v>44.54693333333336</v>
-      </c>
-      <c r="I279" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11052,9 +10213,6 @@
         <v>10.86</v>
       </c>
       <c r="H280" t="n">
-        <v>33.68693333333336</v>
-      </c>
-      <c r="I280" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11089,9 +10247,6 @@
         <v>1.979999999999999</v>
       </c>
       <c r="H281" t="n">
-        <v>31.70693333333336</v>
-      </c>
-      <c r="I281" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11126,9 +10281,6 @@
         <v>-116.25</v>
       </c>
       <c r="H282" t="n">
-        <v>147.9569333333334</v>
-      </c>
-      <c r="I282" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11163,9 +10315,6 @@
         <v>1.98</v>
       </c>
       <c r="H283" t="n">
-        <v>145.9769333333334</v>
-      </c>
-      <c r="I283" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11200,9 +10349,6 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="H284" t="n">
-        <v>145.8936</v>
-      </c>
-      <c r="I284" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11239,9 +10385,6 @@
         <v>12.8496</v>
       </c>
       <c r="H285" t="n">
-        <v>133.044</v>
-      </c>
-      <c r="I285" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11276,9 +10419,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H286" t="n">
-        <v>132.2106666666667</v>
-      </c>
-      <c r="I286" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11315,9 +10455,6 @@
         <v>10.86</v>
       </c>
       <c r="H287" t="n">
-        <v>121.3506666666667</v>
-      </c>
-      <c r="I287" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11352,9 +10489,6 @@
         <v>1.625</v>
       </c>
       <c r="H288" t="n">
-        <v>119.7256666666667</v>
-      </c>
-      <c r="I288" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11391,9 +10525,6 @@
         <v>10.8036</v>
       </c>
       <c r="H289" t="n">
-        <v>108.9220666666667</v>
-      </c>
-      <c r="I289" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11428,9 +10559,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H290" t="n">
-        <v>108.5887333333333</v>
-      </c>
-      <c r="I290" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11467,9 +10595,6 @@
         <v>10.86</v>
       </c>
       <c r="H291" t="n">
-        <v>97.72873333333334</v>
-      </c>
-      <c r="I291" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11504,9 +10629,6 @@
         <v>2.041666666666667</v>
       </c>
       <c r="H292" t="n">
-        <v>95.68706666666667</v>
-      </c>
-      <c r="I292" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11543,9 +10665,6 @@
         <v>12.8496</v>
       </c>
       <c r="H293" t="n">
-        <v>82.83746666666667</v>
-      </c>
-      <c r="I293" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11580,9 +10699,6 @@
         <v>2.083333333333333</v>
       </c>
       <c r="H294" t="n">
-        <v>80.75413333333334</v>
-      </c>
-      <c r="I294" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11619,9 +10735,6 @@
         <v>10.86</v>
       </c>
       <c r="H295" t="n">
-        <v>69.89413333333334</v>
-      </c>
-      <c r="I295" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11656,9 +10769,6 @@
         <v>7.708333333333334</v>
       </c>
       <c r="H296" t="n">
-        <v>62.18580000000001</v>
-      </c>
-      <c r="I296" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11695,9 +10805,6 @@
         <v>10.8036</v>
       </c>
       <c r="H297" t="n">
-        <v>51.3822</v>
-      </c>
-      <c r="I297" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11732,9 +10839,6 @@
         <v>10.8</v>
       </c>
       <c r="H298" t="n">
-        <v>40.5822</v>
-      </c>
-      <c r="I298" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11769,9 +10873,6 @@
         <v>-208.72876</v>
       </c>
       <c r="H299" t="n">
-        <v>249.31096</v>
-      </c>
-      <c r="I299" t="n">
         <v>5</v>
       </c>
     </row>
@@ -11808,9 +10909,6 @@
         <v>1.98</v>
       </c>
       <c r="H300" t="n">
-        <v>253.02</v>
-      </c>
-      <c r="I300" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11847,9 +10945,6 @@
         <v>10.8036</v>
       </c>
       <c r="H301" t="n">
-        <v>242.2164</v>
-      </c>
-      <c r="I301" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11884,9 +10979,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H302" t="n">
-        <v>241.8830666666667</v>
-      </c>
-      <c r="I302" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11923,9 +11015,6 @@
         <v>10.86</v>
       </c>
       <c r="H303" t="n">
-        <v>231.0230666666667</v>
-      </c>
-      <c r="I303" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11960,9 +11049,6 @@
         <v>0.5416666666666667</v>
       </c>
       <c r="H304" t="n">
-        <v>230.4814</v>
-      </c>
-      <c r="I304" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11999,9 +11085,6 @@
         <v>12.8496</v>
       </c>
       <c r="H305" t="n">
-        <v>217.6318</v>
-      </c>
-      <c r="I305" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12036,9 +11119,6 @@
         <v>0.5</v>
       </c>
       <c r="H306" t="n">
-        <v>217.1318</v>
-      </c>
-      <c r="I306" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12075,9 +11155,6 @@
         <v>12.3</v>
       </c>
       <c r="H307" t="n">
-        <v>204.8318</v>
-      </c>
-      <c r="I307" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12112,9 +11189,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H308" t="n">
-        <v>203.9984666666666</v>
-      </c>
-      <c r="I308" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12151,9 +11225,6 @@
         <v>12.8496</v>
       </c>
       <c r="H309" t="n">
-        <v>191.1488666666666</v>
-      </c>
-      <c r="I309" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12188,9 +11259,6 @@
         <v>0.5</v>
       </c>
       <c r="H310" t="n">
-        <v>190.6488666666666</v>
-      </c>
-      <c r="I310" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12227,9 +11295,6 @@
         <v>12.3</v>
       </c>
       <c r="H311" t="n">
-        <v>178.3488666666667</v>
-      </c>
-      <c r="I311" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12264,9 +11329,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H312" t="n">
-        <v>177.5155333333333</v>
-      </c>
-      <c r="I312" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12303,9 +11365,6 @@
         <v>12.8496</v>
       </c>
       <c r="H313" t="n">
-        <v>164.6659333333333</v>
-      </c>
-      <c r="I313" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12340,9 +11399,6 @@
         <v>0.5</v>
       </c>
       <c r="H314" t="n">
-        <v>164.1659333333333</v>
-      </c>
-      <c r="I314" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12379,9 +11435,6 @@
         <v>12.3</v>
       </c>
       <c r="H315" t="n">
-        <v>151.8659333333333</v>
-      </c>
-      <c r="I315" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12416,9 +11469,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H316" t="n">
-        <v>151.0326</v>
-      </c>
-      <c r="I316" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12455,9 +11505,6 @@
         <v>12.8496</v>
       </c>
       <c r="H317" t="n">
-        <v>138.183</v>
-      </c>
-      <c r="I317" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12492,9 +11539,6 @@
         <v>0.5</v>
       </c>
       <c r="H318" t="n">
-        <v>137.683</v>
-      </c>
-      <c r="I318" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12531,9 +11575,6 @@
         <v>12.3</v>
       </c>
       <c r="H319" t="n">
-        <v>125.383</v>
-      </c>
-      <c r="I319" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12568,9 +11609,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H320" t="n">
-        <v>124.5496666666666</v>
-      </c>
-      <c r="I320" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12607,9 +11645,6 @@
         <v>12.8496</v>
       </c>
       <c r="H321" t="n">
-        <v>111.7000666666666</v>
-      </c>
-      <c r="I321" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12644,9 +11679,6 @@
         <v>0.5</v>
       </c>
       <c r="H322" t="n">
-        <v>111.2000666666666</v>
-      </c>
-      <c r="I322" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12683,9 +11715,6 @@
         <v>12.3</v>
       </c>
       <c r="H323" t="n">
-        <v>98.90006666666665</v>
-      </c>
-      <c r="I323" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12720,9 +11749,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H324" t="n">
-        <v>98.06673333333332</v>
-      </c>
-      <c r="I324" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12759,9 +11785,6 @@
         <v>12.8496</v>
       </c>
       <c r="H325" t="n">
-        <v>85.21713333333332</v>
-      </c>
-      <c r="I325" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12796,9 +11819,6 @@
         <v>0.5</v>
       </c>
       <c r="H326" t="n">
-        <v>84.71713333333332</v>
-      </c>
-      <c r="I326" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12835,9 +11855,6 @@
         <v>12.3</v>
       </c>
       <c r="H327" t="n">
-        <v>72.41713333333333</v>
-      </c>
-      <c r="I327" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12872,9 +11889,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H328" t="n">
-        <v>71.5838</v>
-      </c>
-      <c r="I328" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12911,9 +11925,6 @@
         <v>12.8496</v>
       </c>
       <c r="H329" t="n">
-        <v>58.7342</v>
-      </c>
-      <c r="I329" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12948,9 +11959,6 @@
         <v>0.5</v>
       </c>
       <c r="H330" t="n">
-        <v>58.2342</v>
-      </c>
-      <c r="I330" t="n">
         <v>6</v>
       </c>
     </row>
@@ -12987,9 +11995,6 @@
         <v>12.3</v>
       </c>
       <c r="H331" t="n">
-        <v>45.9342</v>
-      </c>
-      <c r="I331" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13024,9 +12029,6 @@
         <v>1.979999999999999</v>
       </c>
       <c r="H332" t="n">
-        <v>43.95420000000001</v>
-      </c>
-      <c r="I332" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13061,9 +12063,6 @@
         <v>-120</v>
       </c>
       <c r="H333" t="n">
-        <v>163.9542</v>
-      </c>
-      <c r="I333" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13098,9 +12097,6 @@
         <v>1.98</v>
       </c>
       <c r="H334" t="n">
-        <v>161.9742</v>
-      </c>
-      <c r="I334" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13135,9 +12131,6 @@
         <v>0.75</v>
       </c>
       <c r="H335" t="n">
-        <v>161.2242</v>
-      </c>
-      <c r="I335" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13174,9 +12167,6 @@
         <v>10.8036</v>
       </c>
       <c r="H336" t="n">
-        <v>150.4206</v>
-      </c>
-      <c r="I336" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13211,9 +12201,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H337" t="n">
-        <v>150.0039333333334</v>
-      </c>
-      <c r="I337" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13250,9 +12237,6 @@
         <v>12.3</v>
       </c>
       <c r="H338" t="n">
-        <v>137.7039333333334</v>
-      </c>
-      <c r="I338" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13287,9 +12271,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H339" t="n">
-        <v>136.8706000000001</v>
-      </c>
-      <c r="I339" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13326,9 +12307,6 @@
         <v>10.8036</v>
       </c>
       <c r="H340" t="n">
-        <v>126.067</v>
-      </c>
-      <c r="I340" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13363,9 +12341,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H341" t="n">
-        <v>125.6503333333334</v>
-      </c>
-      <c r="I341" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13402,9 +12377,6 @@
         <v>12.3</v>
       </c>
       <c r="H342" t="n">
-        <v>113.3503333333334</v>
-      </c>
-      <c r="I342" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13439,9 +12411,6 @@
         <v>1.416666666666667</v>
       </c>
       <c r="H343" t="n">
-        <v>111.9336666666667</v>
-      </c>
-      <c r="I343" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13478,9 +12447,6 @@
         <v>12.8496</v>
       </c>
       <c r="H344" t="n">
-        <v>99.08406666666671</v>
-      </c>
-      <c r="I344" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13515,9 +12481,6 @@
         <v>0.5</v>
       </c>
       <c r="H345" t="n">
-        <v>98.58406666666671</v>
-      </c>
-      <c r="I345" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13554,9 +12517,6 @@
         <v>12.3</v>
       </c>
       <c r="H346" t="n">
-        <v>86.28406666666672</v>
-      </c>
-      <c r="I346" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13591,9 +12551,6 @@
         <v>10.32</v>
       </c>
       <c r="H347" t="n">
-        <v>75.96406666666672</v>
-      </c>
-      <c r="I347" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13628,9 +12585,6 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="H348" t="n">
-        <v>75.8807333333334</v>
-      </c>
-      <c r="I348" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13667,9 +12621,6 @@
         <v>12.3</v>
       </c>
       <c r="H349" t="n">
-        <v>63.5807333333334</v>
-      </c>
-      <c r="I349" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13704,9 +12655,6 @@
         <v>10.32</v>
       </c>
       <c r="H350" t="n">
-        <v>53.2607333333334</v>
-      </c>
-      <c r="I350" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13741,9 +12689,6 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="H351" t="n">
-        <v>53.17740000000006</v>
-      </c>
-      <c r="I351" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13780,9 +12725,6 @@
         <v>12.3</v>
       </c>
       <c r="H352" t="n">
-        <v>40.87740000000007</v>
-      </c>
-      <c r="I352" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13817,9 +12759,6 @@
         <v>1.979999999999999</v>
       </c>
       <c r="H353" t="n">
-        <v>38.89740000000007</v>
-      </c>
-      <c r="I353" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13854,9 +12793,6 @@
         <v>-165</v>
       </c>
       <c r="H354" t="n">
-        <v>203.8974000000001</v>
-      </c>
-      <c r="I354" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13891,9 +12827,6 @@
         <v>10.8</v>
       </c>
       <c r="H355" t="n">
-        <v>193.0974000000001</v>
-      </c>
-      <c r="I355" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13928,9 +12861,6 @@
         <v>9.416666666666666</v>
       </c>
       <c r="H356" t="n">
-        <v>183.6807333333334</v>
-      </c>
-      <c r="I356" t="n">
         <v>6</v>
       </c>
     </row>
@@ -13967,9 +12897,6 @@
         <v>10.86</v>
       </c>
       <c r="H357" t="n">
-        <v>172.8207333333334</v>
-      </c>
-      <c r="I357" t="n">
         <v>6</v>
       </c>
     </row>
@@ -14006,9 +12933,6 @@
         <v>1.98</v>
       </c>
       <c r="H358" t="n">
-        <v>253.02</v>
-      </c>
-      <c r="I358" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14045,9 +12969,6 @@
         <v>10.8036</v>
       </c>
       <c r="H359" t="n">
-        <v>242.2164</v>
-      </c>
-      <c r="I359" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14082,9 +13003,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H360" t="n">
-        <v>241.8830666666667</v>
-      </c>
-      <c r="I360" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14121,9 +13039,6 @@
         <v>10.86</v>
       </c>
       <c r="H361" t="n">
-        <v>231.0230666666667</v>
-      </c>
-      <c r="I361" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14158,9 +13073,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H362" t="n">
-        <v>230.2314</v>
-      </c>
-      <c r="I362" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14197,9 +13109,6 @@
         <v>10.8036</v>
       </c>
       <c r="H363" t="n">
-        <v>219.4278</v>
-      </c>
-      <c r="I363" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14234,9 +13143,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H364" t="n">
-        <v>219.0944666666667</v>
-      </c>
-      <c r="I364" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14273,9 +13179,6 @@
         <v>10.86</v>
       </c>
       <c r="H365" t="n">
-        <v>208.2344666666667</v>
-      </c>
-      <c r="I365" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14310,9 +13213,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H366" t="n">
-        <v>207.4428</v>
-      </c>
-      <c r="I366" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14349,9 +13249,6 @@
         <v>10.8036</v>
       </c>
       <c r="H367" t="n">
-        <v>196.6392</v>
-      </c>
-      <c r="I367" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14386,9 +13283,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H368" t="n">
-        <v>196.3058666666667</v>
-      </c>
-      <c r="I368" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14425,9 +13319,6 @@
         <v>10.86</v>
       </c>
       <c r="H369" t="n">
-        <v>185.4458666666667</v>
-      </c>
-      <c r="I369" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14462,9 +13353,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H370" t="n">
-        <v>184.6542</v>
-      </c>
-      <c r="I370" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14501,9 +13389,6 @@
         <v>10.8036</v>
       </c>
       <c r="H371" t="n">
-        <v>173.8506</v>
-      </c>
-      <c r="I371" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14538,9 +13423,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H372" t="n">
-        <v>173.5172666666667</v>
-      </c>
-      <c r="I372" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14577,9 +13459,6 @@
         <v>10.86</v>
       </c>
       <c r="H373" t="n">
-        <v>162.6572666666667</v>
-      </c>
-      <c r="I373" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14614,9 +13493,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H374" t="n">
-        <v>161.8656</v>
-      </c>
-      <c r="I374" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14653,9 +13529,6 @@
         <v>10.8036</v>
       </c>
       <c r="H375" t="n">
-        <v>151.062</v>
-      </c>
-      <c r="I375" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14690,9 +13563,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H376" t="n">
-        <v>150.7286666666667</v>
-      </c>
-      <c r="I376" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14729,9 +13599,6 @@
         <v>10.86</v>
       </c>
       <c r="H377" t="n">
-        <v>139.8686666666667</v>
-      </c>
-      <c r="I377" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14766,9 +13633,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H378" t="n">
-        <v>139.077</v>
-      </c>
-      <c r="I378" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14805,9 +13669,6 @@
         <v>10.8036</v>
       </c>
       <c r="H379" t="n">
-        <v>128.2734</v>
-      </c>
-      <c r="I379" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14842,9 +13703,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H380" t="n">
-        <v>127.9400666666667</v>
-      </c>
-      <c r="I380" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14881,9 +13739,6 @@
         <v>10.86</v>
       </c>
       <c r="H381" t="n">
-        <v>117.0800666666667</v>
-      </c>
-      <c r="I381" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14918,9 +13773,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H382" t="n">
-        <v>116.2884</v>
-      </c>
-      <c r="I382" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14957,9 +13809,6 @@
         <v>10.8036</v>
       </c>
       <c r="H383" t="n">
-        <v>105.4848</v>
-      </c>
-      <c r="I383" t="n">
         <v>7</v>
       </c>
     </row>
@@ -14994,9 +13843,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H384" t="n">
-        <v>105.1514666666667</v>
-      </c>
-      <c r="I384" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15033,9 +13879,6 @@
         <v>10.86</v>
       </c>
       <c r="H385" t="n">
-        <v>94.29146666666668</v>
-      </c>
-      <c r="I385" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15070,9 +13913,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H386" t="n">
-        <v>93.49980000000001</v>
-      </c>
-      <c r="I386" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15109,9 +13949,6 @@
         <v>10.8036</v>
       </c>
       <c r="H387" t="n">
-        <v>82.6962</v>
-      </c>
-      <c r="I387" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15146,9 +13983,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H388" t="n">
-        <v>82.36286666666668</v>
-      </c>
-      <c r="I388" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15185,9 +14019,6 @@
         <v>10.86</v>
       </c>
       <c r="H389" t="n">
-        <v>71.50286666666668</v>
-      </c>
-      <c r="I389" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15222,9 +14053,6 @@
         <v>0.9583333333333334</v>
       </c>
       <c r="H390" t="n">
-        <v>70.54453333333335</v>
-      </c>
-      <c r="I390" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15261,9 +14089,6 @@
         <v>12.8496</v>
       </c>
       <c r="H391" t="n">
-        <v>57.69493333333335</v>
-      </c>
-      <c r="I391" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15298,9 +14123,6 @@
         <v>0.5</v>
       </c>
       <c r="H392" t="n">
-        <v>57.19493333333335</v>
-      </c>
-      <c r="I392" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15337,9 +14159,6 @@
         <v>12.3</v>
       </c>
       <c r="H393" t="n">
-        <v>44.89493333333336</v>
-      </c>
-      <c r="I393" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15374,9 +14193,6 @@
         <v>1.979999999999999</v>
       </c>
       <c r="H394" t="n">
-        <v>42.91493333333336</v>
-      </c>
-      <c r="I394" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15411,9 +14227,6 @@
         <v>-142.5</v>
       </c>
       <c r="H395" t="n">
-        <v>185.4149333333334</v>
-      </c>
-      <c r="I395" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15448,9 +14261,6 @@
         <v>1.98</v>
       </c>
       <c r="H396" t="n">
-        <v>183.4349333333334</v>
-      </c>
-      <c r="I396" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15485,9 +14295,6 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H397" t="n">
-        <v>182.5182666666667</v>
-      </c>
-      <c r="I397" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15524,9 +14331,6 @@
         <v>10.8036</v>
       </c>
       <c r="H398" t="n">
-        <v>171.7146666666667</v>
-      </c>
-      <c r="I398" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15561,9 +14365,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H399" t="n">
-        <v>171.3813333333334</v>
-      </c>
-      <c r="I399" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15600,9 +14401,6 @@
         <v>10.86</v>
       </c>
       <c r="H400" t="n">
-        <v>160.5213333333334</v>
-      </c>
-      <c r="I400" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15637,9 +14435,6 @@
         <v>1.625</v>
       </c>
       <c r="H401" t="n">
-        <v>158.8963333333334</v>
-      </c>
-      <c r="I401" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15676,9 +14471,6 @@
         <v>10.8036</v>
       </c>
       <c r="H402" t="n">
-        <v>148.0927333333334</v>
-      </c>
-      <c r="I402" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15713,9 +14505,6 @@
         <v>1.583333333333333</v>
       </c>
       <c r="H403" t="n">
-        <v>146.5094</v>
-      </c>
-      <c r="I403" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15752,9 +14541,6 @@
         <v>10.86</v>
       </c>
       <c r="H404" t="n">
-        <v>135.6494</v>
-      </c>
-      <c r="I404" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15789,9 +14575,6 @@
         <v>10.32</v>
       </c>
       <c r="H405" t="n">
-        <v>125.3294</v>
-      </c>
-      <c r="I405" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15826,9 +14609,6 @@
         <v>0.04166666666666666</v>
       </c>
       <c r="H406" t="n">
-        <v>125.2877333333333</v>
-      </c>
-      <c r="I406" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15865,9 +14645,6 @@
         <v>12.3</v>
       </c>
       <c r="H407" t="n">
-        <v>112.9877333333334</v>
-      </c>
-      <c r="I407" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15902,9 +14679,6 @@
         <v>10.32</v>
       </c>
       <c r="H408" t="n">
-        <v>102.6677333333334</v>
-      </c>
-      <c r="I408" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15939,9 +14713,6 @@
         <v>2.916666666666667</v>
       </c>
       <c r="H409" t="n">
-        <v>99.75106666666669</v>
-      </c>
-      <c r="I409" t="n">
         <v>7</v>
       </c>
     </row>
@@ -15978,9 +14749,6 @@
         <v>12.3</v>
       </c>
       <c r="H410" t="n">
-        <v>87.45106666666669</v>
-      </c>
-      <c r="I410" t="n">
         <v>7</v>
       </c>
     </row>
@@ -16015,9 +14783,6 @@
         <v>10.32</v>
       </c>
       <c r="H411" t="n">
-        <v>77.1310666666667</v>
-      </c>
-      <c r="I411" t="n">
         <v>7</v>
       </c>
     </row>
@@ -16052,9 +14817,6 @@
         <v>15.08333333333333</v>
       </c>
       <c r="H412" t="n">
-        <v>62.04773333333337</v>
-      </c>
-      <c r="I412" t="n">
         <v>7</v>
       </c>
     </row>
@@ -16091,9 +14853,6 @@
         <v>10.86</v>
       </c>
       <c r="H413" t="n">
-        <v>51.18773333333337</v>
-      </c>
-      <c r="I413" t="n">
         <v>7</v>
       </c>
     </row>
@@ -16130,9 +14889,6 @@
         <v>1.98</v>
       </c>
       <c r="H414" t="n">
-        <v>253.02</v>
-      </c>
-      <c r="I414" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16169,9 +14925,6 @@
         <v>10.8036</v>
       </c>
       <c r="H415" t="n">
-        <v>242.2164</v>
-      </c>
-      <c r="I415" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16206,9 +14959,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H416" t="n">
-        <v>241.8830666666667</v>
-      </c>
-      <c r="I416" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16245,9 +14995,6 @@
         <v>10.86</v>
       </c>
       <c r="H417" t="n">
-        <v>231.0230666666667</v>
-      </c>
-      <c r="I417" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16282,9 +15029,6 @@
         <v>0.375</v>
       </c>
       <c r="H418" t="n">
-        <v>230.6480666666667</v>
-      </c>
-      <c r="I418" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16321,9 +15065,6 @@
         <v>12.8496</v>
       </c>
       <c r="H419" t="n">
-        <v>217.7984666666667</v>
-      </c>
-      <c r="I419" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16358,9 +15099,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H420" t="n">
-        <v>216.9651333333333</v>
-      </c>
-      <c r="I420" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16397,9 +15135,6 @@
         <v>10.86</v>
       </c>
       <c r="H421" t="n">
-        <v>206.1051333333333</v>
-      </c>
-      <c r="I421" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16434,9 +15169,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H422" t="n">
-        <v>205.3134666666666</v>
-      </c>
-      <c r="I422" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16473,9 +15205,6 @@
         <v>10.8036</v>
       </c>
       <c r="H423" t="n">
-        <v>194.5098666666667</v>
-      </c>
-      <c r="I423" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16510,9 +15239,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H424" t="n">
-        <v>194.0932</v>
-      </c>
-      <c r="I424" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16549,9 +15275,6 @@
         <v>12.3</v>
       </c>
       <c r="H425" t="n">
-        <v>181.7932</v>
-      </c>
-      <c r="I425" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16586,9 +15309,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H426" t="n">
-        <v>181.3765333333334</v>
-      </c>
-      <c r="I426" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16625,9 +15345,6 @@
         <v>12.8496</v>
       </c>
       <c r="H427" t="n">
-        <v>168.5269333333333</v>
-      </c>
-      <c r="I427" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16662,9 +15379,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H428" t="n">
-        <v>167.6936</v>
-      </c>
-      <c r="I428" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16701,9 +15415,6 @@
         <v>10.86</v>
       </c>
       <c r="H429" t="n">
-        <v>156.8336</v>
-      </c>
-      <c r="I429" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16738,9 +15449,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H430" t="n">
-        <v>156.0419333333333</v>
-      </c>
-      <c r="I430" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16777,9 +15485,6 @@
         <v>10.8036</v>
       </c>
       <c r="H431" t="n">
-        <v>145.2383333333333</v>
-      </c>
-      <c r="I431" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16814,9 +15519,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H432" t="n">
-        <v>144.8216666666667</v>
-      </c>
-      <c r="I432" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16853,9 +15555,6 @@
         <v>12.3</v>
       </c>
       <c r="H433" t="n">
-        <v>132.5216666666667</v>
-      </c>
-      <c r="I433" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16890,9 +15589,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H434" t="n">
-        <v>132.105</v>
-      </c>
-      <c r="I434" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16929,9 +15625,6 @@
         <v>12.8496</v>
       </c>
       <c r="H435" t="n">
-        <v>119.2554000000001</v>
-      </c>
-      <c r="I435" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16966,9 +15659,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H436" t="n">
-        <v>118.4220666666667</v>
-      </c>
-      <c r="I436" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17005,9 +15695,6 @@
         <v>10.86</v>
       </c>
       <c r="H437" t="n">
-        <v>107.5620666666667</v>
-      </c>
-      <c r="I437" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17042,9 +15729,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H438" t="n">
-        <v>106.7704000000001</v>
-      </c>
-      <c r="I438" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17081,9 +15765,6 @@
         <v>10.8036</v>
       </c>
       <c r="H439" t="n">
-        <v>95.96680000000005</v>
-      </c>
-      <c r="I439" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17118,9 +15799,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H440" t="n">
-        <v>95.63346666666672</v>
-      </c>
-      <c r="I440" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17157,9 +15835,6 @@
         <v>10.86</v>
       </c>
       <c r="H441" t="n">
-        <v>84.77346666666672</v>
-      </c>
-      <c r="I441" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17194,9 +15869,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H442" t="n">
-        <v>83.98180000000005</v>
-      </c>
-      <c r="I442" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17233,9 +15905,6 @@
         <v>10.8036</v>
       </c>
       <c r="H443" t="n">
-        <v>73.17820000000005</v>
-      </c>
-      <c r="I443" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17270,9 +15939,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H444" t="n">
-        <v>72.76153333333338</v>
-      </c>
-      <c r="I444" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17309,9 +15975,6 @@
         <v>12.3</v>
       </c>
       <c r="H445" t="n">
-        <v>60.46153333333338</v>
-      </c>
-      <c r="I445" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17346,9 +16009,6 @@
         <v>1.416666666666667</v>
       </c>
       <c r="H446" t="n">
-        <v>59.04486666666671</v>
-      </c>
-      <c r="I446" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17385,9 +16045,6 @@
         <v>12.8496</v>
       </c>
       <c r="H447" t="n">
-        <v>46.19526666666671</v>
-      </c>
-      <c r="I447" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17422,9 +16079,6 @@
         <v>0.5</v>
       </c>
       <c r="H448" t="n">
-        <v>45.69526666666671</v>
-      </c>
-      <c r="I448" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17461,9 +16115,6 @@
         <v>12.3</v>
       </c>
       <c r="H449" t="n">
-        <v>33.39526666666671</v>
-      </c>
-      <c r="I449" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17498,9 +16149,6 @@
         <v>1.979999999999999</v>
       </c>
       <c r="H450" t="n">
-        <v>31.41526666666671</v>
-      </c>
-      <c r="I450" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17535,9 +16183,6 @@
         <v>-120</v>
       </c>
       <c r="H451" t="n">
-        <v>151.4152666666667</v>
-      </c>
-      <c r="I451" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17572,9 +16217,6 @@
         <v>1.98</v>
       </c>
       <c r="H452" t="n">
-        <v>149.4352666666667</v>
-      </c>
-      <c r="I452" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17609,9 +16251,6 @@
         <v>0.75</v>
       </c>
       <c r="H453" t="n">
-        <v>148.6852666666667</v>
-      </c>
-      <c r="I453" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17648,9 +16287,6 @@
         <v>10.8036</v>
       </c>
       <c r="H454" t="n">
-        <v>137.8816666666667</v>
-      </c>
-      <c r="I454" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17685,9 +16321,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H455" t="n">
-        <v>137.4650000000001</v>
-      </c>
-      <c r="I455" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17724,9 +16357,6 @@
         <v>12.3</v>
       </c>
       <c r="H456" t="n">
-        <v>125.1650000000001</v>
-      </c>
-      <c r="I456" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17761,9 +16391,6 @@
         <v>1.5</v>
       </c>
       <c r="H457" t="n">
-        <v>123.6650000000001</v>
-      </c>
-      <c r="I457" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17800,9 +16427,6 @@
         <v>12.8496</v>
       </c>
       <c r="H458" t="n">
-        <v>110.8154000000001</v>
-      </c>
-      <c r="I458" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17837,9 +16461,6 @@
         <v>10.32</v>
       </c>
       <c r="H459" t="n">
-        <v>100.4954000000001</v>
-      </c>
-      <c r="I459" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17874,9 +16495,6 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="H460" t="n">
-        <v>100.4120666666668</v>
-      </c>
-      <c r="I460" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17913,9 +16531,6 @@
         <v>12.8496</v>
       </c>
       <c r="H461" t="n">
-        <v>87.56246666666677</v>
-      </c>
-      <c r="I461" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17950,9 +16565,6 @@
         <v>10.32</v>
       </c>
       <c r="H462" t="n">
-        <v>77.24246666666676</v>
-      </c>
-      <c r="I462" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17987,9 +16599,6 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="H463" t="n">
-        <v>77.15913333333343</v>
-      </c>
-      <c r="I463" t="n">
         <v>8</v>
       </c>
     </row>
@@ -18026,9 +16635,6 @@
         <v>12.8496</v>
       </c>
       <c r="H464" t="n">
-        <v>64.30953333333343</v>
-      </c>
-      <c r="I464" t="n">
         <v>8</v>
       </c>
     </row>
@@ -18063,9 +16669,6 @@
         <v>8</v>
       </c>
       <c r="H465" t="n">
-        <v>56.30953333333343</v>
-      </c>
-      <c r="I465" t="n">
         <v>8</v>
       </c>
     </row>
@@ -18102,9 +16705,6 @@
         <v>10.86</v>
       </c>
       <c r="H466" t="n">
-        <v>45.44953333333343</v>
-      </c>
-      <c r="I466" t="n">
         <v>8</v>
       </c>
     </row>
@@ -18139,9 +16739,6 @@
         <v>1.979999999999999</v>
       </c>
       <c r="H467" t="n">
-        <v>43.46953333333344</v>
-      </c>
-      <c r="I467" t="n">
         <v>8</v>
       </c>
     </row>
@@ -18176,9 +16773,6 @@
         <v>-193.7264044444444</v>
       </c>
       <c r="H468" t="n">
-        <v>237.1959377777778</v>
-      </c>
-      <c r="I468" t="n">
         <v>8</v>
       </c>
     </row>
@@ -18215,9 +16809,6 @@
         <v>1.98</v>
       </c>
       <c r="H469" t="n">
-        <v>253.02</v>
-      </c>
-      <c r="I469" t="n">
         <v>9</v>
       </c>
     </row>
@@ -18254,9 +16845,6 @@
         <v>10.8036</v>
       </c>
       <c r="H470" t="n">
-        <v>242.2164</v>
-      </c>
-      <c r="I470" t="n">
         <v>9</v>
       </c>
     </row>
@@ -18291,9 +16879,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H471" t="n">
-        <v>241.8830666666667</v>
-      </c>
-      <c r="I471" t="n">
         <v>9</v>
       </c>
     </row>
@@ -18330,9 +16915,6 @@
         <v>10.86</v>
       </c>
       <c r="H472" t="n">
-        <v>231.0230666666667</v>
-      </c>
-      <c r="I472" t="n">
         <v>9</v>
       </c>
     </row>
@@ -18367,9 +16949,6 @@
         <v>0.5416666666666667</v>
       </c>
       <c r="H473" t="n">
-        <v>230.4814</v>
-      </c>
-      <c r="I473" t="n">
         <v>9</v>
       </c>
     </row>
@@ -18406,9 +16985,6 @@
         <v>12.8496</v>
       </c>
       <c r="H474" t="n">
-        <v>217.6318</v>
-      </c>
-      <c r="I474" t="n">
         <v>9</v>
       </c>
     </row>
@@ -18443,9 +17019,6 @@
         <v>0.5</v>
       </c>
       <c r="H475" t="n">
-        <v>217.1318</v>
-      </c>
-      <c r="I475" t="n">
         <v>9</v>
       </c>
     </row>
@@ -18482,9 +17055,6 @@
         <v>12.3</v>
       </c>
       <c r="H476" t="n">
-        <v>204.8318</v>
-      </c>
-      <c r="I476" t="n">
         <v>9</v>
       </c>
     </row>
@@ -18519,9 +17089,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H477" t="n">
-        <v>203.9984666666666</v>
-      </c>
-      <c r="I477" t="n">
         <v>9</v>
       </c>
     </row>
@@ -18558,9 +17125,6 @@
         <v>12.8496</v>
       </c>
       <c r="H478" t="n">
-        <v>191.1488666666666</v>
-      </c>
-      <c r="I478" t="n">
         <v>9</v>
       </c>
     </row>
@@ -18595,9 +17159,6 @@
         <v>0.5</v>
       </c>
       <c r="H479" t="n">
-        <v>190.6488666666666</v>
-      </c>
-      <c r="I479" t="n">
         <v>9</v>
       </c>
     </row>
@@ -18634,9 +17195,6 @@
         <v>12.3</v>
       </c>
       <c r="H480" t="n">
-        <v>178.3488666666667</v>
-      </c>
-      <c r="I480" t="n">
         <v>9</v>
       </c>
     </row>
@@ -18671,9 +17229,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H481" t="n">
-        <v>177.5155333333333</v>
-      </c>
-      <c r="I481" t="n">
         <v>9</v>
       </c>
     </row>
@@ -18710,9 +17265,6 @@
         <v>12.8496</v>
       </c>
       <c r="H482" t="n">
-        <v>164.6659333333333</v>
-      </c>
-      <c r="I482" t="n">
         <v>9</v>
       </c>
     </row>
@@ -18747,9 +17299,6 @@
         <v>0.5</v>
       </c>
       <c r="H483" t="n">
-        <v>164.1659333333333</v>
-      </c>
-      <c r="I483" t="n">
         <v>9</v>
       </c>
     </row>
@@ -18786,9 +17335,6 @@
         <v>12.3</v>
       </c>
       <c r="H484" t="n">
-        <v>151.8659333333333</v>
-      </c>
-      <c r="I484" t="n">
         <v>9</v>
       </c>
     </row>
@@ -18823,9 +17369,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H485" t="n">
-        <v>151.0326</v>
-      </c>
-      <c r="I485" t="n">
         <v>9</v>
       </c>
     </row>
@@ -18862,9 +17405,6 @@
         <v>12.8496</v>
       </c>
       <c r="H486" t="n">
-        <v>138.183</v>
-      </c>
-      <c r="I486" t="n">
         <v>9</v>
       </c>
     </row>
@@ -18899,9 +17439,6 @@
         <v>0.5</v>
       </c>
       <c r="H487" t="n">
-        <v>137.683</v>
-      </c>
-      <c r="I487" t="n">
         <v>9</v>
       </c>
     </row>
@@ -18938,9 +17475,6 @@
         <v>12.3</v>
       </c>
       <c r="H488" t="n">
-        <v>125.383</v>
-      </c>
-      <c r="I488" t="n">
         <v>9</v>
       </c>
     </row>
@@ -18975,9 +17509,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H489" t="n">
-        <v>124.5496666666666</v>
-      </c>
-      <c r="I489" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19014,9 +17545,6 @@
         <v>12.8496</v>
       </c>
       <c r="H490" t="n">
-        <v>111.7000666666666</v>
-      </c>
-      <c r="I490" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19051,9 +17579,6 @@
         <v>0.5</v>
       </c>
       <c r="H491" t="n">
-        <v>111.2000666666666</v>
-      </c>
-      <c r="I491" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19090,9 +17615,6 @@
         <v>12.3</v>
       </c>
       <c r="H492" t="n">
-        <v>98.90006666666665</v>
-      </c>
-      <c r="I492" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19127,9 +17649,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H493" t="n">
-        <v>98.06673333333332</v>
-      </c>
-      <c r="I493" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19166,9 +17685,6 @@
         <v>12.8496</v>
       </c>
       <c r="H494" t="n">
-        <v>85.21713333333332</v>
-      </c>
-      <c r="I494" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19203,9 +17719,6 @@
         <v>0.5</v>
       </c>
       <c r="H495" t="n">
-        <v>84.71713333333332</v>
-      </c>
-      <c r="I495" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19242,9 +17755,6 @@
         <v>12.3</v>
       </c>
       <c r="H496" t="n">
-        <v>72.41713333333333</v>
-      </c>
-      <c r="I496" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19279,9 +17789,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H497" t="n">
-        <v>71.5838</v>
-      </c>
-      <c r="I497" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19318,9 +17825,6 @@
         <v>12.8496</v>
       </c>
       <c r="H498" t="n">
-        <v>58.7342</v>
-      </c>
-      <c r="I498" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19355,9 +17859,6 @@
         <v>0.5</v>
       </c>
       <c r="H499" t="n">
-        <v>58.2342</v>
-      </c>
-      <c r="I499" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19394,9 +17895,6 @@
         <v>12.3</v>
       </c>
       <c r="H500" t="n">
-        <v>45.9342</v>
-      </c>
-      <c r="I500" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19431,9 +17929,6 @@
         <v>1.979999999999999</v>
       </c>
       <c r="H501" t="n">
-        <v>43.95420000000001</v>
-      </c>
-      <c r="I501" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19468,9 +17963,6 @@
         <v>-120</v>
       </c>
       <c r="H502" t="n">
-        <v>163.9542</v>
-      </c>
-      <c r="I502" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19505,9 +17997,6 @@
         <v>1.98</v>
       </c>
       <c r="H503" t="n">
-        <v>161.9742</v>
-      </c>
-      <c r="I503" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19542,9 +18031,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H504" t="n">
-        <v>161.6408666666667</v>
-      </c>
-      <c r="I504" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19581,9 +18067,6 @@
         <v>12.8496</v>
       </c>
       <c r="H505" t="n">
-        <v>148.7912666666667</v>
-      </c>
-      <c r="I505" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19618,9 +18101,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H506" t="n">
-        <v>147.9579333333333</v>
-      </c>
-      <c r="I506" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19657,9 +18137,6 @@
         <v>10.86</v>
       </c>
       <c r="H507" t="n">
-        <v>137.0979333333333</v>
-      </c>
-      <c r="I507" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19694,9 +18171,6 @@
         <v>1.625</v>
       </c>
       <c r="H508" t="n">
-        <v>135.4729333333333</v>
-      </c>
-      <c r="I508" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19733,9 +18207,6 @@
         <v>10.8036</v>
       </c>
       <c r="H509" t="n">
-        <v>124.6693333333333</v>
-      </c>
-      <c r="I509" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19770,9 +18241,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H510" t="n">
-        <v>124.336</v>
-      </c>
-      <c r="I510" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19809,9 +18277,6 @@
         <v>10.86</v>
       </c>
       <c r="H511" t="n">
-        <v>113.476</v>
-      </c>
-      <c r="I511" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19846,9 +18311,6 @@
         <v>1.875</v>
       </c>
       <c r="H512" t="n">
-        <v>111.601</v>
-      </c>
-      <c r="I512" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19885,9 +18347,6 @@
         <v>12.8496</v>
       </c>
       <c r="H513" t="n">
-        <v>98.75139999999999</v>
-      </c>
-      <c r="I513" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19922,9 +18381,6 @@
         <v>1.083333333333333</v>
       </c>
       <c r="H514" t="n">
-        <v>97.66806666666666</v>
-      </c>
-      <c r="I514" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19961,9 +18417,6 @@
         <v>12.3</v>
       </c>
       <c r="H515" t="n">
-        <v>85.36806666666666</v>
-      </c>
-      <c r="I515" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19998,9 +18451,6 @@
         <v>2.083333333333333</v>
       </c>
       <c r="H516" t="n">
-        <v>83.28473333333334</v>
-      </c>
-      <c r="I516" t="n">
         <v>9</v>
       </c>
     </row>
@@ -20037,9 +18487,6 @@
         <v>10.8036</v>
       </c>
       <c r="H517" t="n">
-        <v>72.48113333333333</v>
-      </c>
-      <c r="I517" t="n">
         <v>9</v>
       </c>
     </row>
@@ -20074,9 +18521,6 @@
         <v>9.833333333333332</v>
       </c>
       <c r="H518" t="n">
-        <v>62.6478</v>
-      </c>
-      <c r="I518" t="n">
         <v>9</v>
       </c>
     </row>
@@ -20113,9 +18557,6 @@
         <v>10.86</v>
       </c>
       <c r="H519" t="n">
-        <v>51.7878</v>
-      </c>
-      <c r="I519" t="n">
         <v>9</v>
       </c>
     </row>
@@ -20150,9 +18591,6 @@
         <v>1.979999999999999</v>
       </c>
       <c r="H520" t="n">
-        <v>49.80780000000001</v>
-      </c>
-      <c r="I520" t="n">
         <v>9</v>
       </c>
     </row>
@@ -20187,9 +18625,6 @@
         <v>-205.1922</v>
       </c>
       <c r="H521" t="n">
-        <v>255</v>
-      </c>
-      <c r="I521" t="n">
         <v>9</v>
       </c>
     </row>
@@ -20226,9 +18661,6 @@
         <v>1.98</v>
       </c>
       <c r="H522" t="n">
-        <v>253.02</v>
-      </c>
-      <c r="I522" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20265,9 +18697,6 @@
         <v>12.8496</v>
       </c>
       <c r="H523" t="n">
-        <v>240.1704</v>
-      </c>
-      <c r="I523" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20302,9 +18731,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H524" t="n">
-        <v>239.3370666666667</v>
-      </c>
-      <c r="I524" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20341,9 +18767,6 @@
         <v>10.86</v>
       </c>
       <c r="H525" t="n">
-        <v>228.4770666666666</v>
-      </c>
-      <c r="I525" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20378,9 +18801,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H526" t="n">
-        <v>227.6854</v>
-      </c>
-      <c r="I526" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20417,9 +18837,6 @@
         <v>10.8036</v>
       </c>
       <c r="H527" t="n">
-        <v>216.8818</v>
-      </c>
-      <c r="I527" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20454,9 +18871,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H528" t="n">
-        <v>216.4651333333333</v>
-      </c>
-      <c r="I528" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20493,9 +18907,6 @@
         <v>12.3</v>
       </c>
       <c r="H529" t="n">
-        <v>204.1651333333334</v>
-      </c>
-      <c r="I529" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20530,9 +18941,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H530" t="n">
-        <v>203.7484666666667</v>
-      </c>
-      <c r="I530" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20569,9 +18977,6 @@
         <v>12.8496</v>
       </c>
       <c r="H531" t="n">
-        <v>190.8988666666667</v>
-      </c>
-      <c r="I531" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20606,9 +19011,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H532" t="n">
-        <v>190.0655333333333</v>
-      </c>
-      <c r="I532" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20645,9 +19047,6 @@
         <v>10.86</v>
       </c>
       <c r="H533" t="n">
-        <v>179.2055333333333</v>
-      </c>
-      <c r="I533" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20682,9 +19081,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H534" t="n">
-        <v>178.4138666666667</v>
-      </c>
-      <c r="I534" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20721,9 +19117,6 @@
         <v>10.8036</v>
       </c>
       <c r="H535" t="n">
-        <v>167.6102666666667</v>
-      </c>
-      <c r="I535" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20758,9 +19151,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H536" t="n">
-        <v>167.1936</v>
-      </c>
-      <c r="I536" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20797,9 +19187,6 @@
         <v>12.3</v>
       </c>
       <c r="H537" t="n">
-        <v>154.8936</v>
-      </c>
-      <c r="I537" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20834,9 +19221,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H538" t="n">
-        <v>154.4769333333334</v>
-      </c>
-      <c r="I538" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20873,9 +19257,6 @@
         <v>12.8496</v>
       </c>
       <c r="H539" t="n">
-        <v>141.6273333333334</v>
-      </c>
-      <c r="I539" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20910,9 +19291,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H540" t="n">
-        <v>140.794</v>
-      </c>
-      <c r="I540" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20949,9 +19327,6 @@
         <v>10.86</v>
       </c>
       <c r="H541" t="n">
-        <v>129.934</v>
-      </c>
-      <c r="I541" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20986,9 +19361,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H542" t="n">
-        <v>129.1423333333334</v>
-      </c>
-      <c r="I542" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21025,9 +19397,6 @@
         <v>10.8036</v>
       </c>
       <c r="H543" t="n">
-        <v>118.3387333333334</v>
-      </c>
-      <c r="I543" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21062,9 +19431,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H544" t="n">
-        <v>117.9220666666667</v>
-      </c>
-      <c r="I544" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21101,9 +19467,6 @@
         <v>12.3</v>
       </c>
       <c r="H545" t="n">
-        <v>105.6220666666667</v>
-      </c>
-      <c r="I545" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21138,9 +19501,6 @@
         <v>0.4166666666666666</v>
       </c>
       <c r="H546" t="n">
-        <v>105.2054</v>
-      </c>
-      <c r="I546" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21177,9 +19537,6 @@
         <v>12.8496</v>
       </c>
       <c r="H547" t="n">
-        <v>92.35580000000003</v>
-      </c>
-      <c r="I547" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21214,9 +19571,6 @@
         <v>0.25</v>
       </c>
       <c r="H548" t="n">
-        <v>92.10580000000003</v>
-      </c>
-      <c r="I548" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21253,9 +19607,6 @@
         <v>12.3</v>
       </c>
       <c r="H549" t="n">
-        <v>79.80580000000003</v>
-      </c>
-      <c r="I549" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21290,9 +19641,6 @@
         <v>1.083333333333333</v>
       </c>
       <c r="H550" t="n">
-        <v>78.7224666666667</v>
-      </c>
-      <c r="I550" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21329,9 +19677,6 @@
         <v>12.8496</v>
       </c>
       <c r="H551" t="n">
-        <v>65.87286666666671</v>
-      </c>
-      <c r="I551" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21366,9 +19711,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H552" t="n">
-        <v>65.03953333333338</v>
-      </c>
-      <c r="I552" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21405,9 +19747,6 @@
         <v>10.86</v>
       </c>
       <c r="H553" t="n">
-        <v>54.17953333333338</v>
-      </c>
-      <c r="I553" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21442,9 +19781,6 @@
         <v>1.375</v>
       </c>
       <c r="H554" t="n">
-        <v>52.80453333333338</v>
-      </c>
-      <c r="I554" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21481,9 +19817,6 @@
         <v>12.8496</v>
       </c>
       <c r="H555" t="n">
-        <v>39.95493333333339</v>
-      </c>
-      <c r="I555" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21518,9 +19851,6 @@
         <v>10.8</v>
       </c>
       <c r="H556" t="n">
-        <v>29.15493333333338</v>
-      </c>
-      <c r="I556" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21555,9 +19885,6 @@
         <v>-120</v>
       </c>
       <c r="H557" t="n">
-        <v>149.1549333333334</v>
-      </c>
-      <c r="I557" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21592,9 +19919,6 @@
         <v>1.98</v>
       </c>
       <c r="H558" t="n">
-        <v>147.1749333333334</v>
-      </c>
-      <c r="I558" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21629,9 +19953,6 @@
         <v>1.333333333333333</v>
       </c>
       <c r="H559" t="n">
-        <v>145.8416000000001</v>
-      </c>
-      <c r="I559" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21668,9 +19989,6 @@
         <v>12.8496</v>
       </c>
       <c r="H560" t="n">
-        <v>132.992</v>
-      </c>
-      <c r="I560" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21705,9 +20023,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H561" t="n">
-        <v>132.1586666666667</v>
-      </c>
-      <c r="I561" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21744,9 +20059,6 @@
         <v>10.86</v>
       </c>
       <c r="H562" t="n">
-        <v>121.2986666666667</v>
-      </c>
-      <c r="I562" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21781,9 +20093,6 @@
         <v>2.041666666666667</v>
       </c>
       <c r="H563" t="n">
-        <v>119.257</v>
-      </c>
-      <c r="I563" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21820,9 +20129,6 @@
         <v>10.8036</v>
       </c>
       <c r="H564" t="n">
-        <v>108.4534</v>
-      </c>
-      <c r="I564" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21857,9 +20163,6 @@
         <v>1.583333333333333</v>
       </c>
       <c r="H565" t="n">
-        <v>106.8700666666667</v>
-      </c>
-      <c r="I565" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21896,9 +20199,6 @@
         <v>10.86</v>
       </c>
       <c r="H566" t="n">
-        <v>96.0100666666667</v>
-      </c>
-      <c r="I566" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21933,9 +20233,6 @@
         <v>10.32</v>
       </c>
       <c r="H567" t="n">
-        <v>85.6900666666667</v>
-      </c>
-      <c r="I567" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21970,9 +20267,6 @@
         <v>4.458333333333334</v>
       </c>
       <c r="H568" t="n">
-        <v>81.23173333333337</v>
-      </c>
-      <c r="I568" t="n">
         <v>10</v>
       </c>
     </row>
@@ -22009,9 +20303,6 @@
         <v>10.86</v>
       </c>
       <c r="H569" t="n">
-        <v>70.37173333333337</v>
-      </c>
-      <c r="I569" t="n">
         <v>10</v>
       </c>
     </row>
@@ -22048,9 +20339,6 @@
         <v>1.98</v>
       </c>
       <c r="H570" t="n">
-        <v>253.02</v>
-      </c>
-      <c r="I570" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22087,9 +20375,6 @@
         <v>10.8036</v>
       </c>
       <c r="H571" t="n">
-        <v>242.2164</v>
-      </c>
-      <c r="I571" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22124,9 +20409,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H572" t="n">
-        <v>241.8830666666667</v>
-      </c>
-      <c r="I572" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22163,9 +20445,6 @@
         <v>10.86</v>
       </c>
       <c r="H573" t="n">
-        <v>231.0230666666667</v>
-      </c>
-      <c r="I573" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22200,9 +20479,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H574" t="n">
-        <v>230.2314</v>
-      </c>
-      <c r="I574" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22239,9 +20515,6 @@
         <v>10.8036</v>
       </c>
       <c r="H575" t="n">
-        <v>219.4278</v>
-      </c>
-      <c r="I575" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22276,9 +20549,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H576" t="n">
-        <v>219.0944666666667</v>
-      </c>
-      <c r="I576" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22315,9 +20585,6 @@
         <v>10.86</v>
       </c>
       <c r="H577" t="n">
-        <v>208.2344666666667</v>
-      </c>
-      <c r="I577" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22352,9 +20619,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H578" t="n">
-        <v>207.4428</v>
-      </c>
-      <c r="I578" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22391,9 +20655,6 @@
         <v>10.8036</v>
       </c>
       <c r="H579" t="n">
-        <v>196.6392</v>
-      </c>
-      <c r="I579" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22428,9 +20689,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H580" t="n">
-        <v>196.3058666666667</v>
-      </c>
-      <c r="I580" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22467,9 +20725,6 @@
         <v>10.86</v>
       </c>
       <c r="H581" t="n">
-        <v>185.4458666666667</v>
-      </c>
-      <c r="I581" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22504,9 +20759,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H582" t="n">
-        <v>184.6542</v>
-      </c>
-      <c r="I582" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22543,9 +20795,6 @@
         <v>10.8036</v>
       </c>
       <c r="H583" t="n">
-        <v>173.8506</v>
-      </c>
-      <c r="I583" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22580,9 +20829,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H584" t="n">
-        <v>173.5172666666667</v>
-      </c>
-      <c r="I584" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22619,9 +20865,6 @@
         <v>10.86</v>
       </c>
       <c r="H585" t="n">
-        <v>162.6572666666667</v>
-      </c>
-      <c r="I585" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22656,9 +20899,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H586" t="n">
-        <v>161.8656</v>
-      </c>
-      <c r="I586" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22695,9 +20935,6 @@
         <v>10.8036</v>
       </c>
       <c r="H587" t="n">
-        <v>151.062</v>
-      </c>
-      <c r="I587" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22732,9 +20969,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H588" t="n">
-        <v>150.7286666666667</v>
-      </c>
-      <c r="I588" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22771,9 +21005,6 @@
         <v>10.86</v>
       </c>
       <c r="H589" t="n">
-        <v>139.8686666666667</v>
-      </c>
-      <c r="I589" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22808,9 +21039,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H590" t="n">
-        <v>139.077</v>
-      </c>
-      <c r="I590" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22847,9 +21075,6 @@
         <v>10.8036</v>
       </c>
       <c r="H591" t="n">
-        <v>128.2734</v>
-      </c>
-      <c r="I591" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22884,9 +21109,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H592" t="n">
-        <v>127.9400666666667</v>
-      </c>
-      <c r="I592" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22923,9 +21145,6 @@
         <v>10.86</v>
       </c>
       <c r="H593" t="n">
-        <v>117.0800666666667</v>
-      </c>
-      <c r="I593" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22960,9 +21179,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H594" t="n">
-        <v>116.2884</v>
-      </c>
-      <c r="I594" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22999,9 +21215,6 @@
         <v>10.8036</v>
       </c>
       <c r="H595" t="n">
-        <v>105.4848</v>
-      </c>
-      <c r="I595" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23036,9 +21249,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H596" t="n">
-        <v>105.1514666666667</v>
-      </c>
-      <c r="I596" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23075,9 +21285,6 @@
         <v>10.86</v>
       </c>
       <c r="H597" t="n">
-        <v>94.29146666666668</v>
-      </c>
-      <c r="I597" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23112,9 +21319,6 @@
         <v>1.625</v>
       </c>
       <c r="H598" t="n">
-        <v>92.66646666666668</v>
-      </c>
-      <c r="I598" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23151,9 +21355,6 @@
         <v>10.8036</v>
       </c>
       <c r="H599" t="n">
-        <v>81.86286666666668</v>
-      </c>
-      <c r="I599" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23188,9 +21389,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H600" t="n">
-        <v>81.52953333333335</v>
-      </c>
-      <c r="I600" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23227,9 +21425,6 @@
         <v>10.86</v>
       </c>
       <c r="H601" t="n">
-        <v>70.66953333333335</v>
-      </c>
-      <c r="I601" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23264,9 +21459,6 @@
         <v>0.9583333333333334</v>
       </c>
       <c r="H602" t="n">
-        <v>69.71120000000002</v>
-      </c>
-      <c r="I602" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23303,9 +21495,6 @@
         <v>12.8496</v>
       </c>
       <c r="H603" t="n">
-        <v>56.86160000000002</v>
-      </c>
-      <c r="I603" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23340,9 +21529,6 @@
         <v>0.5</v>
       </c>
       <c r="H604" t="n">
-        <v>56.36160000000002</v>
-      </c>
-      <c r="I604" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23379,9 +21565,6 @@
         <v>12.3</v>
       </c>
       <c r="H605" t="n">
-        <v>44.06160000000003</v>
-      </c>
-      <c r="I605" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23416,9 +21599,6 @@
         <v>1.979999999999999</v>
       </c>
       <c r="H606" t="n">
-        <v>42.08160000000003</v>
-      </c>
-      <c r="I606" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23453,9 +21633,6 @@
         <v>-142.5</v>
       </c>
       <c r="H607" t="n">
-        <v>184.5816</v>
-      </c>
-      <c r="I607" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23490,9 +21667,6 @@
         <v>1.98</v>
       </c>
       <c r="H608" t="n">
-        <v>182.6016</v>
-      </c>
-      <c r="I608" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23527,9 +21701,6 @@
         <v>1.333333333333333</v>
       </c>
       <c r="H609" t="n">
-        <v>181.2682666666667</v>
-      </c>
-      <c r="I609" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23566,9 +21737,6 @@
         <v>12.8496</v>
       </c>
       <c r="H610" t="n">
-        <v>168.4186666666667</v>
-      </c>
-      <c r="I610" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23603,9 +21771,6 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="H611" t="n">
-        <v>167.502</v>
-      </c>
-      <c r="I611" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23642,9 +21807,6 @@
         <v>12.3</v>
       </c>
       <c r="H612" t="n">
-        <v>155.2020000000001</v>
-      </c>
-      <c r="I612" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23679,9 +21841,6 @@
         <v>1.5</v>
       </c>
       <c r="H613" t="n">
-        <v>153.7020000000001</v>
-      </c>
-      <c r="I613" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23718,9 +21877,6 @@
         <v>12.8496</v>
       </c>
       <c r="H614" t="n">
-        <v>140.8524</v>
-      </c>
-      <c r="I614" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23755,9 +21911,6 @@
         <v>10.32</v>
       </c>
       <c r="H615" t="n">
-        <v>130.5324000000001</v>
-      </c>
-      <c r="I615" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23792,9 +21945,6 @@
         <v>1.333333333333333</v>
       </c>
       <c r="H616" t="n">
-        <v>129.1990666666667</v>
-      </c>
-      <c r="I616" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23831,9 +21981,6 @@
         <v>10.8036</v>
       </c>
       <c r="H617" t="n">
-        <v>118.3954666666667</v>
-      </c>
-      <c r="I617" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23868,9 +22015,6 @@
         <v>12.91666666666667</v>
       </c>
       <c r="H618" t="n">
-        <v>105.4788</v>
-      </c>
-      <c r="I618" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23907,9 +22051,6 @@
         <v>10.86</v>
       </c>
       <c r="H619" t="n">
-        <v>94.61880000000004</v>
-      </c>
-      <c r="I619" t="n">
         <v>11</v>
       </c>
     </row>
@@ -23946,9 +22087,6 @@
         <v>1.98</v>
       </c>
       <c r="H620" t="n">
-        <v>253.02</v>
-      </c>
-      <c r="I620" t="n">
         <v>12</v>
       </c>
     </row>
@@ -23985,9 +22123,6 @@
         <v>10.8036</v>
       </c>
       <c r="H621" t="n">
-        <v>242.2164</v>
-      </c>
-      <c r="I621" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24022,9 +22157,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H622" t="n">
-        <v>241.8830666666667</v>
-      </c>
-      <c r="I622" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24061,9 +22193,6 @@
         <v>10.86</v>
       </c>
       <c r="H623" t="n">
-        <v>231.0230666666667</v>
-      </c>
-      <c r="I623" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24098,9 +22227,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H624" t="n">
-        <v>230.2314</v>
-      </c>
-      <c r="I624" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24137,9 +22263,6 @@
         <v>10.8036</v>
       </c>
       <c r="H625" t="n">
-        <v>219.4278</v>
-      </c>
-      <c r="I625" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24174,9 +22297,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H626" t="n">
-        <v>219.0944666666667</v>
-      </c>
-      <c r="I626" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24213,9 +22333,6 @@
         <v>10.86</v>
       </c>
       <c r="H627" t="n">
-        <v>208.2344666666667</v>
-      </c>
-      <c r="I627" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24250,9 +22367,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H628" t="n">
-        <v>207.4428</v>
-      </c>
-      <c r="I628" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24289,9 +22403,6 @@
         <v>10.8036</v>
       </c>
       <c r="H629" t="n">
-        <v>196.6392</v>
-      </c>
-      <c r="I629" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24326,9 +22437,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H630" t="n">
-        <v>196.3058666666667</v>
-      </c>
-      <c r="I630" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24365,9 +22473,6 @@
         <v>10.86</v>
       </c>
       <c r="H631" t="n">
-        <v>185.4458666666667</v>
-      </c>
-      <c r="I631" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24402,9 +22507,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H632" t="n">
-        <v>184.6542</v>
-      </c>
-      <c r="I632" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24441,9 +22543,6 @@
         <v>10.8036</v>
       </c>
       <c r="H633" t="n">
-        <v>173.8506</v>
-      </c>
-      <c r="I633" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24478,9 +22577,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H634" t="n">
-        <v>173.5172666666667</v>
-      </c>
-      <c r="I634" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24517,9 +22613,6 @@
         <v>10.86</v>
       </c>
       <c r="H635" t="n">
-        <v>162.6572666666667</v>
-      </c>
-      <c r="I635" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24554,9 +22647,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H636" t="n">
-        <v>161.8656</v>
-      </c>
-      <c r="I636" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24593,9 +22683,6 @@
         <v>10.8036</v>
       </c>
       <c r="H637" t="n">
-        <v>151.062</v>
-      </c>
-      <c r="I637" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24630,9 +22717,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H638" t="n">
-        <v>150.7286666666667</v>
-      </c>
-      <c r="I638" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24669,9 +22753,6 @@
         <v>10.86</v>
       </c>
       <c r="H639" t="n">
-        <v>139.8686666666667</v>
-      </c>
-      <c r="I639" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24706,9 +22787,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H640" t="n">
-        <v>139.077</v>
-      </c>
-      <c r="I640" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24745,9 +22823,6 @@
         <v>10.8036</v>
       </c>
       <c r="H641" t="n">
-        <v>128.2734</v>
-      </c>
-      <c r="I641" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24782,9 +22857,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H642" t="n">
-        <v>127.9400666666667</v>
-      </c>
-      <c r="I642" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24821,9 +22893,6 @@
         <v>10.86</v>
       </c>
       <c r="H643" t="n">
-        <v>117.0800666666667</v>
-      </c>
-      <c r="I643" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24858,9 +22927,6 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="H644" t="n">
-        <v>116.2884</v>
-      </c>
-      <c r="I644" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24897,9 +22963,6 @@
         <v>10.8036</v>
       </c>
       <c r="H645" t="n">
-        <v>105.4848</v>
-      </c>
-      <c r="I645" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24934,9 +22997,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H646" t="n">
-        <v>105.1514666666667</v>
-      </c>
-      <c r="I646" t="n">
         <v>12</v>
       </c>
     </row>
@@ -24973,9 +23033,6 @@
         <v>10.86</v>
       </c>
       <c r="H647" t="n">
-        <v>94.29146666666668</v>
-      </c>
-      <c r="I647" t="n">
         <v>12</v>
       </c>
     </row>
@@ -25010,9 +23067,6 @@
         <v>1.625</v>
       </c>
       <c r="H648" t="n">
-        <v>92.66646666666668</v>
-      </c>
-      <c r="I648" t="n">
         <v>12</v>
       </c>
     </row>
@@ -25049,9 +23103,6 @@
         <v>10.8036</v>
       </c>
       <c r="H649" t="n">
-        <v>81.86286666666668</v>
-      </c>
-      <c r="I649" t="n">
         <v>12</v>
       </c>
     </row>
@@ -25086,9 +23137,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H650" t="n">
-        <v>81.52953333333335</v>
-      </c>
-      <c r="I650" t="n">
         <v>12</v>
       </c>
     </row>
@@ -25125,9 +23173,6 @@
         <v>10.86</v>
       </c>
       <c r="H651" t="n">
-        <v>70.66953333333335</v>
-      </c>
-      <c r="I651" t="n">
         <v>12</v>
       </c>
     </row>
@@ -25162,9 +23207,6 @@
         <v>0.9583333333333334</v>
       </c>
       <c r="H652" t="n">
-        <v>69.71120000000002</v>
-      </c>
-      <c r="I652" t="n">
         <v>12</v>
       </c>
     </row>
@@ -25201,9 +23243,6 @@
         <v>12.8496</v>
       </c>
       <c r="H653" t="n">
-        <v>56.86160000000002</v>
-      </c>
-      <c r="I653" t="n">
         <v>12</v>
       </c>
     </row>
@@ -25238,9 +23277,6 @@
         <v>0.5</v>
       </c>
       <c r="H654" t="n">
-        <v>56.36160000000002</v>
-      </c>
-      <c r="I654" t="n">
         <v>12</v>
       </c>
     </row>
@@ -25277,9 +23313,6 @@
         <v>12.3</v>
       </c>
       <c r="H655" t="n">
-        <v>44.06160000000003</v>
-      </c>
-      <c r="I655" t="n">
         <v>12</v>
       </c>
     </row>
@@ -25314,9 +23347,6 @@
         <v>1.979999999999999</v>
       </c>
       <c r="H656" t="n">
-        <v>42.08160000000003</v>
-      </c>
-      <c r="I656" t="n">
         <v>12</v>
       </c>
     </row>
@@ -25351,9 +23381,6 @@
         <v>-142.5</v>
       </c>
       <c r="H657" t="n">
-        <v>184.5816</v>
-      </c>
-      <c r="I657" t="n">
         <v>12</v>
       </c>
     </row>
@@ -25388,9 +23415,6 @@
         <v>1.98</v>
       </c>
       <c r="H658" t="n">
-        <v>182.6016</v>
-      </c>
-      <c r="I658" t="n">
         <v>12</v>
       </c>
     </row>
@@ -25425,9 +23449,6 @@
         <v>1.333333333333333</v>
       </c>
       <c r="H659" t="n">
-        <v>181.2682666666667</v>
-      </c>
-      <c r="I659" t="n">
         <v>12</v>
       </c>
     </row>
@@ -25464,9 +23485,6 @@
         <v>12.8496</v>
       </c>
       <c r="H660" t="n">
-        <v>168.4186666666667</v>
-      </c>
-      <c r="I660" t="n">
         <v>12</v>
       </c>
     </row>
@@ -25501,9 +23519,6 @@
         <v>1.5</v>
       </c>
       <c r="H661" t="n">
-        <v>166.9186666666667</v>
-      </c>
-      <c r="I661" t="n">
         <v>12</v>
       </c>
     </row>
@@ -25540,9 +23555,6 @@
         <v>12.3</v>
       </c>
       <c r="H662" t="n">
-        <v>154.6186666666667</v>
-      </c>
-      <c r="I662" t="n">
         <v>12</v>
       </c>
     </row>
@@ -25577,9 +23589,6 @@
         <v>10.32</v>
       </c>
       <c r="H663" t="n">
-        <v>144.2986666666667</v>
-      </c>
-      <c r="I663" t="n">
         <v>12</v>
       </c>
     </row>
@@ -25614,9 +23623,6 @@
         <v>1.333333333333333</v>
       </c>
       <c r="H664" t="n">
-        <v>142.9653333333333</v>
-      </c>
-      <c r="I664" t="n">
         <v>12</v>
       </c>
     </row>
@@ -25653,9 +23659,6 @@
         <v>12.3</v>
       </c>
       <c r="H665" t="n">
-        <v>130.6653333333334</v>
-      </c>
-      <c r="I665" t="n">
         <v>12</v>
       </c>
     </row>
@@ -25690,9 +23693,6 @@
         <v>10.91666666666667</v>
       </c>
       <c r="H666" t="n">
-        <v>119.7486666666667</v>
-      </c>
-      <c r="I666" t="n">
         <v>12</v>
       </c>
     </row>
@@ -25729,9 +23729,6 @@
         <v>10.8036</v>
       </c>
       <c r="H667" t="n">
-        <v>108.9450666666667</v>
-      </c>
-      <c r="I667" t="n">
         <v>12</v>
       </c>
     </row>
@@ -25768,9 +23765,6 @@
         <v>10.8</v>
       </c>
       <c r="H668" t="n">
-        <v>244.2</v>
-      </c>
-      <c r="I668" t="n">
         <v>13</v>
       </c>
     </row>
@@ -25807,9 +23801,6 @@
         <v>12.3</v>
       </c>
       <c r="H669" t="n">
-        <v>231.9</v>
-      </c>
-      <c r="I669" t="n">
         <v>13</v>
       </c>
     </row>
@@ -25844,9 +23835,6 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="H670" t="n">
-        <v>231.7333333333333</v>
-      </c>
-      <c r="I670" t="n">
         <v>13</v>
       </c>
     </row>
@@ -25883,9 +23871,6 @@
         <v>12.8496</v>
       </c>
       <c r="H671" t="n">
-        <v>218.8837333333333</v>
-      </c>
-      <c r="I671" t="n">
         <v>13</v>
       </c>
     </row>
@@ -25920,9 +23905,6 @@
         <v>0.5</v>
       </c>
       <c r="H672" t="n">
-        <v>218.3837333333333</v>
-      </c>
-      <c r="I672" t="n">
         <v>13</v>
       </c>
     </row>
@@ -25959,9 +23941,6 @@
         <v>12.3</v>
       </c>
       <c r="H673" t="n">
-        <v>206.0837333333333</v>
-      </c>
-      <c r="I673" t="n">
         <v>13</v>
       </c>
     </row>
@@ -25996,9 +23975,6 @@
         <v>1.083333333333333</v>
       </c>
       <c r="H674" t="n">
-        <v>205.0004</v>
-      </c>
-      <c r="I674" t="n">
         <v>13</v>
       </c>
     </row>
@@ -26035,9 +24011,6 @@
         <v>12.8496</v>
       </c>
       <c r="H675" t="n">
-        <v>192.1508</v>
-      </c>
-      <c r="I675" t="n">
         <v>13</v>
       </c>
     </row>
@@ -26072,9 +24045,6 @@
         <v>0.8333333333333333</v>
       </c>
       <c r="H676" t="n">
-        <v>191.3174666666666</v>
-      </c>
-      <c r="I676" t="n">
         <v>13</v>
       </c>
     </row>
@@ -26111,9 +24081,6 @@
         <v>10.86</v>
       </c>
       <c r="H677" t="n">
-        <v>180.4574666666666</v>
-      </c>
-      <c r="I677" t="n">
         <v>13</v>
       </c>
     </row>
@@ -26148,9 +24115,6 @@
         <v>1.375</v>
       </c>
       <c r="H678" t="n">
-        <v>179.0824666666666</v>
-      </c>
-      <c r="I678" t="n">
         <v>13</v>
       </c>
     </row>
@@ -26187,9 +24151,6 @@
         <v>12.8496</v>
       </c>
       <c r="H679" t="n">
-        <v>166.2328666666666</v>
-      </c>
-      <c r="I679" t="n">
         <v>13</v>
       </c>
     </row>
@@ -26224,9 +24185,6 @@
         <v>0.5</v>
       </c>
       <c r="H680" t="n">
-        <v>165.7328666666666</v>
-      </c>
-      <c r="I680" t="n">
         <v>13</v>
       </c>
     </row>
@@ -26263,9 +24221,6 @@
         <v>12.3</v>
       </c>
       <c r="H681" t="n">
-        <v>153.4328666666666</v>
-      </c>
-      <c r="I681" t="n">
         <v>13</v>
       </c>
     </row>
@@ -26300,9 +24255,6 @@
         <v>1.916666666666667</v>
       </c>
       <c r="H682" t="n">
-        <v>151.5161999999999</v>
-      </c>
-      <c r="I682" t="n">
         <v>13</v>
       </c>
     </row>
@@ -26339,9 +24291,6 @@
         <v>10.8036</v>
       </c>
       <c r="H683" t="n">
-        <v>140.7126</v>
-      </c>
-      <c r="I683" t="n">
         <v>13</v>
       </c>
     </row>
@@ -26376,9 +24325,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H684" t="n">
-        <v>140.3792666666666</v>
-      </c>
-      <c r="I684" t="n">
         <v>13</v>
       </c>
     </row>
@@ -26415,9 +24361,6 @@
         <v>10.86</v>
       </c>
       <c r="H685" t="n">
-        <v>129.5192666666666</v>
-      </c>
-      <c r="I685" t="n">
         <v>13</v>
       </c>
     </row>
@@ -26452,9 +24395,6 @@
         <v>1.625</v>
       </c>
       <c r="H686" t="n">
-        <v>127.8942666666666</v>
-      </c>
-      <c r="I686" t="n">
         <v>13</v>
       </c>
     </row>
@@ -26491,9 +24431,6 @@
         <v>10.8036</v>
       </c>
       <c r="H687" t="n">
-        <v>117.0906666666666</v>
-      </c>
-      <c r="I687" t="n">
         <v>13</v>
       </c>
     </row>
@@ -26528,9 +24465,6 @@
         <v>2.833333333333333</v>
       </c>
       <c r="H688" t="n">
-        <v>114.2573333333333</v>
-      </c>
-      <c r="I688" t="n">
         <v>13</v>
       </c>
     </row>
@@ -26567,9 +24501,6 @@
         <v>10.86</v>
       </c>
       <c r="H689" t="n">
-        <v>103.3973333333333</v>
-      </c>
-      <c r="I689" t="n">
         <v>13</v>
       </c>
     </row>
@@ -26604,9 +24535,6 @@
         <v>8.958333333333334</v>
       </c>
       <c r="H690" t="n">
-        <v>94.43899999999994</v>
-      </c>
-      <c r="I690" t="n">
         <v>13</v>
       </c>
     </row>
@@ -26643,9 +24571,6 @@
         <v>10.8036</v>
       </c>
       <c r="H691" t="n">
-        <v>83.63539999999993</v>
-      </c>
-      <c r="I691" t="n">
         <v>13</v>
       </c>
     </row>
@@ -26682,9 +24607,6 @@
         <v>10.8</v>
       </c>
       <c r="H692" t="n">
-        <v>244.2</v>
-      </c>
-      <c r="I692" t="n">
         <v>14</v>
       </c>
     </row>
@@ -26721,9 +24643,6 @@
         <v>12.3</v>
       </c>
       <c r="H693" t="n">
-        <v>231.9</v>
-      </c>
-      <c r="I693" t="n">
         <v>14</v>
       </c>
     </row>
@@ -26758,9 +24677,6 @@
         <v>1.416666666666667</v>
       </c>
       <c r="H694" t="n">
-        <v>230.4833333333333</v>
-      </c>
-      <c r="I694" t="n">
         <v>14</v>
       </c>
     </row>
@@ -26797,9 +24713,6 @@
         <v>12.8496</v>
       </c>
       <c r="H695" t="n">
-        <v>217.6337333333333</v>
-      </c>
-      <c r="I695" t="n">
         <v>14</v>
       </c>
     </row>
@@ -26834,9 +24747,6 @@
         <v>0.5</v>
       </c>
       <c r="H696" t="n">
-        <v>217.1337333333333</v>
-      </c>
-      <c r="I696" t="n">
         <v>14</v>
       </c>
     </row>
@@ -26873,9 +24783,6 @@
         <v>12.3</v>
       </c>
       <c r="H697" t="n">
-        <v>204.8337333333333</v>
-      </c>
-      <c r="I697" t="n">
         <v>14</v>
       </c>
     </row>
@@ -26910,9 +24817,6 @@
         <v>1.083333333333333</v>
       </c>
       <c r="H698" t="n">
-        <v>203.7504</v>
-      </c>
-      <c r="I698" t="n">
         <v>14</v>
       </c>
     </row>
@@ -26949,9 +24853,6 @@
         <v>10.8036</v>
       </c>
       <c r="H699" t="n">
-        <v>192.9468</v>
-      </c>
-      <c r="I699" t="n">
         <v>14</v>
       </c>
     </row>
@@ -26986,9 +24887,6 @@
         <v>0.1666666666666667</v>
       </c>
       <c r="H700" t="n">
-        <v>192.7801333333333</v>
-      </c>
-      <c r="I700" t="n">
         <v>14</v>
       </c>
     </row>
@@ -27025,9 +24923,6 @@
         <v>12.3</v>
       </c>
       <c r="H701" t="n">
-        <v>180.4801333333334</v>
-      </c>
-      <c r="I701" t="n">
         <v>14</v>
       </c>
     </row>
@@ -27062,9 +24957,6 @@
         <v>1.916666666666667</v>
       </c>
       <c r="H702" t="n">
-        <v>178.5634666666667</v>
-      </c>
-      <c r="I702" t="n">
         <v>14</v>
       </c>
     </row>
@@ -27101,9 +24993,6 @@
         <v>10.8036</v>
       </c>
       <c r="H703" t="n">
-        <v>167.7598666666667</v>
-      </c>
-      <c r="I703" t="n">
         <v>14</v>
       </c>
     </row>
@@ -27138,9 +25027,6 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="H704" t="n">
-        <v>167.4265333333334</v>
-      </c>
-      <c r="I704" t="n">
         <v>14</v>
       </c>
     </row>
@@ -27177,9 +25063,6 @@
         <v>10.86</v>
       </c>
       <c r="H705" t="n">
-        <v>156.5665333333334</v>
-      </c>
-      <c r="I705" t="n">
         <v>14</v>
       </c>
     </row>
@@ -27214,9 +25097,6 @@
         <v>1.625</v>
       </c>
       <c r="H706" t="n">
-        <v>154.9415333333334</v>
-      </c>
-      <c r="I706" t="n">
         <v>14</v>
       </c>
     </row>
@@ -27253,9 +25133,6 @@
         <v>10.8036</v>
       </c>
       <c r="H707" t="n">
-        <v>144.1379333333334</v>
-      </c>
-      <c r="I707" t="n">
         <v>14</v>
       </c>
     </row>
@@ -27290,9 +25167,6 @@
         <v>1.583333333333333</v>
       </c>
       <c r="H708" t="n">
-        <v>142.5546</v>
-      </c>
-      <c r="I708" t="n">
         <v>14</v>
       </c>
     </row>
@@ -27329,9 +25203,6 @@
         <v>10.86</v>
       </c>
       <c r="H709" t="n">
-        <v>131.6946</v>
-      </c>
-      <c r="I709" t="n">
         <v>14</v>
       </c>
     </row>
@@ -27366,9 +25237,6 @@
         <v>10.32</v>
       </c>
       <c r="H710" t="n">
-        <v>121.3746</v>
-      </c>
-      <c r="I710" t="n">
         <v>14</v>
       </c>
     </row>
@@ -27403,9 +25271,6 @@
         <v>1.208333333333333</v>
       </c>
       <c r="H711" t="n">
-        <v>120.1662666666667</v>
-      </c>
-      <c r="I711" t="n">
         <v>14</v>
       </c>
     </row>
@@ -27442,9 +25307,6 @@
         <v>10.86</v>
       </c>
       <c r="H712" t="n">
-        <v>109.3062666666667</v>
-      </c>
-      <c r="I712" t="n">
         <v>14</v>
       </c>
     </row>
@@ -27479,9 +25341,6 @@
         <v>12.70833333333333</v>
       </c>
       <c r="H713" t="n">
-        <v>96.59793333333336</v>
-      </c>
-      <c r="I713" t="n">
         <v>14</v>
       </c>
     </row>
@@ -27518,9 +25377,6 @@
         <v>10.8036</v>
       </c>
       <c r="H714" t="n">
-        <v>85.79433333333336</v>
-      </c>
-      <c r="I714" t="n">
         <v>14</v>
       </c>
     </row>
@@ -27557,9 +25413,6 @@
         <v>10.8</v>
       </c>
       <c r="H715" t="n">
-        <v>244.2</v>
-      </c>
-      <c r="I715" t="n">
         <v>15</v>
       </c>
     </row>
@@ -27596,9 +25449,6 @@
         <v>10.86</v>
       </c>
       <c r="H716" t="n">
-        <v>233.34</v>
-      </c>
-      <c r="I716" t="n">
         <v>15</v>
       </c>
     </row>
@@ -27633,9 +25483,6 @@
         <v>1.791666666666667</v>
       </c>
       <c r="H717" t="n">
-        <v>231.5483333333333</v>
-      </c>
-      <c r="I717" t="n">
         <v>15</v>
       </c>
     </row>
@@ -27672,9 +25519,6 @@
         <v>12.8496</v>
       </c>
       <c r="H718" t="n">
-        <v>218.6987333333333</v>
-      </c>
-      <c r="I718" t="n">
         <v>15</v>
       </c>
     </row>
@@ -27709,9 +25553,6 @@
         <v>0.5</v>
       </c>
       <c r="H719" t="n">
-        <v>218.1987333333333</v>
-      </c>
-      <c r="I719" t="n">
         <v>15</v>
       </c>
     </row>
@@ -27748,9 +25589,6 @@
         <v>12.3</v>
       </c>
       <c r="H720" t="n">
-        <v>205.8987333333333</v>
-      </c>
-      <c r="I720" t="n">
         <v>15</v>
       </c>
     </row>
@@ -27785,9 +25623,6 @@
         <v>10.32</v>
       </c>
       <c r="H721" t="n">
-        <v>195.5787333333333</v>
-      </c>
-      <c r="I721" t="n">
         <v>15</v>
       </c>
     </row>
@@ -27822,9 +25657,6 @@
         <v>0.08333333333333333</v>
       </c>
       <c r="H722" t="n">
-        <v>195.4954</v>
-      </c>
-      <c r="I722" t="n">
         <v>15</v>
       </c>
     </row>
@@ -27861,9 +25693,6 @@
         <v>12.3</v>
       </c>
       <c r="H723" t="n">
-        <v>183.1954</v>
-      </c>
-      <c r="I723" t="n">
         <v>15</v>
       </c>
     </row>
@@ -27898,9 +25727,6 @@
         <v>1.5</v>
       </c>
       <c r="H724" t="n">
-        <v>181.6954</v>
-      </c>
-      <c r="I724" t="n">
         <v>15</v>
       </c>
     </row>
@@ -27937,9 +25763,6 @@
         <v>10.8036</v>
       </c>
       <c r="H725" t="n">
-        <v>170.8918</v>
-      </c>
-      <c r="I725" t="n">
         <v>15</v>
       </c>
     </row>
@@ -27974,9 +25797,6 @@
         <v>10.32</v>
       </c>
       <c r="H726" t="n">
-        <v>160.5718</v>
-      </c>
-      <c r="I726" t="n">
         <v>15</v>
       </c>
     </row>
@@ -28011,9 +25831,6 @@
         <v>1.916666666666667</v>
       </c>
       <c r="H727" t="n">
-        <v>158.6551333333334</v>
-      </c>
-      <c r="I727" t="n">
         <v>15</v>
       </c>
     </row>
@@ -28050,9 +25867,6 @@
         <v>10.8036</v>
       </c>
       <c r="H728" t="n">
-        <v>147.8515333333334</v>
-      </c>
-      <c r="I728" t="n">
         <v>15</v>
       </c>
     </row>
@@ -28087,9 +25901,6 @@
         <v>10.32</v>
       </c>
       <c r="H729" t="n">
-        <v>137.5315333333334</v>
-      </c>
-      <c r="I729" t="n">
         <v>15</v>
       </c>
     </row>
@@ -28124,9 +25935,6 @@
         <v>12.5</v>
       </c>
       <c r="H730" t="n">
-        <v>125.0315333333334</v>
-      </c>
-      <c r="I730" t="n">
         <v>15</v>
       </c>
     </row>
@@ -28163,9 +25971,6 @@
         <v>10.8036</v>
       </c>
       <c r="H731" t="n">
-        <v>114.2279333333334</v>
-      </c>
-      <c r="I731" t="n">
         <v>15</v>
       </c>
     </row>
